--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2710"/>
+  <dimension ref="A1:G2712"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2502,7 +2502,7 @@
         <v>45822594</v>
       </c>
       <c r="F105">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="106">
@@ -2519,7 +2519,7 @@
         <v>45822531</v>
       </c>
       <c r="F106">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="107">
@@ -3980,7 +3980,7 @@
         <v>00221575</v>
       </c>
       <c r="F178">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="179">
@@ -6852,7 +6852,7 @@
         <v>00221502</v>
       </c>
       <c r="F309">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="310">
@@ -7452,7 +7452,7 @@
         <v>00221477</v>
       </c>
       <c r="F339">
-        <v>3280500</v>
+        <v>243</v>
       </c>
     </row>
     <row r="340">
@@ -8092,7 +8092,7 @@
         <v>00221450</v>
       </c>
       <c r="F371">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="372">
@@ -8475,7 +8475,7 @@
         <v>00221440</v>
       </c>
       <c r="F390">
-        <v>2893000</v>
+        <v>312</v>
       </c>
     </row>
     <row r="391">
@@ -8495,7 +8495,7 @@
         <v>00221440</v>
       </c>
       <c r="F391">
-        <v>2893000</v>
+        <v>312</v>
       </c>
     </row>
     <row r="392">
@@ -8515,7 +8515,7 @@
         <v>00221440</v>
       </c>
       <c r="F392">
-        <v>2893000</v>
+        <v>312</v>
       </c>
     </row>
     <row r="393">
@@ -9475,7 +9475,7 @@
         <v>00221421</v>
       </c>
       <c r="F440">
-        <v>2431000</v>
+        <v>218</v>
       </c>
     </row>
     <row r="441">
@@ -9495,7 +9495,7 @@
         <v>00221421</v>
       </c>
       <c r="F441">
-        <v>2431000</v>
+        <v>218</v>
       </c>
     </row>
     <row r="442">
@@ -9615,7 +9615,7 @@
         <v>00221419</v>
       </c>
       <c r="F447">
-        <v>2010000</v>
+        <v>308</v>
       </c>
     </row>
     <row r="448">
@@ -9875,7 +9875,7 @@
         <v>00221035</v>
       </c>
       <c r="F460">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="461">
@@ -11608,7 +11608,7 @@
         <v>00221182</v>
       </c>
       <c r="F551">
-        <v>4950000</v>
+        <v>422</v>
       </c>
     </row>
     <row r="552">
@@ -11925,7 +11925,7 @@
         <v>38147716</v>
       </c>
       <c r="F567">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G567">
         <v>35000</v>
@@ -11945,7 +11945,7 @@
         <v>38147321</v>
       </c>
       <c r="F568">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G568">
         <v>35000</v>
@@ -11965,7 +11965,7 @@
         <v>38146217</v>
       </c>
       <c r="F569">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G569">
         <v>35000</v>
@@ -13088,7 +13088,7 @@
         <v>00221027</v>
       </c>
       <c r="F625">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="626">
@@ -13388,7 +13388,7 @@
         <v>00221035</v>
       </c>
       <c r="F640">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="641">
@@ -13408,7 +13408,7 @@
         <v>00221040</v>
       </c>
       <c r="F641">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="642">
@@ -13868,7 +13868,7 @@
         <v>00221070</v>
       </c>
       <c r="F664">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="665">
@@ -14228,7 +14228,7 @@
         <v>00221035</v>
       </c>
       <c r="F682">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="683">
@@ -14248,7 +14248,7 @@
         <v>00221050</v>
       </c>
       <c r="F683">
-        <v>2497500</v>
+        <v>185</v>
       </c>
     </row>
     <row r="684">
@@ -14268,7 +14268,7 @@
         <v>00221050</v>
       </c>
       <c r="F684">
-        <v>2497500</v>
+        <v>185</v>
       </c>
     </row>
     <row r="685">
@@ -14871,7 +14871,7 @@
         <v>35978635</v>
       </c>
       <c r="F714">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="715">
@@ -14888,7 +14888,7 @@
         <v>35978537</v>
       </c>
       <c r="F715">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="716">
@@ -20367,7 +20367,7 @@
         <v>34371439</v>
       </c>
       <c r="F999">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1000">
@@ -24305,7 +24305,7 @@
         <v>00221178</v>
       </c>
       <c r="F1207">
-        <v>5670000</v>
+        <v>422</v>
       </c>
     </row>
     <row r="1208">
@@ -24365,7 +24365,7 @@
         <v>00221061</v>
       </c>
       <c r="F1210">
-        <v>2189000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1211">
@@ -24805,7 +24805,7 @@
         <v>00221043</v>
       </c>
       <c r="F1232">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1233">
@@ -25425,7 +25425,7 @@
         <v>00221199</v>
       </c>
       <c r="F1263">
-        <v>2875500</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1264">
@@ -25525,7 +25525,7 @@
         <v>00221027</v>
       </c>
       <c r="F1268">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1269">
@@ -25885,7 +25885,7 @@
         <v>00221199</v>
       </c>
       <c r="F1286">
-        <v>2875500</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1287">
@@ -26785,7 +26785,7 @@
         <v>00221303</v>
       </c>
       <c r="F1331">
-        <v>1957500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1332">
@@ -27005,7 +27005,7 @@
         <v>00221349</v>
       </c>
       <c r="F1342">
-        <v>2960700</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1343">
@@ -27065,7 +27065,7 @@
         <v>00221043</v>
       </c>
       <c r="F1345">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1346">
@@ -27165,7 +27165,7 @@
         <v>00221043</v>
       </c>
       <c r="F1350">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1351">
@@ -27305,7 +27305,7 @@
         <v>00221303</v>
       </c>
       <c r="F1357">
-        <v>1957500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1358">
@@ -27745,7 +27745,7 @@
         <v>00221082</v>
       </c>
       <c r="F1379">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1380">
@@ -28261,7 +28261,7 @@
         <v>00221266</v>
       </c>
       <c r="F1403">
-        <v>1190000</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1404">
@@ -28341,7 +28341,7 @@
         <v>00221266</v>
       </c>
       <c r="F1407">
-        <v>1190000</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1408">
@@ -29755,7 +29755,7 @@
         <v>00221166</v>
       </c>
       <c r="F1472">
-        <v>4301000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1473">
@@ -29875,7 +29875,7 @@
         <v>00221166</v>
       </c>
       <c r="F1478">
-        <v>4301000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1479">
@@ -30075,7 +30075,7 @@
         <v>00221323</v>
       </c>
       <c r="F1488">
-        <v>3223000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1489">
@@ -30095,7 +30095,7 @@
         <v>00221323</v>
       </c>
       <c r="F1489">
-        <v>3223000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1490">
@@ -30467,7 +30467,7 @@
         <v>00221002</v>
       </c>
       <c r="F1507">
-        <v>3762000</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1508">
@@ -30681,7 +30681,7 @@
         <v>30834962</v>
       </c>
       <c r="F1518">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1519">
@@ -30804,7 +30804,7 @@
         <v>00221070</v>
       </c>
       <c r="F1524">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1525">
@@ -30824,7 +30824,7 @@
         <v>00221070</v>
       </c>
       <c r="F1525">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1526">
@@ -30930,7 +30930,7 @@
         <v>00221195</v>
       </c>
       <c r="F1530">
-        <v>2365000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1531">
@@ -30950,7 +30950,7 @@
         <v>00221195</v>
       </c>
       <c r="F1531">
-        <v>2365000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1532">
@@ -31099,7 +31099,7 @@
         <v>00221322</v>
       </c>
       <c r="F1538">
-        <v>4351200</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1539">
@@ -31409,7 +31409,7 @@
         <v>00221002</v>
       </c>
       <c r="F1552">
-        <v>3762000</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1553">
@@ -31872,7 +31872,7 @@
         <v>00221056</v>
       </c>
       <c r="F1575">
-        <v>5373500</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1576">
@@ -32132,7 +32132,7 @@
         <v>00221038</v>
       </c>
       <c r="F1588">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1589">
@@ -32152,7 +32152,7 @@
         <v>00221038</v>
       </c>
       <c r="F1589">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1590">
@@ -32492,7 +32492,7 @@
         <v>00221056</v>
       </c>
       <c r="F1606">
-        <v>5373500</v>
+        <v>528</v>
       </c>
     </row>
     <row r="1607">
@@ -32693,7 +32693,7 @@
         <v>00221262</v>
       </c>
       <c r="F1615">
-        <v>155</v>
+        <v>2092500</v>
       </c>
     </row>
     <row r="1616">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>3252600</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1619">
@@ -33096,7 +33096,7 @@
         <v>55003389</v>
       </c>
       <c r="F1635">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1636">
@@ -34351,7 +34351,7 @@
         <v>48696472</v>
       </c>
       <c r="F1703">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1704">
@@ -34368,7 +34368,7 @@
         <v>48696438</v>
       </c>
       <c r="F1704">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1705">
@@ -34385,7 +34385,7 @@
         <v>48696304</v>
       </c>
       <c r="F1705">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1706">
@@ -34402,7 +34402,7 @@
         <v>48696268</v>
       </c>
       <c r="F1706">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1707">
@@ -34419,7 +34419,7 @@
         <v>48484996</v>
       </c>
       <c r="F1707">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1708">
@@ -34436,7 +34436,7 @@
         <v>48005865</v>
       </c>
       <c r="F1708">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1709">
@@ -34453,7 +34453,7 @@
         <v>48005831</v>
       </c>
       <c r="F1709">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1710">
@@ -34470,7 +34470,7 @@
         <v>48005800</v>
       </c>
       <c r="F1710">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1711">
@@ -34487,7 +34487,7 @@
         <v>48005774</v>
       </c>
       <c r="F1711">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1712">
@@ -34504,7 +34504,7 @@
         <v>48004979</v>
       </c>
       <c r="F1712">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1713">
@@ -34521,7 +34521,7 @@
         <v>48004895</v>
       </c>
       <c r="F1713">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1714">
@@ -34538,7 +34538,7 @@
         <v>48004738</v>
       </c>
       <c r="F1714">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1715">
@@ -34555,7 +34555,7 @@
         <v>49176643</v>
       </c>
       <c r="F1715">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1715">
         <v>974800</v>
@@ -34575,7 +34575,7 @@
         <v>49095632</v>
       </c>
       <c r="F1716">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1716">
         <v>657500</v>
@@ -34595,7 +34595,7 @@
         <v>48005692</v>
       </c>
       <c r="F1717">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1718">
@@ -34612,7 +34612,7 @@
         <v>48805764</v>
       </c>
       <c r="F1718">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1719">
@@ -34629,7 +34629,7 @@
         <v>48499213</v>
       </c>
       <c r="F1719">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1719">
         <v>450000</v>
@@ -34649,7 +34649,7 @@
         <v>48499173</v>
       </c>
       <c r="F1720">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1720">
         <v>1740000</v>
@@ -34669,7 +34669,7 @@
         <v>48483945</v>
       </c>
       <c r="F1721">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1721">
         <v>1740000</v>
@@ -34689,7 +34689,7 @@
         <v>48483874</v>
       </c>
       <c r="F1722">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1722">
         <v>590000</v>
@@ -34709,7 +34709,7 @@
         <v>48483840</v>
       </c>
       <c r="F1723">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1723">
         <v>590000</v>
@@ -34729,7 +34729,7 @@
         <v>47445192</v>
       </c>
       <c r="F1724">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1725">
@@ -34746,7 +34746,7 @@
         <v>47445075</v>
       </c>
       <c r="F1725">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1726">
@@ -34763,7 +34763,7 @@
         <v>44470822</v>
       </c>
       <c r="F1726">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1727">
@@ -34780,7 +34780,7 @@
         <v>43636861</v>
       </c>
       <c r="F1727">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1728">
@@ -34814,7 +34814,7 @@
         <v>00221680</v>
       </c>
       <c r="F1729">
-        <v>1639000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1730">
@@ -36228,7 +36228,7 @@
         <v>111111</v>
       </c>
       <c r="F1806">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1807">
@@ -36824,7 +36824,7 @@
         <v>56329672</v>
       </c>
       <c r="F1840">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1840">
         <v>275200</v>
@@ -37541,7 +37541,7 @@
         <v>50000020</v>
       </c>
       <c r="F1876">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1876">
         <v>275200</v>
@@ -37558,7 +37558,7 @@
         <v>50000030</v>
       </c>
       <c r="F1877">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1877">
         <v>275200</v>
@@ -37575,7 +37575,7 @@
         <v>50000040</v>
       </c>
       <c r="F1878">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G1878">
         <v>275200</v>
@@ -38375,7 +38375,7 @@
         <v>221705</v>
       </c>
       <c r="F1918">
-        <v>2719500</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1919">
@@ -38392,7 +38392,7 @@
         <v>00216030</v>
       </c>
       <c r="F1919">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1919">
         <v>1296000</v>
@@ -38432,7 +38432,7 @@
         <v>00216032</v>
       </c>
       <c r="F1921">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1921">
         <v>1296000</v>
@@ -38472,7 +38472,7 @@
         <v>00216034</v>
       </c>
       <c r="F1923">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1923">
         <v>1296000</v>
@@ -38492,7 +38492,7 @@
         <v>00216035</v>
       </c>
       <c r="F1924">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1924">
         <v>1296000</v>
@@ -38512,7 +38512,7 @@
         <v>00216036</v>
       </c>
       <c r="F1925">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1925">
         <v>1296000</v>
@@ -38532,7 +38532,7 @@
         <v>00216037</v>
       </c>
       <c r="F1926">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1926">
         <v>1296000</v>
@@ -38552,7 +38552,7 @@
         <v>00216038</v>
       </c>
       <c r="F1927">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1927">
         <v>1296000</v>
@@ -38572,7 +38572,7 @@
         <v>00216039</v>
       </c>
       <c r="F1928">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1928">
         <v>1296000</v>
@@ -38592,7 +38592,7 @@
         <v>00216040</v>
       </c>
       <c r="F1929">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1929">
         <v>1296000</v>
@@ -38612,7 +38612,7 @@
         <v>00216041</v>
       </c>
       <c r="F1930">
-        <v>1296000</v>
+        <v>900000</v>
       </c>
       <c r="G1930">
         <v>1296000</v>
@@ -38924,7 +38924,7 @@
         <v>57178841</v>
       </c>
       <c r="F1948">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1949">
@@ -38938,7 +38938,7 @@
         <v>56887918</v>
       </c>
       <c r="F1949">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1950">
@@ -38952,7 +38952,7 @@
         <v>56887895</v>
       </c>
       <c r="F1950">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1951">
@@ -38966,7 +38966,7 @@
         <v>57178901</v>
       </c>
       <c r="F1951">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1952">
@@ -38980,7 +38980,7 @@
         <v>57178772</v>
       </c>
       <c r="F1952">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1953">
@@ -39575,7 +39575,7 @@
         <v>00221711</v>
       </c>
       <c r="F1987">
-        <v>2151600</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1988">
@@ -39609,7 +39609,7 @@
         <v>00221709</v>
       </c>
       <c r="F1989">
-        <v>2807700</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1990">
@@ -39762,7 +39762,7 @@
         <v>00221726</v>
       </c>
       <c r="F1998">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1999">
@@ -40990,7 +40990,7 @@
         <v>00220029</v>
       </c>
       <c r="F2063">
-        <v>1320000</v>
+        <v>2040000</v>
       </c>
       <c r="G2063">
         <v>980000</v>
@@ -41010,7 +41010,7 @@
         <v>00220029</v>
       </c>
       <c r="F2064">
-        <v>1320000</v>
+        <v>2040000</v>
       </c>
       <c r="G2064">
         <v>980000</v>
@@ -41030,7 +41030,7 @@
         <v>00220030</v>
       </c>
       <c r="F2065">
-        <v>1080000</v>
+        <v>2330000</v>
       </c>
       <c r="G2065">
         <v>1080000</v>
@@ -42167,7 +42167,7 @@
         <v>64111292</v>
       </c>
       <c r="F2122">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2122">
         <v>3617000</v>
@@ -42198,7 +42198,7 @@
         <v>64690629</v>
       </c>
       <c r="F2124">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2124">
         <v>1550000</v>
@@ -42212,7 +42212,7 @@
         <v>64690614</v>
       </c>
       <c r="F2125">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2125">
         <v>1550000</v>
@@ -42226,7 +42226,7 @@
         <v>64690581</v>
       </c>
       <c r="F2126">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2126">
         <v>1550000</v>
@@ -42240,7 +42240,7 @@
         <v>64690544</v>
       </c>
       <c r="F2127">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2127">
         <v>1550000</v>
@@ -42254,7 +42254,7 @@
         <v>64690511</v>
       </c>
       <c r="F2128">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2128">
         <v>1550000</v>
@@ -42557,7 +42557,7 @@
         <v>64428822</v>
       </c>
       <c r="F2146">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2146">
         <v>765450</v>
@@ -42571,7 +42571,7 @@
         <v>64333086</v>
       </c>
       <c r="F2147">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2147">
         <v>2256660</v>
@@ -42585,7 +42585,7 @@
         <v>64333041</v>
       </c>
       <c r="F2148">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2148">
         <v>1128330</v>
@@ -42599,7 +42599,7 @@
         <v>64332133</v>
       </c>
       <c r="F2149">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2149">
         <v>2608200</v>
@@ -42613,7 +42613,7 @@
         <v>64332096</v>
       </c>
       <c r="F2150">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2150">
         <v>1304100</v>
@@ -42627,7 +42627,7 @@
         <v>64331568</v>
       </c>
       <c r="F2151">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2151">
         <v>680400</v>
@@ -42641,7 +42641,7 @@
         <v>64331041</v>
       </c>
       <c r="F2152">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2152">
         <v>1338120</v>
@@ -42655,7 +42655,7 @@
         <v>64329671</v>
       </c>
       <c r="F2153">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2153">
         <v>765450</v>
@@ -42669,7 +42669,7 @@
         <v>64328929</v>
       </c>
       <c r="F2154">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2154">
         <v>1020600</v>
@@ -42683,7 +42683,7 @@
         <v>64328529</v>
       </c>
       <c r="F2155">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2155">
         <v>1020600</v>
@@ -42697,7 +42697,7 @@
         <v>64305454</v>
       </c>
       <c r="F2156">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2156">
         <v>517140</v>
@@ -42711,7 +42711,7 @@
         <v>64305180</v>
       </c>
       <c r="F2157">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2157">
         <v>901530</v>
@@ -42725,7 +42725,7 @@
         <v>64305020</v>
       </c>
       <c r="F2158">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2158">
         <v>561330</v>
@@ -42739,7 +42739,7 @@
         <v>64295538</v>
       </c>
       <c r="F2159">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2159">
         <v>425250</v>
@@ -42753,7 +42753,7 @@
         <v>64295369</v>
       </c>
       <c r="F2160">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2160">
         <v>878850</v>
@@ -42767,7 +42767,7 @@
         <v>64295105</v>
       </c>
       <c r="F2161">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2161">
         <v>561330</v>
@@ -42781,7 +42781,7 @@
         <v>64294796</v>
       </c>
       <c r="F2162">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
       <c r="G2162">
         <v>686070</v>
@@ -42868,7 +42868,7 @@
         <v>00230017</v>
       </c>
       <c r="F2168">
-        <v>1928000</v>
+        <v>2020000</v>
       </c>
     </row>
     <row r="2169">
@@ -43134,7 +43134,7 @@
         <v>00230054</v>
       </c>
       <c r="F2187">
-        <v>2080000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="2188">
@@ -43470,7 +43470,7 @@
         <v>00230011</v>
       </c>
       <c r="F2211">
-        <v>2080000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="2212">
@@ -43568,7 +43568,7 @@
         <v>00230019</v>
       </c>
       <c r="F2218">
-        <v>2010000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="2219">
@@ -43582,7 +43582,7 @@
         <v>00230020</v>
       </c>
       <c r="F2219">
-        <v>2010000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="2220">
@@ -43596,7 +43596,7 @@
         <v>00230021</v>
       </c>
       <c r="F2220">
-        <v>2010000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="2221">
@@ -43610,7 +43610,7 @@
         <v>00230022</v>
       </c>
       <c r="F2221">
-        <v>2010000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="2222">
@@ -43708,7 +43708,7 @@
         <v>00230029</v>
       </c>
       <c r="F2228">
-        <v>1912500</v>
+        <v>3049000</v>
       </c>
     </row>
     <row r="2229">
@@ -43736,7 +43736,7 @@
         <v>00230074</v>
       </c>
       <c r="F2230">
-        <v>1722000</v>
+        <v>2710000</v>
       </c>
     </row>
     <row r="2231">
@@ -43778,7 +43778,7 @@
         <v>00230077</v>
       </c>
       <c r="F2233">
-        <v>1912500</v>
+        <v>2710000</v>
       </c>
     </row>
     <row r="2234">
@@ -43901,7 +43901,7 @@
         <v>68580695</v>
       </c>
       <c r="F2242">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2243">
@@ -43912,7 +43912,7 @@
         <v>68580509</v>
       </c>
       <c r="F2243">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2244">
@@ -43923,7 +43923,7 @@
         <v>68580412</v>
       </c>
       <c r="F2244">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2245">
@@ -43934,7 +43934,7 @@
         <v>68580248</v>
       </c>
       <c r="F2245">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2246">
@@ -43945,7 +43945,7 @@
         <v>68580059</v>
       </c>
       <c r="F2246">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2247">
@@ -43956,7 +43956,7 @@
         <v>68579941</v>
       </c>
       <c r="F2247">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2248">
@@ -43967,7 +43967,7 @@
         <v>68579550</v>
       </c>
       <c r="F2248">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2249">
@@ -43978,7 +43978,7 @@
         <v>68579471</v>
       </c>
       <c r="F2249">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2250">
@@ -43989,7 +43989,7 @@
         <v>68579358</v>
       </c>
       <c r="F2250">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2251">
@@ -44000,7 +44000,7 @@
         <v>68579117</v>
       </c>
       <c r="F2251">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2252">
@@ -44011,7 +44011,7 @@
         <v>68579081</v>
       </c>
       <c r="F2252">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2253">
@@ -44022,7 +44022,7 @@
         <v>68578915</v>
       </c>
       <c r="F2253">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2254">
@@ -44033,7 +44033,7 @@
         <v>68578887</v>
       </c>
       <c r="F2254">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2255">
@@ -44044,7 +44044,7 @@
         <v>68578792</v>
       </c>
       <c r="F2255">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2256">
@@ -44055,7 +44055,7 @@
         <v>68578665</v>
       </c>
       <c r="F2256">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2257">
@@ -44066,7 +44066,7 @@
         <v>68577686</v>
       </c>
       <c r="F2257">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2258">
@@ -44077,7 +44077,7 @@
         <v>68577652</v>
       </c>
       <c r="F2258">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2259">
@@ -44088,7 +44088,7 @@
         <v>68576994</v>
       </c>
       <c r="F2259">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2260">
@@ -44099,7 +44099,7 @@
         <v>68576906</v>
       </c>
       <c r="F2260">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2261">
@@ -44110,7 +44110,7 @@
         <v>68573468</v>
       </c>
       <c r="F2261">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2262">
@@ -44121,7 +44121,7 @@
         <v>68573370</v>
       </c>
       <c r="F2262">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2263">
@@ -44132,7 +44132,7 @@
         <v>68572279</v>
       </c>
       <c r="F2263">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2264">
@@ -44143,7 +44143,7 @@
         <v>68315781</v>
       </c>
       <c r="F2264">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2265">
@@ -44154,7 +44154,7 @@
         <v>68315647</v>
       </c>
       <c r="F2265">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2266">
@@ -44165,7 +44165,7 @@
         <v>68297855</v>
       </c>
       <c r="F2266">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2267">
@@ -44176,7 +44176,7 @@
         <v>68297737</v>
       </c>
       <c r="F2267">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2268">
@@ -44187,7 +44187,7 @@
         <v>68297319</v>
       </c>
       <c r="F2268">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2269">
@@ -44198,7 +44198,7 @@
         <v>68289446</v>
       </c>
       <c r="F2269">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2270">
@@ -44223,7 +44223,7 @@
         <v>55555555</v>
       </c>
       <c r="F2271">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2272">
@@ -44234,7 +44234,7 @@
         <v>55555556</v>
       </c>
       <c r="F2272">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2273">
@@ -44242,7 +44242,7 @@
         <v xml:space="preserve">دستمال مرطوب دافی  Q10 </v>
       </c>
       <c r="F2273">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2274">
@@ -45737,7 +45737,7 @@
         <v>72014008</v>
       </c>
       <c r="F2380">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2381">
@@ -46003,7 +46003,7 @@
         <v>00230092</v>
       </c>
       <c r="F2399">
-        <v>2289000</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="2400">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>3252600</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2430">
@@ -46437,7 +46437,7 @@
         <v>00221002</v>
       </c>
       <c r="F2430">
-        <v>3762000</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2431">
@@ -46507,7 +46507,7 @@
         <v>00221056</v>
       </c>
       <c r="F2435">
-        <v>5373500</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2436">
@@ -46521,7 +46521,7 @@
         <v>00221070</v>
       </c>
       <c r="F2436">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2437">
@@ -46801,7 +46801,7 @@
         <v>00230101</v>
       </c>
       <c r="F2456">
-        <v>1065000</v>
+        <v>958000</v>
       </c>
     </row>
     <row r="2457">
@@ -47011,7 +47011,7 @@
         <v>00221349</v>
       </c>
       <c r="F2471">
-        <v>2960700</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2472">
@@ -47109,7 +47109,7 @@
         <v>00221575</v>
       </c>
       <c r="F2478">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2479">
@@ -47123,7 +47123,7 @@
         <v>00221680</v>
       </c>
       <c r="F2479">
-        <v>1639000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2480">
@@ -47137,7 +47137,7 @@
         <v>00221038</v>
       </c>
       <c r="F2480">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2481">
@@ -47221,7 +47221,7 @@
         <v>00221421</v>
       </c>
       <c r="F2486">
-        <v>2431000</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2487">
@@ -47305,7 +47305,7 @@
         <v>00221262</v>
       </c>
       <c r="F2492">
-        <v>155</v>
+        <v>2092500</v>
       </c>
     </row>
     <row r="2493">
@@ -47417,7 +47417,7 @@
         <v>00221450</v>
       </c>
       <c r="F2500">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2501">
@@ -47624,7 +47624,7 @@
         <v>74313106</v>
       </c>
       <c r="F2515">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2516">
@@ -47722,7 +47722,7 @@
         <v>00221070</v>
       </c>
       <c r="F2522">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2523">
@@ -47876,7 +47876,7 @@
         <v>00221082</v>
       </c>
       <c r="F2533">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2534">
@@ -48072,7 +48072,7 @@
         <v>00221323</v>
       </c>
       <c r="F2547">
-        <v>3223000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2548">
@@ -48685,7 +48685,7 @@
         <v>75283541</v>
       </c>
       <c r="F2591">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2592">
@@ -48727,7 +48727,7 @@
         <v>00221349</v>
       </c>
       <c r="F2594">
-        <v>2960700</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2595">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>3252600</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>3252600</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2618">
@@ -49413,7 +49413,7 @@
         <v>00221780</v>
       </c>
       <c r="F2643">
-        <v>1</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2644">
@@ -49525,7 +49525,7 @@
         <v>00221790</v>
       </c>
       <c r="F2651">
-        <v>1</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2652">
@@ -49819,7 +49819,7 @@
         <v>00221760</v>
       </c>
       <c r="F2672">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2673">
@@ -49830,7 +49830,7 @@
         <v>76410461</v>
       </c>
       <c r="F2673">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2674">
@@ -49844,7 +49844,7 @@
         <v>00221764</v>
       </c>
       <c r="F2674">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2675">
@@ -49900,7 +49900,7 @@
         <v>00221809</v>
       </c>
       <c r="F2678">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2679">
@@ -49911,7 +49911,7 @@
         <v>76636716</v>
       </c>
       <c r="F2679">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2680">
@@ -49922,7 +49922,7 @@
         <v>76636706</v>
       </c>
       <c r="F2680">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2681">
@@ -49933,7 +49933,7 @@
         <v>76636688</v>
       </c>
       <c r="F2681">
-        <v>777000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="2682">
@@ -50283,7 +50283,7 @@
         <v>00221816</v>
       </c>
       <c r="F2706">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2707">
@@ -50342,9 +50342,37 @@
         <v>2744500</v>
       </c>
     </row>
+    <row r="2711">
+      <c r="B2711" t="str">
+        <v>مداد لب آدور مدل Waterproof شماره 401</v>
+      </c>
+      <c r="D2711" t="str">
+        <v>79804490</v>
+      </c>
+      <c r="E2711" t="str">
+        <v>00201094</v>
+      </c>
+      <c r="F2711">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="B2712" t="str">
+        <v>کرم مرطوب کننده کامان مدل NORMAL حجم 75 میلی لیتر</v>
+      </c>
+      <c r="D2712" t="str">
+        <v>79804782</v>
+      </c>
+      <c r="E2712" t="str">
+        <v>00324013</v>
+      </c>
+      <c r="F2712">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2710"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2712"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2712"/>
+  <dimension ref="A1:G2720"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>00221283</v>
       </c>
       <c r="F2">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -579,7 +579,7 @@
         <v>00221669</v>
       </c>
       <c r="F9">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -619,7 +619,7 @@
         <v>00221667</v>
       </c>
       <c r="F11">
-        <v>1215000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -1105,7 +1105,7 @@
         <v>00221631</v>
       </c>
       <c r="F35">
-        <v>2057200</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36">
@@ -1645,7 +1645,7 @@
         <v>00221658</v>
       </c>
       <c r="F62">
-        <v>1990000</v>
+        <v>308</v>
       </c>
     </row>
     <row r="63">
@@ -2739,7 +2739,7 @@
         <v>00221594</v>
       </c>
       <c r="F117">
-        <v>1270000</v>
+        <v>191</v>
       </c>
     </row>
     <row r="118">
@@ -3300,7 +3300,7 @@
         <v>00221620</v>
       </c>
       <c r="F144">
-        <v>2587200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="145">
@@ -3340,7 +3340,7 @@
         <v>00221622</v>
       </c>
       <c r="F146">
-        <v>2387000</v>
+        <v>215</v>
       </c>
     </row>
     <row r="147">
@@ -3780,7 +3780,7 @@
         <v>00221571</v>
       </c>
       <c r="F168">
-        <v>3220800</v>
+        <v>289</v>
       </c>
     </row>
     <row r="169">
@@ -7172,7 +7172,7 @@
         <v>00221490</v>
       </c>
       <c r="F325">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="326">
@@ -7212,7 +7212,7 @@
         <v>00221481</v>
       </c>
       <c r="F327">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="328">
@@ -7332,7 +7332,7 @@
         <v>00221487</v>
       </c>
       <c r="F333">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="334">
@@ -7352,7 +7352,7 @@
         <v>00221488</v>
       </c>
       <c r="F334">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="335">
@@ -7472,7 +7472,7 @@
         <v>00221476</v>
       </c>
       <c r="F340">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="341">
@@ -7512,7 +7512,7 @@
         <v>00221474</v>
       </c>
       <c r="F342">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="343">
@@ -7692,7 +7692,7 @@
         <v>00221446</v>
       </c>
       <c r="F351">
-        <v>1804000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="352">
@@ -8152,7 +8152,7 @@
         <v>00221447</v>
       </c>
       <c r="F374">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="375">
@@ -8435,7 +8435,7 @@
         <v>00221312</v>
       </c>
       <c r="F388">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="389">
@@ -8575,7 +8575,7 @@
         <v>00221438</v>
       </c>
       <c r="F395">
-        <v>4156100</v>
+        <v>299</v>
       </c>
     </row>
     <row r="396">
@@ -8655,7 +8655,7 @@
         <v>00221436</v>
       </c>
       <c r="F399">
-        <v>1639000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="400">
@@ -8835,7 +8835,7 @@
         <v>00221431</v>
       </c>
       <c r="F408">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="409">
@@ -9175,7 +9175,7 @@
         <v>00221154</v>
       </c>
       <c r="F425">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="426">
@@ -9255,7 +9255,7 @@
         <v>00221147</v>
       </c>
       <c r="F429">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="430">
@@ -9515,7 +9515,7 @@
         <v>00221420</v>
       </c>
       <c r="F442">
-        <v>2431000</v>
+        <v>218</v>
       </c>
     </row>
     <row r="443">
@@ -9535,7 +9535,7 @@
         <v>00221420</v>
       </c>
       <c r="F443">
-        <v>2431000</v>
+        <v>218</v>
       </c>
     </row>
     <row r="444">
@@ -9675,7 +9675,7 @@
         <v>00221088</v>
       </c>
       <c r="F450">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="451">
@@ -10309,7 +10309,7 @@
         <v>00201002</v>
       </c>
       <c r="F482">
-        <v>1030000</v>
+        <v>3600000</v>
       </c>
       <c r="G482">
         <v>1783500</v>
@@ -12108,7 +12108,7 @@
         <v>00221253</v>
       </c>
       <c r="F576">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="577">
@@ -12168,7 +12168,7 @@
         <v>00221255</v>
       </c>
       <c r="F579">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="580">
@@ -12328,7 +12328,7 @@
         <v>00221087</v>
       </c>
       <c r="F587">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="588">
@@ -12488,7 +12488,7 @@
         <v>00221089</v>
       </c>
       <c r="F595">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="596">
@@ -12588,7 +12588,7 @@
         <v>00221248</v>
       </c>
       <c r="F600">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="601">
@@ -12648,7 +12648,7 @@
         <v>00221085</v>
       </c>
       <c r="F603">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="604">
@@ -12868,7 +12868,7 @@
         <v>00221228</v>
       </c>
       <c r="F614">
-        <v>1215000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="615">
@@ -12888,7 +12888,7 @@
         <v>00221228</v>
       </c>
       <c r="F615">
-        <v>1215000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="616">
@@ -13068,7 +13068,7 @@
         <v>00221018</v>
       </c>
       <c r="F624">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="625">
@@ -13248,7 +13248,7 @@
         <v>00221218</v>
       </c>
       <c r="F633">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="634">
@@ -13568,7 +13568,7 @@
         <v>00221088</v>
       </c>
       <c r="F649">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="650">
@@ -13768,7 +13768,7 @@
         <v>00221154</v>
       </c>
       <c r="F659">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="660">
@@ -13808,7 +13808,7 @@
         <v>00221283</v>
       </c>
       <c r="F661">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="662">
@@ -13888,7 +13888,7 @@
         <v>00221083</v>
       </c>
       <c r="F665">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="666">
@@ -13908,7 +13908,7 @@
         <v>00221083</v>
       </c>
       <c r="F666">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="667">
@@ -14048,7 +14048,7 @@
         <v>00221302</v>
       </c>
       <c r="F673">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="674">
@@ -14168,7 +14168,7 @@
         <v>00221123</v>
       </c>
       <c r="F679">
-        <v>3009600</v>
+        <v>270</v>
       </c>
     </row>
     <row r="680">
@@ -14188,7 +14188,7 @@
         <v>00221147</v>
       </c>
       <c r="F680">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="681">
@@ -14459,7 +14459,7 @@
         <v>00221302</v>
       </c>
       <c r="F694">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="695">
@@ -22999,7 +22999,7 @@
         <v>00201081</v>
       </c>
       <c r="F1142">
-        <v>1610000</v>
+        <v>3450000</v>
       </c>
       <c r="G1142">
         <v>1820000</v>
@@ -23022,7 +23022,7 @@
         <v>00201082</v>
       </c>
       <c r="F1143">
-        <v>2270000</v>
+        <v>3450000</v>
       </c>
       <c r="G1143">
         <v>1820000</v>
@@ -23045,7 +23045,7 @@
         <v>00201083</v>
       </c>
       <c r="F1144">
-        <v>2270000</v>
+        <v>3450000</v>
       </c>
       <c r="G1144">
         <v>1820000</v>
@@ -24325,7 +24325,7 @@
         <v>00221170</v>
       </c>
       <c r="F1208">
-        <v>1210000</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1209">
@@ -24445,7 +24445,7 @@
         <v>00221072</v>
       </c>
       <c r="F1214">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1215">
@@ -24525,7 +24525,7 @@
         <v>00221072</v>
       </c>
       <c r="F1218">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1219">
@@ -24605,7 +24605,7 @@
         <v>00221174</v>
       </c>
       <c r="F1222">
-        <v>4950000</v>
+        <v>422</v>
       </c>
     </row>
     <row r="1223">
@@ -24845,7 +24845,7 @@
         <v>00221239</v>
       </c>
       <c r="F1234">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1235">
@@ -25185,7 +25185,7 @@
         <v>00221147</v>
       </c>
       <c r="F1251">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="1252">
@@ -25585,7 +25585,7 @@
         <v>00221037</v>
       </c>
       <c r="F1271">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1272">
@@ -25605,7 +25605,7 @@
         <v>00221037</v>
       </c>
       <c r="F1272">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1273">
@@ -25625,7 +25625,7 @@
         <v>00221037</v>
       </c>
       <c r="F1273">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1274">
@@ -25685,7 +25685,7 @@
         <v>00221103</v>
       </c>
       <c r="F1276">
-        <v>1479500</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1277">
@@ -25725,7 +25725,7 @@
         <v>00221312</v>
       </c>
       <c r="F1278">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1279">
@@ -26245,7 +26245,7 @@
         <v>00221170</v>
       </c>
       <c r="F1304">
-        <v>1210000</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1305">
@@ -26265,7 +26265,7 @@
         <v>00221312</v>
       </c>
       <c r="F1305">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1306">
@@ -26645,7 +26645,7 @@
         <v>00221306</v>
       </c>
       <c r="F1324">
-        <v>1957500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1325">
@@ -26685,7 +26685,7 @@
         <v>00221196</v>
       </c>
       <c r="F1326">
-        <v>2365000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1327">
@@ -26925,7 +26925,7 @@
         <v>00221348</v>
       </c>
       <c r="F1338">
-        <v>2376000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1339">
@@ -27085,7 +27085,7 @@
         <v>00221037</v>
       </c>
       <c r="F1346">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1347">
@@ -27145,7 +27145,7 @@
         <v>00221352</v>
       </c>
       <c r="F1349">
-        <v>2960700</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1350">
@@ -27265,7 +27265,7 @@
         <v>00221314</v>
       </c>
       <c r="F1355">
-        <v>1957500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1356">
@@ -27325,7 +27325,7 @@
         <v>00221354</v>
       </c>
       <c r="F1358">
-        <v>2376000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1359">
@@ -27405,7 +27405,7 @@
         <v>00221314</v>
       </c>
       <c r="F1362">
-        <v>1957500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1363">
@@ -27525,7 +27525,7 @@
         <v>00221079</v>
       </c>
       <c r="F1368">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1369">
@@ -27989,7 +27989,7 @@
         <v>00201012</v>
       </c>
       <c r="F1390">
-        <v>1420000</v>
+        <v>1770000</v>
       </c>
       <c r="G1390">
         <v>1260000</v>
@@ -28461,7 +28461,7 @@
         <v>00221142</v>
       </c>
       <c r="F1413">
-        <v>4301000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1414">
@@ -28541,7 +28541,7 @@
         <v>00221017</v>
       </c>
       <c r="F1417">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="1418">
@@ -28581,7 +28581,7 @@
         <v>00221017</v>
       </c>
       <c r="F1419">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="1420">
@@ -28601,7 +28601,7 @@
         <v>00221018</v>
       </c>
       <c r="F1420">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="1421">
@@ -28641,7 +28641,7 @@
         <v>00221142</v>
       </c>
       <c r="F1422">
-        <v>4301000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1423">
@@ -29695,7 +29695,7 @@
         <v>00221026</v>
       </c>
       <c r="F1469">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1470">
@@ -30015,7 +30015,7 @@
         <v>00221321</v>
       </c>
       <c r="F1485">
-        <v>3223000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1486">
@@ -30035,7 +30035,7 @@
         <v>00221321</v>
       </c>
       <c r="F1486">
-        <v>3223000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1487">
@@ -30055,7 +30055,7 @@
         <v>00221321</v>
       </c>
       <c r="F1487">
-        <v>3223000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1488">
@@ -30115,7 +30115,7 @@
         <v>00221329</v>
       </c>
       <c r="F1490">
-        <v>1900000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1491">
@@ -30135,7 +30135,7 @@
         <v>00221324</v>
       </c>
       <c r="F1491">
-        <v>3223000</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1492">
@@ -30255,7 +30255,7 @@
         <v>00221140</v>
       </c>
       <c r="F1497">
-        <v>4301000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1498">
@@ -30387,7 +30387,7 @@
         <v>00221039</v>
       </c>
       <c r="F1503">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1504">
@@ -30407,7 +30407,7 @@
         <v>00221039</v>
       </c>
       <c r="F1504">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1505">
@@ -30427,7 +30427,7 @@
         <v>00221039</v>
       </c>
       <c r="F1505">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1506">
@@ -30724,7 +30724,7 @@
         <v>00221134</v>
       </c>
       <c r="F1520">
-        <v>4263600</v>
+        <v>393</v>
       </c>
     </row>
     <row r="1521">
@@ -31119,7 +31119,7 @@
         <v>00201006</v>
       </c>
       <c r="F1539">
-        <v>1750000</v>
+        <v>2710000</v>
       </c>
       <c r="G1539">
         <v>1522500</v>
@@ -31165,7 +31165,7 @@
         <v>00201009</v>
       </c>
       <c r="F1541">
-        <v>1750000</v>
+        <v>2710000</v>
       </c>
       <c r="G1541">
         <v>1522500</v>
@@ -31188,7 +31188,7 @@
         <v>00201010</v>
       </c>
       <c r="F1542">
-        <v>206030</v>
+        <v>2710000</v>
       </c>
       <c r="G1542">
         <v>1522500</v>
@@ -31211,7 +31211,7 @@
         <v>00201008</v>
       </c>
       <c r="F1543">
-        <v>1650000</v>
+        <v>2710000</v>
       </c>
       <c r="G1543">
         <v>1522500</v>
@@ -31234,7 +31234,7 @@
         <v>00201007</v>
       </c>
       <c r="F1544">
-        <v>1750000</v>
+        <v>2710000</v>
       </c>
       <c r="G1544">
         <v>1522500</v>
@@ -31257,7 +31257,7 @@
         <v>00201011</v>
       </c>
       <c r="F1545">
-        <v>1750000</v>
+        <v>2710000</v>
       </c>
       <c r="G1545">
         <v>1522500</v>
@@ -31280,7 +31280,7 @@
         <v>00201011</v>
       </c>
       <c r="F1546">
-        <v>1750000</v>
+        <v>2710000</v>
       </c>
       <c r="G1546">
         <v>1522500</v>
@@ -31303,7 +31303,7 @@
         <v>00201009</v>
       </c>
       <c r="F1547">
-        <v>1750000</v>
+        <v>2710000</v>
       </c>
       <c r="G1547">
         <v>1522500</v>
@@ -31326,7 +31326,7 @@
         <v>00201006</v>
       </c>
       <c r="F1548">
-        <v>1750000</v>
+        <v>2710000</v>
       </c>
       <c r="G1548">
         <v>1522500</v>
@@ -31766,7 +31766,7 @@
         <v>00221053</v>
       </c>
       <c r="F1570">
-        <v>3047000</v>
+        <v>278</v>
       </c>
     </row>
     <row r="1571">
@@ -32052,7 +32052,7 @@
         <v>00221053</v>
       </c>
       <c r="F1584">
-        <v>3047000</v>
+        <v>278</v>
       </c>
     </row>
     <row r="1585">
@@ -32392,7 +32392,7 @@
         <v>00221218</v>
       </c>
       <c r="F1601">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1602">
@@ -36296,7 +36296,7 @@
         <v>00221687</v>
       </c>
       <c r="F1810">
-        <v>2519000</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1811">
@@ -36568,7 +36568,7 @@
         <v>00221248</v>
       </c>
       <c r="F1826">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1827">
@@ -36636,7 +36636,7 @@
         <v>00221248</v>
       </c>
       <c r="F1830">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1831">
@@ -36753,7 +36753,7 @@
         <v>00216028</v>
       </c>
       <c r="F1836">
-        <v>1150000</v>
+        <v>1750000</v>
       </c>
       <c r="G1836">
         <v>1337000</v>
@@ -37652,7 +37652,7 @@
         <v>00201138</v>
       </c>
       <c r="F1882">
-        <v>1450000</v>
+        <v>3050000</v>
       </c>
       <c r="G1882">
         <v>1542000</v>
@@ -37672,7 +37672,7 @@
         <v>00201139</v>
       </c>
       <c r="F1883">
-        <v>2025000</v>
+        <v>3050000</v>
       </c>
       <c r="G1883">
         <v>1542000</v>
@@ -37692,7 +37692,7 @@
         <v>00201140</v>
       </c>
       <c r="F1884">
-        <v>1220000</v>
+        <v>3050000</v>
       </c>
       <c r="G1884">
         <v>1542000</v>
@@ -37712,7 +37712,7 @@
         <v>00201141</v>
       </c>
       <c r="F1885">
-        <v>1220000</v>
+        <v>3050000</v>
       </c>
       <c r="G1885">
         <v>1542000</v>
@@ -37732,7 +37732,7 @@
         <v>00201142</v>
       </c>
       <c r="F1886">
-        <v>2201530</v>
+        <v>3050000</v>
       </c>
       <c r="G1886">
         <v>1542000</v>
@@ -38072,7 +38072,7 @@
         <v>00201143</v>
       </c>
       <c r="F1903">
-        <v>2135000</v>
+        <v>3600000</v>
       </c>
       <c r="G1903">
         <v>1783500</v>
@@ -38235,7 +38235,7 @@
         <v>221253</v>
       </c>
       <c r="F1911">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1912">
@@ -39490,7 +39490,7 @@
         <v>00221306</v>
       </c>
       <c r="F1982">
-        <v>1957500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1983">
@@ -39779,7 +39779,7 @@
         <v>00221727</v>
       </c>
       <c r="F1999">
-        <v>1705000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2000">
@@ -40068,7 +40068,7 @@
         <v>00221744</v>
       </c>
       <c r="F2016">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2017">
@@ -40119,7 +40119,7 @@
         <v>00221748</v>
       </c>
       <c r="F2019">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2020">
@@ -43008,7 +43008,7 @@
         <v>00230043</v>
       </c>
       <c r="F2178">
-        <v>1810000</v>
+        <v>2450000</v>
       </c>
     </row>
     <row r="2179">
@@ -43652,7 +43652,7 @@
         <v>00230025</v>
       </c>
       <c r="F2224">
-        <v>2010000</v>
+        <v>3060000</v>
       </c>
     </row>
     <row r="2225">
@@ -46017,7 +46017,7 @@
         <v>00230093</v>
       </c>
       <c r="F2400">
-        <v>1307000</v>
+        <v>1740000</v>
       </c>
     </row>
     <row r="2401">
@@ -46031,7 +46031,7 @@
         <v>00230094</v>
       </c>
       <c r="F2401">
-        <v>770000</v>
+        <v>1520000</v>
       </c>
     </row>
     <row r="2402">
@@ -46479,7 +46479,7 @@
         <v>00221037</v>
       </c>
       <c r="F2433">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2434">
@@ -46493,7 +46493,7 @@
         <v>00221039</v>
       </c>
       <c r="F2434">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2435">
@@ -46535,7 +46535,7 @@
         <v>00221142</v>
       </c>
       <c r="F2437">
-        <v>4301000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2438">
@@ -46563,7 +46563,7 @@
         <v>00221248</v>
       </c>
       <c r="F2439">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2440">
@@ -46591,7 +46591,7 @@
         <v>00221314</v>
       </c>
       <c r="F2441">
-        <v>1957500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2442">
@@ -46955,7 +46955,7 @@
         <v>00221026</v>
       </c>
       <c r="F2467">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2468">
@@ -46997,7 +46997,7 @@
         <v>00221348</v>
       </c>
       <c r="F2470">
-        <v>2376000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2471">
@@ -47025,7 +47025,7 @@
         <v>00221352</v>
       </c>
       <c r="F2472">
-        <v>2960700</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2473">
@@ -47053,7 +47053,7 @@
         <v>00221447</v>
       </c>
       <c r="F2474">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2475">
@@ -47151,7 +47151,7 @@
         <v>00221228</v>
       </c>
       <c r="F2481">
-        <v>1215000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2482">
@@ -47207,7 +47207,7 @@
         <v>00221420</v>
       </c>
       <c r="F2485">
-        <v>2431000</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2486">
@@ -47750,7 +47750,7 @@
         <v>00221072</v>
       </c>
       <c r="F2524">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2525">
@@ -47834,7 +47834,7 @@
         <v>00221079</v>
       </c>
       <c r="F2530">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2531">
@@ -47848,7 +47848,7 @@
         <v>00221079</v>
       </c>
       <c r="F2531">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2532">
@@ -47890,7 +47890,7 @@
         <v>00221083</v>
       </c>
       <c r="F2534">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2535">
@@ -47918,7 +47918,7 @@
         <v>00221085</v>
       </c>
       <c r="F2536">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2537">
@@ -47946,7 +47946,7 @@
         <v>00221087</v>
       </c>
       <c r="F2538">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2539">
@@ -47960,7 +47960,7 @@
         <v>00221088</v>
       </c>
       <c r="F2539">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2540">
@@ -48044,7 +48044,7 @@
         <v>00221248</v>
       </c>
       <c r="F2545">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2546">
@@ -48114,7 +48114,7 @@
         <v>00221717</v>
       </c>
       <c r="F2550">
-        <v>2695000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2551">
@@ -48128,7 +48128,7 @@
         <v>00221746</v>
       </c>
       <c r="F2551">
-        <v>2695000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2552">
@@ -48184,7 +48184,7 @@
         <v>00221134</v>
       </c>
       <c r="F2555">
-        <v>4263600</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2556">
@@ -48436,7 +48436,7 @@
         <v>00221754</v>
       </c>
       <c r="F2573">
-        <v>2862000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2574">
@@ -48450,7 +48450,7 @@
         <v>00221755</v>
       </c>
       <c r="F2574">
-        <v>2354000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2575">
@@ -48632,7 +48632,7 @@
         <v>00221283</v>
       </c>
       <c r="F2587">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2588">
@@ -48646,7 +48646,7 @@
         <v>00221712</v>
       </c>
       <c r="F2588">
-        <v>2695000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2589">
@@ -48741,7 +48741,7 @@
         <v>00221352</v>
       </c>
       <c r="F2595">
-        <v>2960700</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2596">
@@ -48783,7 +48783,7 @@
         <v>00221283</v>
       </c>
       <c r="F2598">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2599">
@@ -48867,7 +48867,7 @@
         <v>00221089</v>
       </c>
       <c r="F2604">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2605">
@@ -49077,7 +49077,7 @@
         <v>00221218</v>
       </c>
       <c r="F2619">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2620">
@@ -49091,7 +49091,7 @@
         <v>00221228</v>
       </c>
       <c r="F2620">
-        <v>1215000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2621">
@@ -49133,7 +49133,7 @@
         <v>00221354</v>
       </c>
       <c r="F2623">
-        <v>2376000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2624">
@@ -49189,7 +49189,7 @@
         <v>00221622</v>
       </c>
       <c r="F2627">
-        <v>2387000</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2628">
@@ -49273,7 +49273,7 @@
         <v>00221767</v>
       </c>
       <c r="F2633">
-        <v>1</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2634">
@@ -49399,7 +49399,7 @@
         <v>00221777</v>
       </c>
       <c r="F2642">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2643">
@@ -49483,7 +49483,7 @@
         <v>00221787</v>
       </c>
       <c r="F2648">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2649">
@@ -49567,7 +49567,7 @@
         <v>00221793</v>
       </c>
       <c r="F2654">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2655">
@@ -49581,7 +49581,7 @@
         <v>00221794</v>
       </c>
       <c r="F2655">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2656">
@@ -49637,7 +49637,7 @@
         <v>00221798</v>
       </c>
       <c r="F2659">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2660">
@@ -49665,7 +49665,7 @@
         <v>00221800</v>
       </c>
       <c r="F2661">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2662">
@@ -49749,7 +49749,7 @@
         <v>00221806</v>
       </c>
       <c r="F2667">
-        <v>1</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2668">
@@ -49763,7 +49763,7 @@
         <v>00221807</v>
       </c>
       <c r="F2668">
-        <v>1</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2669">
@@ -49886,7 +49886,7 @@
         <v>00221779</v>
       </c>
       <c r="F2677">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2678">
@@ -50031,7 +50031,7 @@
         <v>00221794</v>
       </c>
       <c r="F2688">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2689">
@@ -50087,7 +50087,7 @@
         <v>00221798</v>
       </c>
       <c r="F2692">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2693">
@@ -50115,7 +50115,7 @@
         <v>00221800</v>
       </c>
       <c r="F2694">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2695">
@@ -50241,7 +50241,7 @@
         <v>00221813</v>
       </c>
       <c r="F2703">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2704">
@@ -50370,9 +50370,121 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2713">
+      <c r="B2713" t="str">
+        <v>رژلب جامد گلدن رز مدل Mix شماره 1 مجموعه 4 عددی</v>
+      </c>
+      <c r="D2713" t="str">
+        <v>79809549</v>
+      </c>
+      <c r="E2713" t="str">
+        <v>00221821</v>
+      </c>
+      <c r="F2713">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="B2714" t="str">
+        <v>ریمل حجم‌دهنده، حالت‌دهنده، بلند‌کننده، جداکننده گلدن رز مدل ICONIC LASH</v>
+      </c>
+      <c r="D2714" t="str">
+        <v>80158453</v>
+      </c>
+      <c r="E2714" t="str">
+        <v>00221825</v>
+      </c>
+      <c r="F2714">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="B2715" t="str">
+        <v>روغن آرگان محافظت‌کننده، شاداب‌کننده، تقویت‌کننده ، ترمیم‌کننده گلدن رز مدل ارگانیک SMOOTH &amp; SHINE مناسب موهای خشک، شکننده، آسیب دیده، انواع مو، کراتین شده، دکلره شده حجم 100 میلی‌لیتر</v>
+      </c>
+      <c r="D2715" t="str">
+        <v>80158484</v>
+      </c>
+      <c r="E2715" t="str">
+        <v>00221826</v>
+      </c>
+      <c r="F2715">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="B2716" t="str">
+        <v>رژگونه مایع مات ورشیپ مدل SMART شماره C01</v>
+      </c>
+      <c r="D2716" t="str">
+        <v>80142413</v>
+      </c>
+      <c r="E2716" t="str">
+        <v>00216053</v>
+      </c>
+      <c r="F2716">
+        <v>3400000</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="B2717" t="str">
+        <v>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C02</v>
+      </c>
+      <c r="D2717" t="str">
+        <v>80158422</v>
+      </c>
+      <c r="E2717" t="str">
+        <v>00216054</v>
+      </c>
+      <c r="F2717">
+        <v>3400000</v>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="B2718" t="str">
+        <v>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C03</v>
+      </c>
+      <c r="D2718" t="str">
+        <v>80158374</v>
+      </c>
+      <c r="E2718" t="str">
+        <v>00216055</v>
+      </c>
+      <c r="F2718">
+        <v>3400000</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="B2719" t="str">
+        <v>رژگونه مایع مات ورشیپ مدل SMART CHEEK شماره C04</v>
+      </c>
+      <c r="D2719" t="str">
+        <v>80158467</v>
+      </c>
+      <c r="E2719" t="str">
+        <v>00216056</v>
+      </c>
+      <c r="F2719">
+        <v>3400000</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="B2720" t="str">
+        <v>محلول تثبیت‌کننده آرایش صورت ایلماز مدل FERESH حجم 120 میلی لیتر</v>
+      </c>
+      <c r="D2720" t="str">
+        <v>80040980</v>
+      </c>
+      <c r="E2720" t="str">
+        <v>00208020</v>
+      </c>
+      <c r="F2720">
+        <v>1750000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2712"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2720"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2720"/>
+  <dimension ref="A1:G2742"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -479,7 +479,7 @@
         <v>00221674</v>
       </c>
       <c r="F4">
-        <v>450000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -599,7 +599,7 @@
         <v>00221668</v>
       </c>
       <c r="F10">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -1565,7 +1565,7 @@
         <v>00221654</v>
       </c>
       <c r="F58">
-        <v>3841200</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59">
@@ -1625,7 +1625,7 @@
         <v>00221657</v>
       </c>
       <c r="F61">
-        <v>3841200</v>
+        <v>345</v>
       </c>
     </row>
     <row r="62">
@@ -1665,7 +1665,7 @@
         <v>00221659</v>
       </c>
       <c r="F63">
-        <v>4158000</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64">
@@ -1685,7 +1685,7 @@
         <v>00221660</v>
       </c>
       <c r="F64">
-        <v>4158000</v>
+        <v>308</v>
       </c>
     </row>
     <row r="65">
@@ -1725,7 +1725,7 @@
         <v>00221662</v>
       </c>
       <c r="F66">
-        <v>3432000</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67">
@@ -2165,7 +2165,7 @@
         <v>00221094</v>
       </c>
       <c r="F88">
-        <v>4675000</v>
+        <v>449</v>
       </c>
     </row>
     <row r="89">
@@ -2325,7 +2325,7 @@
         <v>00221430</v>
       </c>
       <c r="F96">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97">
@@ -2699,7 +2699,7 @@
         <v>00221592</v>
       </c>
       <c r="F115">
-        <v>1270000</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116">
@@ -2759,7 +2759,7 @@
         <v>00221595</v>
       </c>
       <c r="F118">
-        <v>2112000</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119">
@@ -3240,7 +3240,7 @@
         <v>00221617</v>
       </c>
       <c r="F141">
-        <v>2587200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="142">
@@ -3320,7 +3320,7 @@
         <v>00221621</v>
       </c>
       <c r="F145">
-        <v>2587200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146">
@@ -4678,7 +4678,7 @@
         <v>00221521</v>
       </c>
       <c r="F209">
-        <v>1408000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210">
@@ -6632,7 +6632,7 @@
         <v>00221512</v>
       </c>
       <c r="F298">
-        <v>2222000</v>
+        <v>299</v>
       </c>
     </row>
     <row r="299">
@@ -7132,7 +7132,7 @@
         <v>00221534</v>
       </c>
       <c r="F323">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="324">
@@ -7312,7 +7312,7 @@
         <v>00221486</v>
       </c>
       <c r="F332">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="333">
@@ -7732,7 +7732,7 @@
         <v>00221467</v>
       </c>
       <c r="F353">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="354">
@@ -7752,7 +7752,7 @@
         <v>00221466</v>
       </c>
       <c r="F354">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="355">
@@ -8132,7 +8132,7 @@
         <v>00221448</v>
       </c>
       <c r="F373">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="374">
@@ -8855,7 +8855,7 @@
         <v>00221430</v>
       </c>
       <c r="F409">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="410">
@@ -9195,7 +9195,7 @@
         <v>00221150</v>
       </c>
       <c r="F426">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="427">
@@ -9235,7 +9235,7 @@
         <v>00221148</v>
       </c>
       <c r="F428">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="429">
@@ -9435,7 +9435,7 @@
         <v>00221423</v>
       </c>
       <c r="F438">
-        <v>3009600</v>
+        <v>270</v>
       </c>
     </row>
     <row r="439">
@@ -9955,7 +9955,7 @@
         <v>00221412</v>
       </c>
       <c r="F464">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="465">
@@ -12268,7 +12268,7 @@
         <v>00221341</v>
       </c>
       <c r="F584">
-        <v>6534000</v>
+        <v>532</v>
       </c>
     </row>
     <row r="585">
@@ -13268,7 +13268,7 @@
         <v>00221236</v>
       </c>
       <c r="F634">
-        <v>1251000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="635">
@@ -13468,7 +13468,7 @@
         <v>00221279</v>
       </c>
       <c r="F644">
-        <v>3630900</v>
+        <v>247</v>
       </c>
     </row>
     <row r="645">
@@ -13488,7 +13488,7 @@
         <v>00221280</v>
       </c>
       <c r="F645">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="646">
@@ -13628,7 +13628,7 @@
         <v>00221219</v>
       </c>
       <c r="F652">
-        <v>578000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="653">
@@ -13748,7 +13748,7 @@
         <v>00221150</v>
       </c>
       <c r="F658">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="659">
@@ -13788,7 +13788,7 @@
         <v>00221148</v>
       </c>
       <c r="F660">
-        <v>1768800</v>
+        <v>159</v>
       </c>
     </row>
     <row r="661">
@@ -14088,7 +14088,7 @@
         <v>00221229</v>
       </c>
       <c r="F675">
-        <v>578000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="676">
@@ -14108,7 +14108,7 @@
         <v>00221229</v>
       </c>
       <c r="F676">
-        <v>578000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="677">
@@ -14128,7 +14128,7 @@
         <v>00221229</v>
       </c>
       <c r="F677">
-        <v>578000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="678">
@@ -24425,7 +24425,7 @@
         <v>00221076</v>
       </c>
       <c r="F1213">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1214">
@@ -24545,7 +24545,7 @@
         <v>00221076</v>
       </c>
       <c r="F1219">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1220">
@@ -25405,7 +25405,7 @@
         <v>00221200</v>
       </c>
       <c r="F1262">
-        <v>2365000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1263">
@@ -25505,7 +25505,7 @@
         <v>00221200</v>
       </c>
       <c r="F1267">
-        <v>2365000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1268">
@@ -25765,7 +25765,7 @@
         <v>00221350</v>
       </c>
       <c r="F1280">
-        <v>2376000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1281">
@@ -26225,7 +26225,7 @@
         <v>00221094</v>
       </c>
       <c r="F1303">
-        <v>4675000</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1304">
@@ -26905,7 +26905,7 @@
         <v>00221370</v>
       </c>
       <c r="F1337">
-        <v>2244000</v>
+        <v>202</v>
       </c>
     </row>
     <row r="1338">
@@ -27285,7 +27285,7 @@
         <v>00221225</v>
       </c>
       <c r="F1356">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1357">
@@ -28281,7 +28281,7 @@
         <v>00221267</v>
       </c>
       <c r="F1404">
-        <v>1190000</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1405">
@@ -28301,7 +28301,7 @@
         <v>00221267</v>
       </c>
       <c r="F1405">
-        <v>1190000</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1406">
@@ -28321,7 +28321,7 @@
         <v>00221268</v>
       </c>
       <c r="F1406">
-        <v>1190000</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1407">
@@ -28381,7 +28381,7 @@
         <v>00221355</v>
       </c>
       <c r="F1409">
-        <v>2151600</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1410">
@@ -31569,7 +31569,7 @@
         <v>00221334</v>
       </c>
       <c r="F1560">
-        <v>2321000</v>
+        <v>209</v>
       </c>
     </row>
     <row r="1561">
@@ -31649,7 +31649,7 @@
         <v>00221290</v>
       </c>
       <c r="F1564">
-        <v>4482000</v>
+        <v>332</v>
       </c>
     </row>
     <row r="1565">
@@ -31912,7 +31912,7 @@
         <v>00221290</v>
       </c>
       <c r="F1577">
-        <v>4482000</v>
+        <v>332</v>
       </c>
     </row>
     <row r="1578">
@@ -31952,7 +31952,7 @@
         <v>00221294</v>
       </c>
       <c r="F1579">
-        <v>3350000</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1580">
@@ -32472,7 +32472,7 @@
         <v>00221290</v>
       </c>
       <c r="F1605">
-        <v>4482000</v>
+        <v>332</v>
       </c>
     </row>
     <row r="1606">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1619">
@@ -34956,7 +34956,7 @@
         <v>00221534</v>
       </c>
       <c r="F1737">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="1738">
@@ -36262,7 +36262,7 @@
         <v>00221617</v>
       </c>
       <c r="F1808">
-        <v>2587200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1809">
@@ -36279,7 +36279,7 @@
         <v>00221621</v>
       </c>
       <c r="F1809">
-        <v>2587200</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1810">
@@ -37595,7 +37595,7 @@
         <v>00221244</v>
       </c>
       <c r="F1879">
-        <v>1160000</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1880">
@@ -39184,7 +39184,7 @@
         <v>00221466</v>
       </c>
       <c r="F1964">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1965">
@@ -39201,7 +39201,7 @@
         <v>00221467</v>
       </c>
       <c r="F1965">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1966">
@@ -39660,7 +39660,7 @@
         <v>00221718</v>
       </c>
       <c r="F1992">
-        <v>1890000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1993">
@@ -39677,7 +39677,7 @@
         <v>00221719</v>
       </c>
       <c r="F1993">
-        <v>1890000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1994">
@@ -39983,7 +39983,7 @@
         <v>00221739</v>
       </c>
       <c r="F2011">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2012">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2430">
@@ -47067,7 +47067,7 @@
         <v>00221448</v>
       </c>
       <c r="F2475">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2476">
@@ -47193,7 +47193,7 @@
         <v>00221334</v>
       </c>
       <c r="F2484">
-        <v>2321000</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2485">
@@ -47571,7 +47571,7 @@
         <v>00221739</v>
       </c>
       <c r="F2511">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2512">
@@ -47806,7 +47806,7 @@
         <v>00221076</v>
       </c>
       <c r="F2528">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2529">
@@ -48002,7 +48002,7 @@
         <v>00221212</v>
       </c>
       <c r="F2542">
-        <v>1491600</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2543">
@@ -48422,7 +48422,7 @@
         <v>00221753</v>
       </c>
       <c r="F2572">
-        <v>2862000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2573">
@@ -48520,7 +48520,7 @@
         <v>00221280</v>
       </c>
       <c r="F2579">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2580">
@@ -48660,7 +48660,7 @@
         <v>00221713</v>
       </c>
       <c r="F2589">
-        <v>2695000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2590">
@@ -48881,7 +48881,7 @@
         <v>00221350</v>
       </c>
       <c r="F2605">
-        <v>2376000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2606">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2618">
@@ -49105,7 +49105,7 @@
         <v>00221244</v>
       </c>
       <c r="F2621">
-        <v>1160000</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2622">
@@ -49245,7 +49245,7 @@
         <v>00221763</v>
       </c>
       <c r="F2631">
-        <v>1</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2632">
@@ -49539,7 +49539,7 @@
         <v>00221791</v>
       </c>
       <c r="F2652">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2653">
@@ -49777,7 +49777,7 @@
         <v>00221808</v>
       </c>
       <c r="F2669">
-        <v>1</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2670">
@@ -50199,7 +50199,7 @@
         <v>00221810</v>
       </c>
       <c r="F2700">
-        <v>1</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2701">
@@ -50325,7 +50325,7 @@
         <v>00221819</v>
       </c>
       <c r="F2709">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2710">
@@ -50482,9 +50482,317 @@
         <v>1750000</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="B2721" t="str">
+        <v>ریمل حجم‌دهنده گلدن رز مدل Eyeful</v>
+      </c>
+      <c r="D2721" t="str">
+        <v>79809616</v>
+      </c>
+      <c r="E2721" t="str">
+        <v>00221822</v>
+      </c>
+      <c r="F2721">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="B2722" t="str">
+        <v>ریمل بلند‌کننده ضد آب گلدن رز مدل Touch</v>
+      </c>
+      <c r="D2722" t="str">
+        <v>79809706</v>
+      </c>
+      <c r="E2722" t="str">
+        <v>00221823</v>
+      </c>
+      <c r="F2722">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="B2723" t="str">
+        <v>ریمل حجم‌دهنده گلدن رز مدل Power</v>
+      </c>
+      <c r="D2723" t="str">
+        <v>79809762</v>
+      </c>
+      <c r="E2723" t="str">
+        <v>00221824</v>
+      </c>
+      <c r="F2723">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="B2724" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 201 رنگ کرم صورتی ملایم</v>
+      </c>
+      <c r="D2724" t="str">
+        <v>80477614</v>
+      </c>
+      <c r="E2724" t="str">
+        <v>00221827</v>
+      </c>
+      <c r="F2724">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="B2725" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 202 رنگ کرم صورتی روشن</v>
+      </c>
+      <c r="D2725" t="str">
+        <v>80477623</v>
+      </c>
+      <c r="E2725" t="str">
+        <v>00221828</v>
+      </c>
+      <c r="F2725">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="B2726" t="str">
+        <v>مقدار قبلی: مداد لب گلدن رز مدل TATTOO SOFT شماره 203 رنگ کرم صورتی</v>
+      </c>
+      <c r="D2726" t="str">
+        <v>80477629</v>
+      </c>
+      <c r="E2726" t="str">
+        <v>00221829</v>
+      </c>
+      <c r="F2726">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="B2727" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 204 رنگ کرم قهوه ای</v>
+      </c>
+      <c r="D2727" t="str">
+        <v>80532821</v>
+      </c>
+      <c r="E2727" t="str">
+        <v>00221830</v>
+      </c>
+      <c r="F2727">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="B2728" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 205 رنگ کرم قهوه ای</v>
+      </c>
+      <c r="D2728" t="str">
+        <v>80537297</v>
+      </c>
+      <c r="E2728" t="str">
+        <v>00221831</v>
+      </c>
+      <c r="F2728">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="B2729" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 206 رنگ قهوه ای</v>
+      </c>
+      <c r="D2729" t="str">
+        <v>80537313</v>
+      </c>
+      <c r="E2729" t="str">
+        <v>00221832</v>
+      </c>
+      <c r="F2729">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="B2730" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 207 رنگ قهوه ای تیره</v>
+      </c>
+      <c r="D2730" t="str">
+        <v>80537320</v>
+      </c>
+      <c r="E2730" t="str">
+        <v>00221833</v>
+      </c>
+      <c r="F2730">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="B2731" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 208 رنگ ماهگونی</v>
+      </c>
+      <c r="D2731" t="str">
+        <v>80537335</v>
+      </c>
+      <c r="E2731" t="str">
+        <v>00221834</v>
+      </c>
+      <c r="F2731">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="B2732" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 210 رنگ آلویی</v>
+      </c>
+      <c r="D2732" t="str">
+        <v>80537348</v>
+      </c>
+      <c r="E2732" t="str">
+        <v>00221835</v>
+      </c>
+      <c r="F2732">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="B2733" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 211 رنگ قرمز آجری</v>
+      </c>
+      <c r="D2733" t="str">
+        <v>80537361</v>
+      </c>
+      <c r="E2733" t="str">
+        <v>00221836</v>
+      </c>
+      <c r="F2733">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="B2734" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 212 رنگ کالباسی صورتی</v>
+      </c>
+      <c r="D2734" t="str">
+        <v>80537374</v>
+      </c>
+      <c r="E2734" t="str">
+        <v>00221837</v>
+      </c>
+      <c r="F2734">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="B2735" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 213 رنگ کرم خاکی</v>
+      </c>
+      <c r="D2735" t="str">
+        <v>80537385</v>
+      </c>
+      <c r="E2735" t="str">
+        <v>00221838</v>
+      </c>
+      <c r="F2735">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="B2736" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 214 رنگ قرمز</v>
+      </c>
+      <c r="D2736" t="str">
+        <v>80537415</v>
+      </c>
+      <c r="E2736" t="str">
+        <v>00221839</v>
+      </c>
+      <c r="F2736">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="B2737" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 215 رنگ قرمز تیره</v>
+      </c>
+      <c r="D2737" t="str">
+        <v>80537449</v>
+      </c>
+      <c r="E2737" t="str">
+        <v>00221840</v>
+      </c>
+      <c r="F2737">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="B2738" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 216 رنگ صورتی</v>
+      </c>
+      <c r="D2738" t="str">
+        <v>80537467</v>
+      </c>
+      <c r="E2738" t="str">
+        <v>00221841</v>
+      </c>
+      <c r="F2738">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="B2739" t="str">
+        <v>مداد لب گلدن رز مدل DREAM شماره 540 رنگ کالباسی</v>
+      </c>
+      <c r="D2739" t="str">
+        <v>80477551</v>
+      </c>
+      <c r="E2739" t="str">
+        <v>00221842</v>
+      </c>
+      <c r="F2739">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="B2740" t="str">
+        <v>مداد لب گلدن رز مدل DREAM شماره 541 رنگ صورتی کالباسی</v>
+      </c>
+      <c r="D2740" t="str">
+        <v>80477573</v>
+      </c>
+      <c r="E2740" t="str">
+        <v>00221843</v>
+      </c>
+      <c r="F2740">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="B2741" t="str">
+        <v>مداد لب گلدن رز مدل DREAM شماره 542 رنگ گوشتی کالباسی</v>
+      </c>
+      <c r="D2741" t="str">
+        <v>80477591</v>
+      </c>
+      <c r="E2741" t="str">
+        <v>00221844</v>
+      </c>
+      <c r="F2741">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="B2742" t="str">
+        <v>مداد لب گلدن رز مدل DREAM شماره 543 رنگ کالباسی</v>
+      </c>
+      <c r="D2742" t="str">
+        <v>80477605</v>
+      </c>
+      <c r="E2742" t="str">
+        <v>00221845</v>
+      </c>
+      <c r="F2742">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2720"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2742"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2742"/>
+  <dimension ref="A1:G2743"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2025,7 +2025,7 @@
         <v>00221588</v>
       </c>
       <c r="F81">
-        <v>2134000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82">
@@ -2345,7 +2345,7 @@
         <v>00221548</v>
       </c>
       <c r="F97">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98">
@@ -2502,7 +2502,7 @@
         <v>45822594</v>
       </c>
       <c r="F105">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="106">
@@ -2519,7 +2519,7 @@
         <v>45822531</v>
       </c>
       <c r="F106">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="107">
@@ -2679,7 +2679,7 @@
         <v>00221591</v>
       </c>
       <c r="F114">
-        <v>2112000</v>
+        <v>191</v>
       </c>
     </row>
     <row r="115">
@@ -2719,7 +2719,7 @@
         <v>00221593</v>
       </c>
       <c r="F116">
-        <v>2112000</v>
+        <v>191</v>
       </c>
     </row>
     <row r="117">
@@ -3480,7 +3480,7 @@
         <v>00221556</v>
       </c>
       <c r="F153">
-        <v>3220800</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154">
@@ -3640,7 +3640,7 @@
         <v>00221564</v>
       </c>
       <c r="F161">
-        <v>3220800</v>
+        <v>289</v>
       </c>
     </row>
     <row r="162">
@@ -3840,7 +3840,7 @@
         <v>00221550</v>
       </c>
       <c r="F171">
-        <v>1245000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172">
@@ -6358,7 +6358,7 @@
         <v>00221515</v>
       </c>
       <c r="F284">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="285">
@@ -6932,7 +6932,7 @@
         <v>00221441</v>
       </c>
       <c r="F313">
-        <v>2710500</v>
+        <v>195</v>
       </c>
     </row>
     <row r="314">
@@ -8315,7 +8315,7 @@
         <v>00221441</v>
       </c>
       <c r="F382">
-        <v>2710500</v>
+        <v>195</v>
       </c>
     </row>
     <row r="383">
@@ -8335,7 +8335,7 @@
         <v>00221441</v>
       </c>
       <c r="F383">
-        <v>2710500</v>
+        <v>195</v>
       </c>
     </row>
     <row r="384">
@@ -8675,7 +8675,7 @@
         <v>00221435</v>
       </c>
       <c r="F400">
-        <v>1639000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="401">
@@ -8695,7 +8695,7 @@
         <v>00221435</v>
       </c>
       <c r="F401">
-        <v>1639000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="402">
@@ -9415,7 +9415,7 @@
         <v>00221133</v>
       </c>
       <c r="F437">
-        <v>5157000</v>
+        <v>393</v>
       </c>
     </row>
     <row r="438">
@@ -9855,7 +9855,7 @@
         <v>00221036</v>
       </c>
       <c r="F459">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="460">
@@ -9995,7 +9995,7 @@
         <v>00221442</v>
       </c>
       <c r="F466">
-        <v>2150500</v>
+        <v>194</v>
       </c>
     </row>
     <row r="467">
@@ -10352,7 +10352,7 @@
         <v>00221216</v>
       </c>
       <c r="F484">
-        <v>1491600</v>
+        <v>135</v>
       </c>
     </row>
     <row r="485">
@@ -11728,7 +11728,7 @@
         <v>00221400</v>
       </c>
       <c r="F557">
-        <v>6000000</v>
+        <v>450</v>
       </c>
     </row>
     <row r="558">
@@ -11925,7 +11925,7 @@
         <v>38147716</v>
       </c>
       <c r="F567">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G567">
         <v>35000</v>
@@ -11945,7 +11945,7 @@
         <v>38147321</v>
       </c>
       <c r="F568">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G568">
         <v>35000</v>
@@ -11965,7 +11965,7 @@
         <v>38146217</v>
       </c>
       <c r="F569">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G569">
         <v>35000</v>
@@ -12388,7 +12388,7 @@
         <v>00221399</v>
       </c>
       <c r="F590">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="591">
@@ -12408,7 +12408,7 @@
         <v>00221398</v>
       </c>
       <c r="F591">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="592">
@@ -12528,7 +12528,7 @@
         <v>00221402</v>
       </c>
       <c r="F597">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="598">
@@ -12608,7 +12608,7 @@
         <v>00221084</v>
       </c>
       <c r="F601">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="602">
@@ -12628,7 +12628,7 @@
         <v>00221084</v>
       </c>
       <c r="F602">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="603">
@@ -13028,7 +13028,7 @@
         <v>00221015</v>
       </c>
       <c r="F622">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="623">
@@ -13048,7 +13048,7 @@
         <v>00221015</v>
       </c>
       <c r="F623">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="624">
@@ -13208,7 +13208,7 @@
         <v>00221230</v>
       </c>
       <c r="F631">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="632">
@@ -13228,7 +13228,7 @@
         <v>00221230</v>
       </c>
       <c r="F632">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="633">
@@ -13288,7 +13288,7 @@
         <v>00221036</v>
       </c>
       <c r="F635">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="636">
@@ -13308,7 +13308,7 @@
         <v>00221047</v>
       </c>
       <c r="F636">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="637">
@@ -13428,7 +13428,7 @@
         <v>00221046</v>
       </c>
       <c r="F642">
-        <v>2497500</v>
+        <v>185</v>
       </c>
     </row>
     <row r="643">
@@ -13448,7 +13448,7 @@
         <v>00221046</v>
       </c>
       <c r="F643">
-        <v>2497500</v>
+        <v>185</v>
       </c>
     </row>
     <row r="644">
@@ -13548,7 +13548,7 @@
         <v>00221409</v>
       </c>
       <c r="F648">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="649">
@@ -13608,7 +13608,7 @@
         <v>00221238</v>
       </c>
       <c r="F651">
-        <v>1215000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="652">
@@ -13648,7 +13648,7 @@
         <v>00221240</v>
       </c>
       <c r="F653">
-        <v>1251000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="654">
@@ -13988,7 +13988,7 @@
         <v>00221311</v>
       </c>
       <c r="F670">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="671">
@@ -14068,7 +14068,7 @@
         <v>00221133</v>
       </c>
       <c r="F674">
-        <v>5157000</v>
+        <v>393</v>
       </c>
     </row>
     <row r="675">
@@ -14208,7 +14208,7 @@
         <v>00221036</v>
       </c>
       <c r="F681">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="682">
@@ -14871,7 +14871,7 @@
         <v>35978635</v>
       </c>
       <c r="F714">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="715">
@@ -14888,7 +14888,7 @@
         <v>35978537</v>
       </c>
       <c r="F715">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="716">
@@ -18920,7 +18920,7 @@
         <v>00221379</v>
       </c>
       <c r="F922">
-        <v>2605500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="923">
@@ -18940,7 +18940,7 @@
         <v>00221381</v>
       </c>
       <c r="F923">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="924">
@@ -20367,7 +20367,7 @@
         <v>34371439</v>
       </c>
       <c r="F999">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1000">
@@ -23398,7 +23398,7 @@
         <v>00216001</v>
       </c>
       <c r="F1160">
-        <v>630000</v>
+        <v>1366000</v>
       </c>
       <c r="G1160">
         <v>760000</v>
@@ -24505,7 +24505,7 @@
         <v>00221073</v>
       </c>
       <c r="F1217">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1218">
@@ -24645,7 +24645,7 @@
         <v>00221041</v>
       </c>
       <c r="F1224">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1225">
@@ -24665,7 +24665,7 @@
         <v>00221041</v>
       </c>
       <c r="F1225">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1226">
@@ -25305,7 +25305,7 @@
         <v>00221351</v>
       </c>
       <c r="F1257">
-        <v>1280000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1258">
@@ -25445,7 +25445,7 @@
         <v>00221179</v>
       </c>
       <c r="F1264">
-        <v>4950000</v>
+        <v>422</v>
       </c>
     </row>
     <row r="1265">
@@ -25545,7 +25545,7 @@
         <v>00221041</v>
       </c>
       <c r="F1269">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1270">
@@ -25565,7 +25565,7 @@
         <v>00221197</v>
       </c>
       <c r="F1270">
-        <v>2365000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1271">
@@ -25905,7 +25905,7 @@
         <v>00221298</v>
       </c>
       <c r="F1287">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1288">
@@ -25945,7 +25945,7 @@
         <v>00221298</v>
       </c>
       <c r="F1289">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1290">
@@ -25985,7 +25985,7 @@
         <v>00221298</v>
       </c>
       <c r="F1291">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1292">
@@ -26045,7 +26045,7 @@
         <v>00221311</v>
       </c>
       <c r="F1294">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1295">
@@ -26085,7 +26085,7 @@
         <v>00221096</v>
       </c>
       <c r="F1296">
-        <v>4675000</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1297">
@@ -26405,7 +26405,7 @@
         <v>00221133</v>
       </c>
       <c r="F1312">
-        <v>5157000</v>
+        <v>393</v>
       </c>
     </row>
     <row r="1313">
@@ -27025,7 +27025,7 @@
         <v>00221032</v>
       </c>
       <c r="F1343">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1344">
@@ -27045,7 +27045,7 @@
         <v>00221032</v>
       </c>
       <c r="F1344">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1345">
@@ -27425,7 +27425,7 @@
         <v>00221133</v>
       </c>
       <c r="F1363">
-        <v>5157000</v>
+        <v>393</v>
       </c>
     </row>
     <row r="1364">
@@ -27465,7 +27465,7 @@
         <v>00221245</v>
       </c>
       <c r="F1365">
-        <v>1595000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1366">
@@ -27585,7 +27585,7 @@
         <v>00221073</v>
       </c>
       <c r="F1371">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1372">
@@ -27725,7 +27725,7 @@
         <v>00221073</v>
       </c>
       <c r="F1378">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1379">
@@ -29955,7 +29955,7 @@
         <v>00221010</v>
       </c>
       <c r="F1482">
-        <v>3822500</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1483">
@@ -30195,7 +30195,7 @@
         <v>00221167</v>
       </c>
       <c r="F1494">
-        <v>4290000</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1495">
@@ -30235,7 +30235,7 @@
         <v>00221167</v>
       </c>
       <c r="F1496">
-        <v>4290000</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1497">
@@ -30275,7 +30275,7 @@
         <v>00221143</v>
       </c>
       <c r="F1498">
-        <v>4301000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1499">
@@ -30681,7 +30681,7 @@
         <v>30834962</v>
       </c>
       <c r="F1518">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1519">
@@ -31079,7 +31079,7 @@
         <v>00221009</v>
       </c>
       <c r="F1537">
-        <v>4119500</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1538">
@@ -32452,7 +32452,7 @@
         <v>00221015</v>
       </c>
       <c r="F1604">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="1605">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1619">
@@ -33096,7 +33096,7 @@
         <v>55003389</v>
       </c>
       <c r="F1635">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1636">
@@ -34351,7 +34351,7 @@
         <v>48696472</v>
       </c>
       <c r="F1703">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1704">
@@ -34368,7 +34368,7 @@
         <v>48696438</v>
       </c>
       <c r="F1704">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1705">
@@ -34385,7 +34385,7 @@
         <v>48696304</v>
       </c>
       <c r="F1705">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1706">
@@ -34402,7 +34402,7 @@
         <v>48696268</v>
       </c>
       <c r="F1706">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1707">
@@ -34419,7 +34419,7 @@
         <v>48484996</v>
       </c>
       <c r="F1707">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1708">
@@ -34436,7 +34436,7 @@
         <v>48005865</v>
       </c>
       <c r="F1708">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1709">
@@ -34453,7 +34453,7 @@
         <v>48005831</v>
       </c>
       <c r="F1709">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1710">
@@ -34470,7 +34470,7 @@
         <v>48005800</v>
       </c>
       <c r="F1710">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1711">
@@ -34487,7 +34487,7 @@
         <v>48005774</v>
       </c>
       <c r="F1711">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1712">
@@ -34504,7 +34504,7 @@
         <v>48004979</v>
       </c>
       <c r="F1712">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1713">
@@ -34521,7 +34521,7 @@
         <v>48004895</v>
       </c>
       <c r="F1713">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1714">
@@ -34538,7 +34538,7 @@
         <v>48004738</v>
       </c>
       <c r="F1714">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1715">
@@ -34555,7 +34555,7 @@
         <v>49176643</v>
       </c>
       <c r="F1715">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1715">
         <v>974800</v>
@@ -34575,7 +34575,7 @@
         <v>49095632</v>
       </c>
       <c r="F1716">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1716">
         <v>657500</v>
@@ -34595,7 +34595,7 @@
         <v>48005692</v>
       </c>
       <c r="F1717">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1718">
@@ -34612,7 +34612,7 @@
         <v>48805764</v>
       </c>
       <c r="F1718">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1719">
@@ -34629,7 +34629,7 @@
         <v>48499213</v>
       </c>
       <c r="F1719">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1719">
         <v>450000</v>
@@ -34649,7 +34649,7 @@
         <v>48499173</v>
       </c>
       <c r="F1720">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1720">
         <v>1740000</v>
@@ -34669,7 +34669,7 @@
         <v>48483945</v>
       </c>
       <c r="F1721">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1721">
         <v>1740000</v>
@@ -34689,7 +34689,7 @@
         <v>48483874</v>
       </c>
       <c r="F1722">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1722">
         <v>590000</v>
@@ -34709,7 +34709,7 @@
         <v>48483840</v>
       </c>
       <c r="F1723">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1723">
         <v>590000</v>
@@ -34729,7 +34729,7 @@
         <v>47445192</v>
       </c>
       <c r="F1724">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1725">
@@ -34746,7 +34746,7 @@
         <v>47445075</v>
       </c>
       <c r="F1725">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1726">
@@ -34763,7 +34763,7 @@
         <v>44470822</v>
       </c>
       <c r="F1726">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1727">
@@ -34780,7 +34780,7 @@
         <v>43636861</v>
       </c>
       <c r="F1727">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1728">
@@ -36228,7 +36228,7 @@
         <v>111111</v>
       </c>
       <c r="F1806">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1807">
@@ -36381,7 +36381,7 @@
         <v>00221692</v>
       </c>
       <c r="F1815">
-        <v>2519000</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1816">
@@ -36534,7 +36534,7 @@
         <v>00221693</v>
       </c>
       <c r="F1824">
-        <v>3658500</v>
+        <v>271</v>
       </c>
     </row>
     <row r="1825">
@@ -36619,7 +36619,7 @@
         <v>00221216</v>
       </c>
       <c r="F1829">
-        <v>1491600</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1830">
@@ -36824,7 +36824,7 @@
         <v>56329672</v>
       </c>
       <c r="F1840">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1840">
         <v>275200</v>
@@ -37541,7 +37541,7 @@
         <v>50000020</v>
       </c>
       <c r="F1876">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1876">
         <v>275200</v>
@@ -37558,7 +37558,7 @@
         <v>50000030</v>
       </c>
       <c r="F1877">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1877">
         <v>275200</v>
@@ -37575,7 +37575,7 @@
         <v>50000040</v>
       </c>
       <c r="F1878">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G1878">
         <v>275200</v>
@@ -38924,7 +38924,7 @@
         <v>57178841</v>
       </c>
       <c r="F1948">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1949">
@@ -38938,7 +38938,7 @@
         <v>56887918</v>
       </c>
       <c r="F1949">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1950">
@@ -38952,7 +38952,7 @@
         <v>56887895</v>
       </c>
       <c r="F1950">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1951">
@@ -38966,7 +38966,7 @@
         <v>57178901</v>
       </c>
       <c r="F1951">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1952">
@@ -38980,7 +38980,7 @@
         <v>57178772</v>
       </c>
       <c r="F1952">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1953">
@@ -39065,7 +39065,7 @@
         <v>00221216</v>
       </c>
       <c r="F1957">
-        <v>1491600</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1958">
@@ -39422,7 +39422,7 @@
         <v>00221041</v>
       </c>
       <c r="F1978">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1979">
@@ -39456,7 +39456,7 @@
         <v>00221216</v>
       </c>
       <c r="F1980">
-        <v>1491600</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1981">
@@ -42167,7 +42167,7 @@
         <v>64111292</v>
       </c>
       <c r="F2122">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2122">
         <v>3617000</v>
@@ -42198,7 +42198,7 @@
         <v>64690629</v>
       </c>
       <c r="F2124">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2124">
         <v>1550000</v>
@@ -42212,7 +42212,7 @@
         <v>64690614</v>
       </c>
       <c r="F2125">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2125">
         <v>1550000</v>
@@ -42226,7 +42226,7 @@
         <v>64690581</v>
       </c>
       <c r="F2126">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2126">
         <v>1550000</v>
@@ -42240,7 +42240,7 @@
         <v>64690544</v>
       </c>
       <c r="F2127">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2127">
         <v>1550000</v>
@@ -42254,7 +42254,7 @@
         <v>64690511</v>
       </c>
       <c r="F2128">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2128">
         <v>1550000</v>
@@ -42557,7 +42557,7 @@
         <v>64428822</v>
       </c>
       <c r="F2146">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2146">
         <v>765450</v>
@@ -42571,7 +42571,7 @@
         <v>64333086</v>
       </c>
       <c r="F2147">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2147">
         <v>2256660</v>
@@ -42585,7 +42585,7 @@
         <v>64333041</v>
       </c>
       <c r="F2148">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2148">
         <v>1128330</v>
@@ -42599,7 +42599,7 @@
         <v>64332133</v>
       </c>
       <c r="F2149">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2149">
         <v>2608200</v>
@@ -42613,7 +42613,7 @@
         <v>64332096</v>
       </c>
       <c r="F2150">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2150">
         <v>1304100</v>
@@ -42627,7 +42627,7 @@
         <v>64331568</v>
       </c>
       <c r="F2151">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2151">
         <v>680400</v>
@@ -42641,7 +42641,7 @@
         <v>64331041</v>
       </c>
       <c r="F2152">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2152">
         <v>1338120</v>
@@ -42655,7 +42655,7 @@
         <v>64329671</v>
       </c>
       <c r="F2153">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2153">
         <v>765450</v>
@@ -42669,7 +42669,7 @@
         <v>64328929</v>
       </c>
       <c r="F2154">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2154">
         <v>1020600</v>
@@ -42683,7 +42683,7 @@
         <v>64328529</v>
       </c>
       <c r="F2155">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2155">
         <v>1020600</v>
@@ -42697,7 +42697,7 @@
         <v>64305454</v>
       </c>
       <c r="F2156">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2156">
         <v>517140</v>
@@ -42711,7 +42711,7 @@
         <v>64305180</v>
       </c>
       <c r="F2157">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2157">
         <v>901530</v>
@@ -42725,7 +42725,7 @@
         <v>64305020</v>
       </c>
       <c r="F2158">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2158">
         <v>561330</v>
@@ -42739,7 +42739,7 @@
         <v>64295538</v>
       </c>
       <c r="F2159">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2159">
         <v>425250</v>
@@ -42753,7 +42753,7 @@
         <v>64295369</v>
       </c>
       <c r="F2160">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2160">
         <v>878850</v>
@@ -42767,7 +42767,7 @@
         <v>64295105</v>
       </c>
       <c r="F2161">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2161">
         <v>561330</v>
@@ -42781,7 +42781,7 @@
         <v>64294796</v>
       </c>
       <c r="F2162">
-        <v>1500000</v>
+        <v>282</v>
       </c>
       <c r="G2162">
         <v>686070</v>
@@ -43901,7 +43901,7 @@
         <v>68580695</v>
       </c>
       <c r="F2242">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2243">
@@ -43912,7 +43912,7 @@
         <v>68580509</v>
       </c>
       <c r="F2243">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2244">
@@ -43923,7 +43923,7 @@
         <v>68580412</v>
       </c>
       <c r="F2244">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2245">
@@ -43934,7 +43934,7 @@
         <v>68580248</v>
       </c>
       <c r="F2245">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2246">
@@ -43945,7 +43945,7 @@
         <v>68580059</v>
       </c>
       <c r="F2246">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2247">
@@ -43956,7 +43956,7 @@
         <v>68579941</v>
       </c>
       <c r="F2247">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2248">
@@ -43967,7 +43967,7 @@
         <v>68579550</v>
       </c>
       <c r="F2248">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2249">
@@ -43978,7 +43978,7 @@
         <v>68579471</v>
       </c>
       <c r="F2249">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2250">
@@ -43989,7 +43989,7 @@
         <v>68579358</v>
       </c>
       <c r="F2250">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2251">
@@ -44000,7 +44000,7 @@
         <v>68579117</v>
       </c>
       <c r="F2251">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2252">
@@ -44011,7 +44011,7 @@
         <v>68579081</v>
       </c>
       <c r="F2252">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2253">
@@ -44022,7 +44022,7 @@
         <v>68578915</v>
       </c>
       <c r="F2253">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2254">
@@ -44033,7 +44033,7 @@
         <v>68578887</v>
       </c>
       <c r="F2254">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2255">
@@ -44044,7 +44044,7 @@
         <v>68578792</v>
       </c>
       <c r="F2255">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2256">
@@ -44055,7 +44055,7 @@
         <v>68578665</v>
       </c>
       <c r="F2256">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2257">
@@ -44066,7 +44066,7 @@
         <v>68577686</v>
       </c>
       <c r="F2257">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2258">
@@ -44077,7 +44077,7 @@
         <v>68577652</v>
       </c>
       <c r="F2258">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2259">
@@ -44088,7 +44088,7 @@
         <v>68576994</v>
       </c>
       <c r="F2259">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2260">
@@ -44099,7 +44099,7 @@
         <v>68576906</v>
       </c>
       <c r="F2260">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2261">
@@ -44110,7 +44110,7 @@
         <v>68573468</v>
       </c>
       <c r="F2261">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2262">
@@ -44121,7 +44121,7 @@
         <v>68573370</v>
       </c>
       <c r="F2262">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2263">
@@ -44132,7 +44132,7 @@
         <v>68572279</v>
       </c>
       <c r="F2263">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2264">
@@ -44143,7 +44143,7 @@
         <v>68315781</v>
       </c>
       <c r="F2264">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2265">
@@ -44154,7 +44154,7 @@
         <v>68315647</v>
       </c>
       <c r="F2265">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2266">
@@ -44165,7 +44165,7 @@
         <v>68297855</v>
       </c>
       <c r="F2266">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2267">
@@ -44176,7 +44176,7 @@
         <v>68297737</v>
       </c>
       <c r="F2267">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2268">
@@ -44187,7 +44187,7 @@
         <v>68297319</v>
       </c>
       <c r="F2268">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2269">
@@ -44198,7 +44198,7 @@
         <v>68289446</v>
       </c>
       <c r="F2269">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2270">
@@ -44223,7 +44223,7 @@
         <v>55555555</v>
       </c>
       <c r="F2271">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2272">
@@ -44234,7 +44234,7 @@
         <v>55555556</v>
       </c>
       <c r="F2272">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2273">
@@ -44242,7 +44242,7 @@
         <v xml:space="preserve">دستمال مرطوب دافی  Q10 </v>
       </c>
       <c r="F2273">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2274">
@@ -45737,7 +45737,7 @@
         <v>72014008</v>
       </c>
       <c r="F2380">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2381">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2430">
@@ -46619,7 +46619,7 @@
         <v>00221216</v>
       </c>
       <c r="F2443">
-        <v>1491600</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2444">
@@ -46633,7 +46633,7 @@
         <v>00221230</v>
       </c>
       <c r="F2444">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2445">
@@ -46647,7 +46647,7 @@
         <v>00221238</v>
       </c>
       <c r="F2445">
-        <v>1215000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2446">
@@ -47039,7 +47039,7 @@
         <v>00221435</v>
       </c>
       <c r="F2473">
-        <v>1639000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2474">
@@ -47165,7 +47165,7 @@
         <v>00221240</v>
       </c>
       <c r="F2482">
-        <v>1251000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2483">
@@ -47235,7 +47235,7 @@
         <v>00221441</v>
       </c>
       <c r="F2487">
-        <v>2710500</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2488">
@@ -47263,7 +47263,7 @@
         <v>00221015</v>
       </c>
       <c r="F2489">
-        <v>4394500</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2490">
@@ -47291,7 +47291,7 @@
         <v>00221245</v>
       </c>
       <c r="F2491">
-        <v>1595000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2492">
@@ -47347,7 +47347,7 @@
         <v>00221398</v>
       </c>
       <c r="F2495">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2496">
@@ -47361,7 +47361,7 @@
         <v>00221399</v>
       </c>
       <c r="F2496">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2497">
@@ -47624,7 +47624,7 @@
         <v>74313106</v>
       </c>
       <c r="F2515">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2516">
@@ -47764,7 +47764,7 @@
         <v>00221073</v>
       </c>
       <c r="F2525">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2526">
@@ -47904,7 +47904,7 @@
         <v>00221084</v>
       </c>
       <c r="F2535">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2536">
@@ -48016,7 +48016,7 @@
         <v>00221216</v>
       </c>
       <c r="F2543">
-        <v>1491600</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2544">
@@ -48478,7 +48478,7 @@
         <v>00221398</v>
       </c>
       <c r="F2576">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2577">
@@ -48492,7 +48492,7 @@
         <v>00221399</v>
       </c>
       <c r="F2577">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2578">
@@ -48685,7 +48685,7 @@
         <v>75283541</v>
       </c>
       <c r="F2591">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2592">
@@ -48699,7 +48699,7 @@
         <v>00221402</v>
       </c>
       <c r="F2592">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2593">
@@ -48811,7 +48811,7 @@
         <v>00221409</v>
       </c>
       <c r="F2600">
-        <v>3861000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2601">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2618">
@@ -49119,7 +49119,7 @@
         <v>00221351</v>
       </c>
       <c r="F2622">
-        <v>1280000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2623">
@@ -49301,7 +49301,7 @@
         <v>00221769</v>
       </c>
       <c r="F2635">
-        <v>1</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2636">
@@ -49497,7 +49497,7 @@
         <v>00221788</v>
       </c>
       <c r="F2649">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2650">
@@ -49511,7 +49511,7 @@
         <v>00221789</v>
       </c>
       <c r="F2650">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2651">
@@ -49595,7 +49595,7 @@
         <v>00221795</v>
       </c>
       <c r="F2656">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2657">
@@ -49830,7 +49830,7 @@
         <v>76410461</v>
       </c>
       <c r="F2673">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2674">
@@ -49911,7 +49911,7 @@
         <v>76636716</v>
       </c>
       <c r="F2679">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2680">
@@ -49922,7 +49922,7 @@
         <v>76636706</v>
       </c>
       <c r="F2680">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2681">
@@ -49933,7 +49933,7 @@
         <v>76636688</v>
       </c>
       <c r="F2681">
-        <v>1500000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2682">
@@ -50045,7 +50045,7 @@
         <v>00221795</v>
       </c>
       <c r="F2689">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2690">
@@ -50269,7 +50269,7 @@
         <v>00221815</v>
       </c>
       <c r="F2705">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2706">
@@ -50790,9 +50790,20 @@
         <v>90</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="B2743" t="str">
+        <v>مداد لب گلدن رز مدل TATTOO SOFT شماره 209 رنگ قهوه ای</v>
+      </c>
+      <c r="D2743" t="str">
+        <v>80628922</v>
+      </c>
+      <c r="F2743">
+        <v>282</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2742"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2743"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -1765,7 +1765,7 @@
         <v>00221664</v>
       </c>
       <c r="F68">
-        <v>2050000</v>
+        <v>307</v>
       </c>
     </row>
     <row r="69">
@@ -2125,7 +2125,7 @@
         <v>00221597</v>
       </c>
       <c r="F86">
-        <v>2084500</v>
+        <v>188</v>
       </c>
     </row>
     <row r="87">
@@ -2145,7 +2145,7 @@
         <v>00221598</v>
       </c>
       <c r="F87">
-        <v>2084500</v>
+        <v>188</v>
       </c>
     </row>
     <row r="88">
@@ -2779,7 +2779,7 @@
         <v>00221596</v>
       </c>
       <c r="F119">
-        <v>2084500</v>
+        <v>188</v>
       </c>
     </row>
     <row r="120">
@@ -4738,7 +4738,7 @@
         <v>00221524</v>
       </c>
       <c r="F212">
-        <v>1408000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="213">
@@ -6712,7 +6712,7 @@
         <v>00221509</v>
       </c>
       <c r="F302">
-        <v>2084500</v>
+        <v>188</v>
       </c>
     </row>
     <row r="303">
@@ -6892,7 +6892,7 @@
         <v>00221501</v>
       </c>
       <c r="F311">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="312">
@@ -6992,7 +6992,7 @@
         <v>00221498</v>
       </c>
       <c r="F316">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="317">
@@ -7152,7 +7152,7 @@
         <v>00221491</v>
       </c>
       <c r="F324">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="325">
@@ -7292,7 +7292,7 @@
         <v>00221485</v>
       </c>
       <c r="F331">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="332">
@@ -7432,7 +7432,7 @@
         <v>00221478</v>
       </c>
       <c r="F338">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="339">
@@ -7592,7 +7592,7 @@
         <v>00221470</v>
       </c>
       <c r="F346">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="347">
@@ -7712,7 +7712,7 @@
         <v>00221458</v>
       </c>
       <c r="F352">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="353">
@@ -7892,7 +7892,7 @@
         <v>00221256</v>
       </c>
       <c r="F361">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="362">
@@ -8112,7 +8112,7 @@
         <v>00221449</v>
       </c>
       <c r="F372">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="373">
@@ -8735,7 +8735,7 @@
         <v>00221287</v>
       </c>
       <c r="F403">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="404">
@@ -9135,7 +9135,7 @@
         <v>00221428</v>
       </c>
       <c r="F423">
-        <v>3000000</v>
+        <v>394</v>
       </c>
     </row>
     <row r="424">
@@ -9715,7 +9715,7 @@
         <v>00221074</v>
       </c>
       <c r="F452">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="453">
@@ -9775,7 +9775,7 @@
         <v>00221069</v>
       </c>
       <c r="F455">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="456">
@@ -9795,7 +9795,7 @@
         <v>00221064</v>
       </c>
       <c r="F456">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="457">
@@ -11337,7 +11337,7 @@
         <v>00221277</v>
       </c>
       <c r="F537">
-        <v>1250000</v>
+        <v>188</v>
       </c>
     </row>
     <row r="538">
@@ -12228,7 +12228,7 @@
         <v>00221052</v>
       </c>
       <c r="F582">
-        <v>2362500</v>
+        <v>175</v>
       </c>
     </row>
     <row r="583">
@@ -12728,7 +12728,7 @@
         <v>00221287</v>
       </c>
       <c r="F607">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="608">
@@ -12908,7 +12908,7 @@
         <v>00221310</v>
       </c>
       <c r="F616">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="617">
@@ -12928,7 +12928,7 @@
         <v>00221310</v>
       </c>
       <c r="F617">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="618">
@@ -19040,7 +19040,7 @@
         <v>00221383</v>
       </c>
       <c r="F928">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="929">
@@ -21262,7 +21262,7 @@
         <v>00221222</v>
       </c>
       <c r="F1046">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1047">
@@ -24385,7 +24385,7 @@
         <v>00221297</v>
       </c>
       <c r="F1211">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1212">
@@ -24405,7 +24405,7 @@
         <v>00221074</v>
       </c>
       <c r="F1212">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1213">
@@ -24485,7 +24485,7 @@
         <v>00221297</v>
       </c>
       <c r="F1216">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1217">
@@ -24565,7 +24565,7 @@
         <v>00221074</v>
       </c>
       <c r="F1220">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1221">
@@ -25245,7 +25245,7 @@
         <v>00221224</v>
       </c>
       <c r="F1254">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1255">
@@ -25325,7 +25325,7 @@
         <v>00221106</v>
       </c>
       <c r="F1258">
-        <v>5918000</v>
+        <v>536</v>
       </c>
     </row>
     <row r="1259">
@@ -25705,7 +25705,7 @@
         <v>00221224</v>
       </c>
       <c r="F1277">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1278">
@@ -25825,7 +25825,7 @@
         <v>00221102</v>
       </c>
       <c r="F1283">
-        <v>1479500</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1284">
@@ -25845,7 +25845,7 @@
         <v>00221102</v>
       </c>
       <c r="F1284">
-        <v>1479500</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1285">
@@ -26205,7 +26205,7 @@
         <v>00221285</v>
       </c>
       <c r="F1302">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1303">
@@ -26445,7 +26445,7 @@
         <v>00221102</v>
       </c>
       <c r="F1314">
-        <v>1479500</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1315">
@@ -26565,7 +26565,7 @@
         <v>00221313</v>
       </c>
       <c r="F1320">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1321">
@@ -26585,7 +26585,7 @@
         <v>00221313</v>
       </c>
       <c r="F1321">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1322">
@@ -26665,7 +26665,7 @@
         <v>00221201</v>
       </c>
       <c r="F1325">
-        <v>2365000</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1326">
@@ -26965,7 +26965,7 @@
         <v>00221320</v>
       </c>
       <c r="F1340">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1341">
@@ -26985,7 +26985,7 @@
         <v>00221320</v>
       </c>
       <c r="F1341">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1342">
@@ -27485,7 +27485,7 @@
         <v>00221066</v>
       </c>
       <c r="F1366">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1367">
@@ -27625,7 +27625,7 @@
         <v>00221064</v>
       </c>
       <c r="F1373">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1374">
@@ -27645,7 +27645,7 @@
         <v>00221066</v>
       </c>
       <c r="F1374">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1375">
@@ -27685,7 +27685,7 @@
         <v>00221069</v>
       </c>
       <c r="F1376">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1377">
@@ -27785,7 +27785,7 @@
         <v>00221069</v>
       </c>
       <c r="F1381">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1382">
@@ -31142,7 +31142,7 @@
         <v>00315004</v>
       </c>
       <c r="F1540">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G1540">
         <v>220000</v>
@@ -31806,7 +31806,7 @@
         <v>00315001</v>
       </c>
       <c r="F1572">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="G1572">
         <v>22000</v>
@@ -32192,7 +32192,7 @@
         <v>00221270</v>
       </c>
       <c r="F1591">
-        <v>1144000</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1592">
@@ -32232,7 +32232,7 @@
         <v>00221297</v>
       </c>
       <c r="F1593">
-        <v>950000</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1594">
@@ -32713,7 +32713,7 @@
         <v>00221008</v>
       </c>
       <c r="F1616">
-        <v>3822500</v>
+        <v>369</v>
       </c>
     </row>
     <row r="1617">
@@ -32733,7 +32733,7 @@
         <v>00221217</v>
       </c>
       <c r="F1617">
-        <v>5038000</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1618">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="1619">
@@ -35721,7 +35721,7 @@
         <v>00801002</v>
       </c>
       <c r="F1776">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1777">
@@ -35738,7 +35738,7 @@
         <v>00801003</v>
       </c>
       <c r="F1777">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1778">
@@ -35755,7 +35755,7 @@
         <v>00801004</v>
       </c>
       <c r="F1778">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1779">
@@ -35772,7 +35772,7 @@
         <v>00801005</v>
       </c>
       <c r="F1779">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1780">
@@ -35789,7 +35789,7 @@
         <v>00801006</v>
       </c>
       <c r="F1780">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1781">
@@ -35806,7 +35806,7 @@
         <v>00801007</v>
       </c>
       <c r="F1781">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1782">
@@ -35823,7 +35823,7 @@
         <v>00801008</v>
       </c>
       <c r="F1782">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1783">
@@ -35840,7 +35840,7 @@
         <v>00801009</v>
       </c>
       <c r="F1783">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1784">
@@ -35857,7 +35857,7 @@
         <v>00801010</v>
       </c>
       <c r="F1784">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1785">
@@ -35874,7 +35874,7 @@
         <v>00801011</v>
       </c>
       <c r="F1785">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1786">
@@ -35891,7 +35891,7 @@
         <v>00801012</v>
       </c>
       <c r="F1786">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1787">
@@ -35908,7 +35908,7 @@
         <v>00801013</v>
       </c>
       <c r="F1787">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1788">
@@ -35925,7 +35925,7 @@
         <v>00801014</v>
       </c>
       <c r="F1788">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1789">
@@ -35942,7 +35942,7 @@
         <v>00801015</v>
       </c>
       <c r="F1789">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1790">
@@ -35959,7 +35959,7 @@
         <v>00801016</v>
       </c>
       <c r="F1790">
-        <v>375000</v>
+        <v>2250000</v>
       </c>
     </row>
     <row r="1791">
@@ -35976,7 +35976,7 @@
         <v>00801017</v>
       </c>
       <c r="F1791">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1792">
@@ -35993,7 +35993,7 @@
         <v>00801018</v>
       </c>
       <c r="F1792">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1793">
@@ -36010,7 +36010,7 @@
         <v>00801019</v>
       </c>
       <c r="F1793">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1794">
@@ -36027,7 +36027,7 @@
         <v>00801020</v>
       </c>
       <c r="F1794">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1795">
@@ -36044,7 +36044,7 @@
         <v>00801021</v>
       </c>
       <c r="F1795">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1796">
@@ -36061,7 +36061,7 @@
         <v>00801022</v>
       </c>
       <c r="F1796">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1797">
@@ -36078,7 +36078,7 @@
         <v>00801023</v>
       </c>
       <c r="F1797">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1798">
@@ -36095,7 +36095,7 @@
         <v>00801024</v>
       </c>
       <c r="F1798">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1799">
@@ -36112,7 +36112,7 @@
         <v>00801025</v>
       </c>
       <c r="F1799">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1800">
@@ -36146,7 +36146,7 @@
         <v>00801027</v>
       </c>
       <c r="F1801">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1802">
@@ -36163,7 +36163,7 @@
         <v>00801028</v>
       </c>
       <c r="F1802">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="1803">
@@ -36330,7 +36330,7 @@
         <v>00221689</v>
       </c>
       <c r="F1812">
-        <v>1408000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1813">
@@ -36364,7 +36364,7 @@
         <v>00221691</v>
       </c>
       <c r="F1814">
-        <v>1408000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1815">
@@ -36398,7 +36398,7 @@
         <v>00221694</v>
       </c>
       <c r="F1816">
-        <v>2519000</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1817">
@@ -36517,7 +36517,7 @@
         <v>00221270</v>
       </c>
       <c r="F1823">
-        <v>1144000</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1824">
@@ -36602,7 +36602,7 @@
         <v>00221052</v>
       </c>
       <c r="F1828">
-        <v>2362500</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1829">
@@ -36793,7 +36793,7 @@
         <v>00221052</v>
       </c>
       <c r="F1838">
-        <v>2362500</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1839">
@@ -39609,7 +39609,7 @@
         <v>00221709</v>
       </c>
       <c r="F1989">
-        <v>1</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1990">
@@ -39745,7 +39745,7 @@
         <v>00221725</v>
       </c>
       <c r="F1997">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1998">
@@ -40102,7 +40102,7 @@
         <v>00221747</v>
       </c>
       <c r="F2018">
-        <v>1611500</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2019">
@@ -42271,7 +42271,7 @@
         <v>00315001</v>
       </c>
       <c r="F2129">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="G2129">
         <v>22000</v>
@@ -42288,7 +42288,7 @@
         <v>00315001</v>
       </c>
       <c r="F2130">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="G2130">
         <v>22000</v>
@@ -42322,7 +42322,7 @@
         <v>00315004</v>
       </c>
       <c r="F2132">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G2132">
         <v>220000</v>
@@ -42339,7 +42339,7 @@
         <v>00315005</v>
       </c>
       <c r="F2133">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G2133">
         <v>447000</v>
@@ -42356,7 +42356,7 @@
         <v>00315005</v>
       </c>
       <c r="F2134">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G2134">
         <v>447000</v>
@@ -42407,7 +42407,7 @@
         <v>00315004</v>
       </c>
       <c r="F2137">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G2137">
         <v>220000</v>
@@ -42424,7 +42424,7 @@
         <v>00315004</v>
       </c>
       <c r="F2138">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G2138">
         <v>220000</v>
@@ -42458,7 +42458,7 @@
         <v>00315004</v>
       </c>
       <c r="F2140">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G2140">
         <v>220000</v>
@@ -42475,7 +42475,7 @@
         <v>00315005</v>
       </c>
       <c r="F2141">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G2141">
         <v>447000</v>
@@ -42492,7 +42492,7 @@
         <v>00315005</v>
       </c>
       <c r="F2142">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G2142">
         <v>447000</v>
@@ -42509,7 +42509,7 @@
         <v>00315002</v>
       </c>
       <c r="F2143">
-        <v>54000</v>
+        <v>162000</v>
       </c>
       <c r="G2143">
         <v>60000</v>
@@ -42543,7 +42543,7 @@
         <v>00315004</v>
       </c>
       <c r="F2145">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G2145">
         <v>220000</v>
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2430">
@@ -47081,7 +47081,7 @@
         <v>00221449</v>
       </c>
       <c r="F2476">
-        <v>1003200</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2477">
@@ -47277,7 +47277,7 @@
         <v>00221052</v>
       </c>
       <c r="F2490">
-        <v>2362500</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2491">
@@ -47666,7 +47666,7 @@
         <v>00221064</v>
       </c>
       <c r="F2518">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2519">
@@ -47694,7 +47694,7 @@
         <v>00221066</v>
       </c>
       <c r="F2520">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2521">
@@ -47708,7 +47708,7 @@
         <v>00221069</v>
       </c>
       <c r="F2521">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2522">
@@ -47778,7 +47778,7 @@
         <v>00221074</v>
       </c>
       <c r="F2526">
-        <v>3190000</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2527">
@@ -48198,7 +48198,7 @@
         <v>00221501</v>
       </c>
       <c r="F2556">
-        <v>2046000</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2557">
@@ -48408,7 +48408,7 @@
         <v>00221458</v>
       </c>
       <c r="F2571">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2572">
@@ -48674,7 +48674,7 @@
         <v>00221716</v>
       </c>
       <c r="F2590">
-        <v>2695000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2591">
@@ -48797,7 +48797,7 @@
         <v>00221287</v>
       </c>
       <c r="F2599">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2600">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>234</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2618">
@@ -49147,7 +49147,7 @@
         <v>00221458</v>
       </c>
       <c r="F2624">
-        <v>1936000</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2625">
@@ -49161,7 +49161,7 @@
         <v>00221485</v>
       </c>
       <c r="F2625">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2626">
@@ -49287,7 +49287,7 @@
         <v>00221768</v>
       </c>
       <c r="F2634">
-        <v>1</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2635">
@@ -49427,7 +49427,7 @@
         <v>00221781</v>
       </c>
       <c r="F2644">
-        <v>1</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2645">
@@ -49455,7 +49455,7 @@
         <v>00221785</v>
       </c>
       <c r="F2646">
-        <v>1</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2647">
@@ -49707,7 +49707,7 @@
         <v>00221803</v>
       </c>
       <c r="F2664">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2665">
@@ -50017,7 +50017,7 @@
         <v>00221285</v>
       </c>
       <c r="F2687">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2688">
@@ -50157,7 +50157,7 @@
         <v>00221803</v>
       </c>
       <c r="F2697">
-        <v>1</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2698">
@@ -50213,7 +50213,7 @@
         <v>00221811</v>
       </c>
       <c r="F2701">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2702">
@@ -50227,7 +50227,7 @@
         <v>00221812</v>
       </c>
       <c r="F2702">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2703">
@@ -50297,7 +50297,7 @@
         <v>00221817</v>
       </c>
       <c r="F2707">
-        <v>1</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2708">

--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2743"/>
+  <dimension ref="A1:G2746"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1525,7 +1525,7 @@
         <v>00221652</v>
       </c>
       <c r="F56">
-        <v>3841200</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57">
@@ -1565,7 +1565,7 @@
         <v>00221654</v>
       </c>
       <c r="F58">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="59">
@@ -1685,7 +1685,7 @@
         <v>00221660</v>
       </c>
       <c r="F64">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65">
@@ -1705,7 +1705,7 @@
         <v>00221661</v>
       </c>
       <c r="F65">
-        <v>4158000</v>
+        <v>302</v>
       </c>
     </row>
     <row r="66">
@@ -2679,7 +2679,7 @@
         <v>00221591</v>
       </c>
       <c r="F114">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="115">
@@ -2739,7 +2739,7 @@
         <v>00221594</v>
       </c>
       <c r="F117">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="118">
@@ -3380,7 +3380,7 @@
         <v>00221624</v>
       </c>
       <c r="F148">
-        <v>4675000</v>
+        <v>457</v>
       </c>
     </row>
     <row r="149">
@@ -4618,7 +4618,7 @@
         <v>00221242</v>
       </c>
       <c r="F206">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="207">
@@ -4718,7 +4718,7 @@
         <v>00221523</v>
       </c>
       <c r="F211">
-        <v>1408000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="212">
@@ -6592,7 +6592,7 @@
         <v>00221514</v>
       </c>
       <c r="F296">
-        <v>5148000</v>
+        <v>482</v>
       </c>
     </row>
     <row r="297">
@@ -6692,7 +6692,7 @@
         <v>00221510</v>
       </c>
       <c r="F301">
-        <v>1738000</v>
+        <v>177</v>
       </c>
     </row>
     <row r="302">
@@ -6952,7 +6952,7 @@
         <v>00221537</v>
       </c>
       <c r="F314">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="315">
@@ -7632,7 +7632,7 @@
         <v>00221469</v>
       </c>
       <c r="F348">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="349">
@@ -7872,7 +7872,7 @@
         <v>00221460</v>
       </c>
       <c r="F360">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="361">
@@ -8635,7 +8635,7 @@
         <v>00221291</v>
       </c>
       <c r="F398">
-        <v>1639000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="399">
@@ -8655,7 +8655,7 @@
         <v>00221436</v>
       </c>
       <c r="F399">
-        <v>148</v>
+        <v>123</v>
       </c>
     </row>
     <row r="400">
@@ -9115,7 +9115,7 @@
         <v>00221155</v>
       </c>
       <c r="F422">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="423">
@@ -9195,7 +9195,7 @@
         <v>00221150</v>
       </c>
       <c r="F426">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="427">
@@ -9795,7 +9795,7 @@
         <v>00221064</v>
       </c>
       <c r="F456">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="457">
@@ -9855,7 +9855,7 @@
         <v>00221036</v>
       </c>
       <c r="F459">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="460">
@@ -10035,7 +10035,7 @@
         <v>00221006</v>
       </c>
       <c r="F468">
-        <v>1705000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="469">
@@ -12468,7 +12468,7 @@
         <v>00221091</v>
       </c>
       <c r="F594">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="595">
@@ -12528,7 +12528,7 @@
         <v>00221402</v>
       </c>
       <c r="F597">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="598">
@@ -12828,7 +12828,7 @@
         <v>00221153</v>
       </c>
       <c r="F612">
-        <v>1768800</v>
+        <v>154</v>
       </c>
     </row>
     <row r="613">
@@ -12848,7 +12848,7 @@
         <v>00221153</v>
       </c>
       <c r="F613">
-        <v>1768800</v>
+        <v>154</v>
       </c>
     </row>
     <row r="614">
@@ -13128,7 +13128,7 @@
         <v>00221006</v>
       </c>
       <c r="F627">
-        <v>1705000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="628">
@@ -13288,7 +13288,7 @@
         <v>00221036</v>
       </c>
       <c r="F635">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="636">
@@ -13328,7 +13328,7 @@
         <v>00221042</v>
       </c>
       <c r="F637">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="638">
@@ -13348,7 +13348,7 @@
         <v>00221042</v>
       </c>
       <c r="F638">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="639">
@@ -13368,7 +13368,7 @@
         <v>00221042</v>
       </c>
       <c r="F639">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="640">
@@ -13428,7 +13428,7 @@
         <v>00221046</v>
       </c>
       <c r="F642">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="643">
@@ -13448,7 +13448,7 @@
         <v>00221046</v>
       </c>
       <c r="F643">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="644">
@@ -13748,7 +13748,7 @@
         <v>00221150</v>
       </c>
       <c r="F658">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="659">
@@ -14208,7 +14208,7 @@
         <v>00221036</v>
       </c>
       <c r="F681">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="682">
@@ -27125,7 +27125,7 @@
         <v>00221291</v>
       </c>
       <c r="F1348">
-        <v>1639000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1349">
@@ -27625,7 +27625,7 @@
         <v>00221064</v>
       </c>
       <c r="F1373">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1374">
@@ -29815,7 +29815,7 @@
         <v>00221155</v>
       </c>
       <c r="F1475">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1476">
@@ -29835,7 +29835,7 @@
         <v>00221155</v>
       </c>
       <c r="F1476">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1477">
@@ -29895,7 +29895,7 @@
         <v>00221156</v>
       </c>
       <c r="F1479">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1480">
@@ -30387,7 +30387,7 @@
         <v>00221039</v>
       </c>
       <c r="F1503">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1504">
@@ -30407,7 +30407,7 @@
         <v>00221039</v>
       </c>
       <c r="F1504">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1505">
@@ -30427,7 +30427,7 @@
         <v>00221039</v>
       </c>
       <c r="F1505">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1506">
@@ -38295,7 +38295,7 @@
         <v>221397</v>
       </c>
       <c r="F1914">
-        <v>1936000</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1915">
@@ -38315,7 +38315,7 @@
         <v>221397</v>
       </c>
       <c r="F1915">
-        <v>1936000</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1916">
@@ -39167,7 +39167,7 @@
         <v>00221460</v>
       </c>
       <c r="F1963">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1964">
@@ -39507,7 +39507,7 @@
         <v>00221514</v>
       </c>
       <c r="F1983">
-        <v>5148000</v>
+        <v>482</v>
       </c>
     </row>
     <row r="1984">
@@ -39575,7 +39575,7 @@
         <v>00221711</v>
       </c>
       <c r="F1987">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1988">
@@ -39626,7 +39626,7 @@
         <v>00221710</v>
       </c>
       <c r="F1990">
-        <v>2151600</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1991">
@@ -39643,7 +39643,7 @@
         <v>00221156</v>
       </c>
       <c r="F1991">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1992">
@@ -46493,7 +46493,7 @@
         <v>00221039</v>
       </c>
       <c r="F2434">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2435">
@@ -46983,7 +46983,7 @@
         <v>00221291</v>
       </c>
       <c r="F2469">
-        <v>1639000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2470">
@@ -47666,7 +47666,7 @@
         <v>00221064</v>
       </c>
       <c r="F2518">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2519">
@@ -47988,7 +47988,7 @@
         <v>00221091</v>
       </c>
       <c r="F2541">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2542">
@@ -48030,7 +48030,7 @@
         <v>00221242</v>
       </c>
       <c r="F2544">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2545">
@@ -48142,7 +48142,7 @@
         <v>00221749</v>
       </c>
       <c r="F2552">
-        <v>2084500</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2553">
@@ -48646,7 +48646,7 @@
         <v>00221712</v>
       </c>
       <c r="F2588">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2589">
@@ -48699,7 +48699,7 @@
         <v>00221402</v>
       </c>
       <c r="F2592">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2593">
@@ -48755,7 +48755,7 @@
         <v>00221758</v>
       </c>
       <c r="F2596">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2597">
@@ -49217,7 +49217,7 @@
         <v>00221749</v>
       </c>
       <c r="F2629">
-        <v>2084500</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2630">
@@ -49273,7 +49273,7 @@
         <v>00221767</v>
       </c>
       <c r="F2633">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2634">
@@ -49329,7 +49329,7 @@
         <v>00221771</v>
       </c>
       <c r="F2637">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2638">
@@ -49357,7 +49357,7 @@
         <v>00221773</v>
       </c>
       <c r="F2639">
-        <v>1</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2640">
@@ -49441,7 +49441,7 @@
         <v>00221783</v>
       </c>
       <c r="F2645">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2646">
@@ -49483,7 +49483,7 @@
         <v>00221787</v>
       </c>
       <c r="F2648">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2649">
@@ -49553,7 +49553,7 @@
         <v>00221792</v>
       </c>
       <c r="F2653">
-        <v>1</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2654">
@@ -49819,7 +49819,7 @@
         <v>00221760</v>
       </c>
       <c r="F2672">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2673">
@@ -49844,7 +49844,7 @@
         <v>00221764</v>
       </c>
       <c r="F2674">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2675">
@@ -49900,7 +49900,7 @@
         <v>00221809</v>
       </c>
       <c r="F2678">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2679">
@@ -50199,7 +50199,7 @@
         <v>00221810</v>
       </c>
       <c r="F2700">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2701">
@@ -50269,7 +50269,7 @@
         <v>00221815</v>
       </c>
       <c r="F2705">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2706">
@@ -50283,7 +50283,7 @@
         <v>00221816</v>
       </c>
       <c r="F2706">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2707">
@@ -50801,9 +50801,51 @@
         <v>282</v>
       </c>
     </row>
+    <row r="2744">
+      <c r="B2744" t="str">
+        <v>کرم پودر گلدن رز مدل Satin smoothing شماره 21 حجم 34 میلی لیتر</v>
+      </c>
+      <c r="D2744" t="str">
+        <v>76409882</v>
+      </c>
+      <c r="E2744" t="str">
+        <v>00221155</v>
+      </c>
+      <c r="F2744">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="B2745" t="str">
+        <v>خط چشم مویی گلدن رز مدل Coral رنگ قرمز</v>
+      </c>
+      <c r="D2745" t="str">
+        <v>76377166</v>
+      </c>
+      <c r="E2745" t="str">
+        <v>00221782</v>
+      </c>
+      <c r="F2745">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="B2746" t="str">
+        <v>خط چشم مویی گلدن رز مدل Burgundy شماره 110 رنگ زرشکی</v>
+      </c>
+      <c r="D2746" t="str">
+        <v>76377094</v>
+      </c>
+      <c r="E2746" t="str">
+        <v>00221784</v>
+      </c>
+      <c r="F2746">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2743"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2746"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2746"/>
+  <dimension ref="A1:G2842"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -479,7 +479,7 @@
         <v>00221674</v>
       </c>
       <c r="F4">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -539,7 +539,7 @@
         <v>00221671</v>
       </c>
       <c r="F7">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         <v>00221667</v>
       </c>
       <c r="F11">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -659,7 +659,7 @@
         <v>00207182</v>
       </c>
       <c r="F13">
-        <v>938000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="14">
@@ -679,7 +679,7 @@
         <v>00207183</v>
       </c>
       <c r="F14">
-        <v>938000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="15">
@@ -699,7 +699,7 @@
         <v>00207184</v>
       </c>
       <c r="F15">
-        <v>938000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="16">
@@ -719,7 +719,7 @@
         <v>00207170</v>
       </c>
       <c r="F16">
-        <v>938000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="17">
@@ -1085,7 +1085,7 @@
         <v>00207168</v>
       </c>
       <c r="F34">
-        <v>938000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="35">
@@ -1605,7 +1605,7 @@
         <v>00221656</v>
       </c>
       <c r="F60">
-        <v>3841200</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61">
@@ -2205,7 +2205,7 @@
         <v>00221391</v>
       </c>
       <c r="F90">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91">
@@ -2245,7 +2245,7 @@
         <v>00221375</v>
       </c>
       <c r="F92">
-        <v>5291000</v>
+        <v>473</v>
       </c>
     </row>
     <row r="93">
@@ -2502,7 +2502,7 @@
         <v>45822594</v>
       </c>
       <c r="F105">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="106">
@@ -2519,7 +2519,7 @@
         <v>45822531</v>
       </c>
       <c r="F106">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="107">
@@ -2779,7 +2779,7 @@
         <v>00221596</v>
       </c>
       <c r="F119">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120">
@@ -3300,7 +3300,7 @@
         <v>00221620</v>
       </c>
       <c r="F144">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="145">
@@ -3559,8 +3559,8 @@
       <c r="E157" t="str">
         <v>00221560</v>
       </c>
-      <c r="F157" t="str">
-        <v>1</v>
+      <c r="F157">
+        <v>257</v>
       </c>
     </row>
     <row r="158">
@@ -4907,7 +4907,7 @@
         <v>00216004</v>
       </c>
       <c r="F220">
-        <v>970000</v>
+        <v>1470000</v>
       </c>
       <c r="G220">
         <v>1100300</v>
@@ -6832,7 +6832,7 @@
         <v>00221500</v>
       </c>
       <c r="F308">
-        <v>1210000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="309">
@@ -7572,7 +7572,7 @@
         <v>00221471</v>
       </c>
       <c r="F345">
-        <v>2706000</v>
+        <v>241</v>
       </c>
     </row>
     <row r="346">
@@ -8355,7 +8355,7 @@
         <v>00221359</v>
       </c>
       <c r="F384">
-        <v>1782000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="385">
@@ -8375,7 +8375,7 @@
         <v>00221359</v>
       </c>
       <c r="F385">
-        <v>1782000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="386">
@@ -8395,7 +8395,7 @@
         <v>00221359</v>
       </c>
       <c r="F386">
-        <v>1782000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="387">
@@ -8435,7 +8435,7 @@
         <v>00221312</v>
       </c>
       <c r="F388">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="389">
@@ -8935,7 +8935,7 @@
         <v>00221209</v>
       </c>
       <c r="F413">
-        <v>3753000</v>
+        <v>275</v>
       </c>
     </row>
     <row r="414">
@@ -8995,7 +8995,7 @@
         <v>00221203</v>
       </c>
       <c r="F416">
-        <v>2365000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="417">
@@ -9075,7 +9075,7 @@
         <v>00221159</v>
       </c>
       <c r="F420">
-        <v>2500000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="421">
@@ -9095,7 +9095,7 @@
         <v>00221158</v>
       </c>
       <c r="F421">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="422">
@@ -9215,7 +9215,7 @@
         <v>00221149</v>
       </c>
       <c r="F427">
-        <v>1768800</v>
+        <v>154</v>
       </c>
     </row>
     <row r="428">
@@ -9415,7 +9415,7 @@
         <v>00221133</v>
       </c>
       <c r="F437">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="438">
@@ -9715,7 +9715,7 @@
         <v>00221074</v>
       </c>
       <c r="F452">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="453">
@@ -9895,7 +9895,7 @@
         <v>00221033</v>
       </c>
       <c r="F461">
-        <v>1023103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="462">
@@ -11748,7 +11748,7 @@
         <v>00221080</v>
       </c>
       <c r="F558">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="559">
@@ -11925,7 +11925,7 @@
         <v>38147716</v>
       </c>
       <c r="F567">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G567">
         <v>35000</v>
@@ -11945,7 +11945,7 @@
         <v>38147321</v>
       </c>
       <c r="F568">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G568">
         <v>35000</v>
@@ -11965,7 +11965,7 @@
         <v>38146217</v>
       </c>
       <c r="F569">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G569">
         <v>35000</v>
@@ -11988,7 +11988,7 @@
         <v>00207061</v>
       </c>
       <c r="F570">
-        <v>938000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="571">
@@ -12008,7 +12008,7 @@
         <v>00207061</v>
       </c>
       <c r="F571">
-        <v>938000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="572">
@@ -12048,7 +12048,7 @@
         <v>00221092</v>
       </c>
       <c r="F573">
-        <v>2072400</v>
+        <v>186</v>
       </c>
     </row>
     <row r="574">
@@ -12188,7 +12188,7 @@
         <v>00221258</v>
       </c>
       <c r="F580">
-        <v>984500</v>
+        <v>90</v>
       </c>
     </row>
     <row r="581">
@@ -12968,7 +12968,7 @@
         <v>00221117</v>
       </c>
       <c r="F619">
-        <v>1815000</v>
+        <v>205</v>
       </c>
     </row>
     <row r="620">
@@ -13068,7 +13068,7 @@
         <v>00221018</v>
       </c>
       <c r="F624">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="625">
@@ -13728,7 +13728,7 @@
         <v>00221391</v>
       </c>
       <c r="F657">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="658">
@@ -13868,7 +13868,7 @@
         <v>00221070</v>
       </c>
       <c r="F664">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="665">
@@ -14008,7 +14008,7 @@
         <v>00221307</v>
       </c>
       <c r="F671">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="672">
@@ -14028,7 +14028,7 @@
         <v>00221307</v>
       </c>
       <c r="F672">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="673">
@@ -14048,7 +14048,7 @@
         <v>00221302</v>
       </c>
       <c r="F673">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="674">
@@ -14068,7 +14068,7 @@
         <v>00221133</v>
       </c>
       <c r="F674">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="675">
@@ -14288,7 +14288,7 @@
         <v>00221033</v>
       </c>
       <c r="F685">
-        <v>1023103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="686">
@@ -14459,7 +14459,7 @@
         <v>00221302</v>
       </c>
       <c r="F694">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="695">
@@ -14519,7 +14519,7 @@
         <v>00221209</v>
       </c>
       <c r="F697">
-        <v>3753000</v>
+        <v>275</v>
       </c>
     </row>
     <row r="698">
@@ -14539,7 +14539,7 @@
         <v>00221149</v>
       </c>
       <c r="F698">
-        <v>1768800</v>
+        <v>154</v>
       </c>
     </row>
     <row r="699">
@@ -14871,7 +14871,7 @@
         <v>35978635</v>
       </c>
       <c r="F714">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="715">
@@ -14888,7 +14888,7 @@
         <v>35978537</v>
       </c>
       <c r="F715">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="716">
@@ -18118,7 +18118,7 @@
         <v>00207052</v>
       </c>
       <c r="F878">
-        <v>994000</v>
+        <v>709474</v>
       </c>
     </row>
     <row r="879">
@@ -19060,7 +19060,7 @@
         <v>00221390</v>
       </c>
       <c r="F929">
-        <v>1245000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="930">
@@ -20367,7 +20367,7 @@
         <v>34371439</v>
       </c>
       <c r="F999">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1000">
@@ -20707,7 +20707,7 @@
         <v>00207069</v>
       </c>
       <c r="F1016">
-        <v>938000</v>
+        <v>515611</v>
       </c>
     </row>
     <row r="1017">
@@ -20747,7 +20747,7 @@
         <v>00207071</v>
       </c>
       <c r="F1018">
-        <v>938000</v>
+        <v>515611</v>
       </c>
     </row>
     <row r="1019">
@@ -20767,7 +20767,7 @@
         <v>00207066</v>
       </c>
       <c r="F1019">
-        <v>994000</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1020">
@@ -20787,7 +20787,7 @@
         <v>00207075</v>
       </c>
       <c r="F1020">
-        <v>980000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="1021">
@@ -20827,7 +20827,7 @@
         <v>00207074</v>
       </c>
       <c r="F1022">
-        <v>938000</v>
+        <v>515611</v>
       </c>
     </row>
     <row r="1023">
@@ -20847,7 +20847,7 @@
         <v>00207077</v>
       </c>
       <c r="F1023">
-        <v>938000</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1024">
@@ -20927,7 +20927,7 @@
         <v>00207070</v>
       </c>
       <c r="F1027">
-        <v>994000</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1028">
@@ -21222,7 +21222,7 @@
         <v>00221246</v>
       </c>
       <c r="F1044">
-        <v>2717000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1045">
@@ -21242,7 +21242,7 @@
         <v>00221246</v>
       </c>
       <c r="F1045">
-        <v>2717000</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1046">
@@ -24145,7 +24145,7 @@
         <v>00207056</v>
       </c>
       <c r="F1199">
-        <v>938000</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="1200">
@@ -24185,7 +24185,7 @@
         <v>00207054</v>
       </c>
       <c r="F1201">
-        <v>938000</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="1202">
@@ -24265,7 +24265,7 @@
         <v>00221112</v>
       </c>
       <c r="F1205">
-        <v>2321000</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1206">
@@ -24405,7 +24405,7 @@
         <v>00221074</v>
       </c>
       <c r="F1212">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1213">
@@ -24425,7 +24425,7 @@
         <v>00221076</v>
       </c>
       <c r="F1213">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1214">
@@ -24545,7 +24545,7 @@
         <v>00221076</v>
       </c>
       <c r="F1219">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1220">
@@ -24565,7 +24565,7 @@
         <v>00221074</v>
       </c>
       <c r="F1220">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1221">
@@ -24685,7 +24685,7 @@
         <v>00221119</v>
       </c>
       <c r="F1226">
-        <v>1815000</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1227">
@@ -24765,7 +24765,7 @@
         <v>00221336</v>
       </c>
       <c r="F1230">
-        <v>7182000</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1231">
@@ -24825,7 +24825,7 @@
         <v>00221295</v>
       </c>
       <c r="F1233">
-        <v>1269000</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1234">
@@ -24865,7 +24865,7 @@
         <v>00221149</v>
       </c>
       <c r="F1235">
-        <v>1768800</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1236">
@@ -25045,7 +25045,7 @@
         <v>00221033</v>
       </c>
       <c r="F1244">
-        <v>1023103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1245">
@@ -25105,7 +25105,7 @@
         <v>00221363</v>
       </c>
       <c r="F1247">
-        <v>1705000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1248">
@@ -25205,7 +25205,7 @@
         <v>00221369</v>
       </c>
       <c r="F1252">
-        <v>1705000</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1253">
@@ -25285,7 +25285,7 @@
         <v>00221202</v>
       </c>
       <c r="F1256">
-        <v>2365000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1257">
@@ -25305,7 +25305,7 @@
         <v>00221351</v>
       </c>
       <c r="F1257">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1258">
@@ -25365,7 +25365,7 @@
         <v>00221105</v>
       </c>
       <c r="F1260">
-        <v>1479500</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1261">
@@ -25465,7 +25465,7 @@
         <v>00221033</v>
       </c>
       <c r="F1265">
-        <v>1023103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1266">
@@ -25585,7 +25585,7 @@
         <v>00221037</v>
       </c>
       <c r="F1271">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1272">
@@ -25605,7 +25605,7 @@
         <v>00221037</v>
       </c>
       <c r="F1272">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1273">
@@ -25625,7 +25625,7 @@
         <v>00221037</v>
       </c>
       <c r="F1273">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1274">
@@ -25725,7 +25725,7 @@
         <v>00221312</v>
       </c>
       <c r="F1278">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1279">
@@ -25745,7 +25745,7 @@
         <v>00221202</v>
       </c>
       <c r="F1279">
-        <v>2365000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1280">
@@ -25765,7 +25765,7 @@
         <v>00221350</v>
       </c>
       <c r="F1280">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1281">
@@ -25785,7 +25785,7 @@
         <v>00221359</v>
       </c>
       <c r="F1281">
-        <v>1782000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1282">
@@ -25805,7 +25805,7 @@
         <v>00221375</v>
       </c>
       <c r="F1282">
-        <v>5291000</v>
+        <v>473</v>
       </c>
     </row>
     <row r="1283">
@@ -26165,7 +26165,7 @@
         <v>00221158</v>
       </c>
       <c r="F1300">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1301">
@@ -26265,7 +26265,7 @@
         <v>00221312</v>
       </c>
       <c r="F1305">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1306">
@@ -26285,7 +26285,7 @@
         <v>00221110</v>
       </c>
       <c r="F1306">
-        <v>1815000</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1307">
@@ -26405,7 +26405,7 @@
         <v>00221133</v>
       </c>
       <c r="F1312">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1313">
@@ -26705,7 +26705,7 @@
         <v>00221373</v>
       </c>
       <c r="F1327">
-        <v>2772000</v>
+        <v>368</v>
       </c>
     </row>
     <row r="1328">
@@ -26725,7 +26725,7 @@
         <v>00221120</v>
       </c>
       <c r="F1328">
-        <v>2321000</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1329">
@@ -26745,7 +26745,7 @@
         <v>00221095</v>
       </c>
       <c r="F1329">
-        <v>6255000</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1330">
@@ -26765,7 +26765,7 @@
         <v>00221105</v>
       </c>
       <c r="F1330">
-        <v>1479500</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1331">
@@ -26885,7 +26885,7 @@
         <v>00221203</v>
       </c>
       <c r="F1336">
-        <v>2365000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1337">
@@ -27005,7 +27005,7 @@
         <v>00221349</v>
       </c>
       <c r="F1342">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1343">
@@ -27025,7 +27025,7 @@
         <v>00221032</v>
       </c>
       <c r="F1343">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1344">
@@ -27045,7 +27045,7 @@
         <v>00221032</v>
       </c>
       <c r="F1344">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1345">
@@ -27085,7 +27085,7 @@
         <v>00221037</v>
       </c>
       <c r="F1346">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1347">
@@ -27105,7 +27105,7 @@
         <v>00221247</v>
       </c>
       <c r="F1347">
-        <v>2244000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1348">
@@ -27145,7 +27145,7 @@
         <v>00221352</v>
       </c>
       <c r="F1349">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1350">
@@ -27225,7 +27225,7 @@
         <v>00221110</v>
       </c>
       <c r="F1353">
-        <v>1815000</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1354">
@@ -27245,7 +27245,7 @@
         <v>00221045</v>
       </c>
       <c r="F1354">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1355">
@@ -27425,7 +27425,7 @@
         <v>00221133</v>
       </c>
       <c r="F1363">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1364">
@@ -28261,7 +28261,7 @@
         <v>00221266</v>
       </c>
       <c r="F1403">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1404">
@@ -28281,7 +28281,7 @@
         <v>00221267</v>
       </c>
       <c r="F1404">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1405">
@@ -28301,7 +28301,7 @@
         <v>00221267</v>
       </c>
       <c r="F1405">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1406">
@@ -28321,7 +28321,7 @@
         <v>00221268</v>
       </c>
       <c r="F1406">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1407">
@@ -28341,7 +28341,7 @@
         <v>00221266</v>
       </c>
       <c r="F1407">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1408">
@@ -28381,7 +28381,7 @@
         <v>00221355</v>
       </c>
       <c r="F1409">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1410">
@@ -28481,7 +28481,7 @@
         <v>00221016</v>
       </c>
       <c r="F1414">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1415">
@@ -28501,7 +28501,7 @@
         <v>00221021</v>
       </c>
       <c r="F1415">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1416">
@@ -28561,7 +28561,7 @@
         <v>00221016</v>
       </c>
       <c r="F1418">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1419">
@@ -28601,7 +28601,7 @@
         <v>00221018</v>
       </c>
       <c r="F1420">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1421">
@@ -28621,7 +28621,7 @@
         <v>00221021</v>
       </c>
       <c r="F1421">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1422">
@@ -29695,7 +29695,7 @@
         <v>00221026</v>
       </c>
       <c r="F1469">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1470">
@@ -29735,7 +29735,7 @@
         <v>00221161</v>
       </c>
       <c r="F1471">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1472">
@@ -29775,7 +29775,7 @@
         <v>00221161</v>
       </c>
       <c r="F1473">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1474">
@@ -29855,7 +29855,7 @@
         <v>00221160</v>
       </c>
       <c r="F1477">
-        <v>3586000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1478">
@@ -30115,7 +30115,7 @@
         <v>00221329</v>
       </c>
       <c r="F1490">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1491">
@@ -30155,7 +30155,7 @@
         <v>00221326</v>
       </c>
       <c r="F1492">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1493">
@@ -30215,7 +30215,7 @@
         <v>00221162</v>
       </c>
       <c r="F1495">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1496">
@@ -30487,7 +30487,7 @@
         <v>00221359</v>
       </c>
       <c r="F1508">
-        <v>1782000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1509">
@@ -30681,7 +30681,7 @@
         <v>30834962</v>
       </c>
       <c r="F1518">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1519">
@@ -30744,7 +30744,7 @@
         <v>00221171</v>
       </c>
       <c r="F1521">
-        <v>1205383</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1522">
@@ -30764,7 +30764,7 @@
         <v>00221171</v>
       </c>
       <c r="F1522">
-        <v>1205383</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1523">
@@ -30784,7 +30784,7 @@
         <v>00221159</v>
       </c>
       <c r="F1523">
-        <v>2500000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1524">
@@ -30804,7 +30804,7 @@
         <v>00221070</v>
       </c>
       <c r="F1524">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1525">
@@ -30824,7 +30824,7 @@
         <v>00221070</v>
       </c>
       <c r="F1525">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1526">
@@ -30910,7 +30910,7 @@
         <v>00221301</v>
       </c>
       <c r="F1529">
-        <v>1957500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1530">
@@ -30970,7 +30970,7 @@
         <v>00221359</v>
       </c>
       <c r="F1532">
-        <v>1782000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1533">
@@ -30990,7 +30990,7 @@
         <v>00221359</v>
       </c>
       <c r="F1533">
-        <v>1782000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1534">
@@ -31099,7 +31099,7 @@
         <v>00221322</v>
       </c>
       <c r="F1538">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1539">
@@ -31165,7 +31165,7 @@
         <v>00201009</v>
       </c>
       <c r="F1541">
-        <v>2710000</v>
+        <v>2870000</v>
       </c>
       <c r="G1541">
         <v>1522500</v>
@@ -31188,7 +31188,7 @@
         <v>00201010</v>
       </c>
       <c r="F1542">
-        <v>2710000</v>
+        <v>2870000</v>
       </c>
       <c r="G1542">
         <v>1522500</v>
@@ -31211,7 +31211,7 @@
         <v>00201008</v>
       </c>
       <c r="F1543">
-        <v>2710000</v>
+        <v>2870000</v>
       </c>
       <c r="G1543">
         <v>1522500</v>
@@ -31257,7 +31257,7 @@
         <v>00201011</v>
       </c>
       <c r="F1545">
-        <v>2710000</v>
+        <v>2870000</v>
       </c>
       <c r="G1545">
         <v>1522500</v>
@@ -31280,7 +31280,7 @@
         <v>00201011</v>
       </c>
       <c r="F1546">
-        <v>2710000</v>
+        <v>2870000</v>
       </c>
       <c r="G1546">
         <v>1522500</v>
@@ -31303,7 +31303,7 @@
         <v>00201009</v>
       </c>
       <c r="F1547">
-        <v>2710000</v>
+        <v>2870000</v>
       </c>
       <c r="G1547">
         <v>1522500</v>
@@ -31349,7 +31349,7 @@
         <v>00221019</v>
       </c>
       <c r="F1549">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1550">
@@ -31369,7 +31369,7 @@
         <v>00221292</v>
       </c>
       <c r="F1550">
-        <v>1998000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1551">
@@ -31389,7 +31389,7 @@
         <v>00221292</v>
       </c>
       <c r="F1551">
-        <v>1998000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1552">
@@ -31429,7 +31429,7 @@
         <v>00221260</v>
       </c>
       <c r="F1553">
-        <v>2299000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1554">
@@ -31469,7 +31469,7 @@
         <v>00221301</v>
       </c>
       <c r="F1555">
-        <v>1957500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1556">
@@ -31569,7 +31569,7 @@
         <v>00221334</v>
       </c>
       <c r="F1560">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1561">
@@ -31589,7 +31589,7 @@
         <v>00221005</v>
       </c>
       <c r="F1561">
-        <v>1705000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1562">
@@ -31609,7 +31609,7 @@
         <v>00221019</v>
       </c>
       <c r="F1562">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1563">
@@ -31649,7 +31649,7 @@
         <v>00221290</v>
       </c>
       <c r="F1564">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1565">
@@ -31669,7 +31669,7 @@
         <v>00221019</v>
       </c>
       <c r="F1565">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1566">
@@ -31726,7 +31726,7 @@
         <v>00221057</v>
       </c>
       <c r="F1568">
-        <v>4235000</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1569">
@@ -31892,7 +31892,7 @@
         <v>00221057</v>
       </c>
       <c r="F1576">
-        <v>4235000</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1577">
@@ -31912,7 +31912,7 @@
         <v>00221290</v>
       </c>
       <c r="F1577">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1578">
@@ -31952,7 +31952,7 @@
         <v>00221294</v>
       </c>
       <c r="F1579">
-        <v>502</v>
+        <v>540</v>
       </c>
     </row>
     <row r="1580">
@@ -31972,7 +31972,7 @@
         <v>00221260</v>
       </c>
       <c r="F1580">
-        <v>2299000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1581">
@@ -32012,7 +32012,7 @@
         <v>00221004</v>
       </c>
       <c r="F1582">
-        <v>1716000</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1583">
@@ -32092,7 +32092,7 @@
         <v>00221034</v>
       </c>
       <c r="F1586">
-        <v>1210000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1587">
@@ -32112,7 +32112,7 @@
         <v>00221034</v>
       </c>
       <c r="F1587">
-        <v>1210000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1588">
@@ -32132,7 +32132,7 @@
         <v>00221038</v>
       </c>
       <c r="F1588">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1589">
@@ -32152,7 +32152,7 @@
         <v>00221038</v>
       </c>
       <c r="F1589">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1590">
@@ -32312,7 +32312,7 @@
         <v>00221048</v>
       </c>
       <c r="F1597">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1598">
@@ -32332,7 +32332,7 @@
         <v>00221093</v>
       </c>
       <c r="F1598">
-        <v>4675000</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1599">
@@ -32432,7 +32432,7 @@
         <v>00221005</v>
       </c>
       <c r="F1603">
-        <v>1705000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1604">
@@ -32472,7 +32472,7 @@
         <v>00221290</v>
       </c>
       <c r="F1605">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1606">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>249</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1619">
@@ -33096,7 +33096,7 @@
         <v>55003389</v>
       </c>
       <c r="F1635">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1636">
@@ -34351,7 +34351,7 @@
         <v>48696472</v>
       </c>
       <c r="F1703">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1704">
@@ -34368,7 +34368,7 @@
         <v>48696438</v>
       </c>
       <c r="F1704">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1705">
@@ -34385,7 +34385,7 @@
         <v>48696304</v>
       </c>
       <c r="F1705">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1706">
@@ -34402,7 +34402,7 @@
         <v>48696268</v>
       </c>
       <c r="F1706">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1707">
@@ -34419,7 +34419,7 @@
         <v>48484996</v>
       </c>
       <c r="F1707">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1708">
@@ -34436,7 +34436,7 @@
         <v>48005865</v>
       </c>
       <c r="F1708">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1709">
@@ -34453,7 +34453,7 @@
         <v>48005831</v>
       </c>
       <c r="F1709">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1710">
@@ -34470,7 +34470,7 @@
         <v>48005800</v>
       </c>
       <c r="F1710">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1711">
@@ -34487,7 +34487,7 @@
         <v>48005774</v>
       </c>
       <c r="F1711">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1712">
@@ -34504,7 +34504,7 @@
         <v>48004979</v>
       </c>
       <c r="F1712">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1713">
@@ -34521,7 +34521,7 @@
         <v>48004895</v>
       </c>
       <c r="F1713">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1714">
@@ -34538,7 +34538,7 @@
         <v>48004738</v>
       </c>
       <c r="F1714">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1715">
@@ -34555,7 +34555,7 @@
         <v>49176643</v>
       </c>
       <c r="F1715">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1715">
         <v>974800</v>
@@ -34575,7 +34575,7 @@
         <v>49095632</v>
       </c>
       <c r="F1716">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1716">
         <v>657500</v>
@@ -34595,7 +34595,7 @@
         <v>48005692</v>
       </c>
       <c r="F1717">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1718">
@@ -34612,7 +34612,7 @@
         <v>48805764</v>
       </c>
       <c r="F1718">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1719">
@@ -34629,7 +34629,7 @@
         <v>48499213</v>
       </c>
       <c r="F1719">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1719">
         <v>450000</v>
@@ -34649,7 +34649,7 @@
         <v>48499173</v>
       </c>
       <c r="F1720">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1720">
         <v>1740000</v>
@@ -34669,7 +34669,7 @@
         <v>48483945</v>
       </c>
       <c r="F1721">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1721">
         <v>1740000</v>
@@ -34689,7 +34689,7 @@
         <v>48483874</v>
       </c>
       <c r="F1722">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1722">
         <v>590000</v>
@@ -34709,7 +34709,7 @@
         <v>48483840</v>
       </c>
       <c r="F1723">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1723">
         <v>590000</v>
@@ -34729,7 +34729,7 @@
         <v>47445192</v>
       </c>
       <c r="F1724">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1725">
@@ -34746,7 +34746,7 @@
         <v>47445075</v>
       </c>
       <c r="F1725">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1726">
@@ -34763,7 +34763,7 @@
         <v>44470822</v>
       </c>
       <c r="F1726">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1727">
@@ -34780,7 +34780,7 @@
         <v>43636861</v>
       </c>
       <c r="F1727">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1728">
@@ -36228,7 +36228,7 @@
         <v>111111</v>
       </c>
       <c r="F1806">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1807">
@@ -36673,7 +36673,7 @@
         <v>00216024</v>
       </c>
       <c r="F1832">
-        <v>1150000</v>
+        <v>1440000</v>
       </c>
       <c r="G1832">
         <v>1337000</v>
@@ -36693,7 +36693,7 @@
         <v>00216025</v>
       </c>
       <c r="F1833">
-        <v>1150000</v>
+        <v>1440000</v>
       </c>
       <c r="G1833">
         <v>1337000</v>
@@ -36753,7 +36753,7 @@
         <v>00216028</v>
       </c>
       <c r="F1836">
-        <v>1750000</v>
+        <v>1440000</v>
       </c>
       <c r="G1836">
         <v>1337000</v>
@@ -36824,7 +36824,7 @@
         <v>56329672</v>
       </c>
       <c r="F1840">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1840">
         <v>275200</v>
@@ -37541,7 +37541,7 @@
         <v>50000020</v>
       </c>
       <c r="F1876">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1876">
         <v>275200</v>
@@ -37558,7 +37558,7 @@
         <v>50000030</v>
       </c>
       <c r="F1877">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1877">
         <v>275200</v>
@@ -37575,7 +37575,7 @@
         <v>50000040</v>
       </c>
       <c r="F1878">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G1878">
         <v>275200</v>
@@ -37595,7 +37595,7 @@
         <v>00221244</v>
       </c>
       <c r="F1879">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="1880">
@@ -37652,7 +37652,7 @@
         <v>00201138</v>
       </c>
       <c r="F1882">
-        <v>3050000</v>
+        <v>3250000</v>
       </c>
       <c r="G1882">
         <v>1542000</v>
@@ -38924,7 +38924,7 @@
         <v>57178841</v>
       </c>
       <c r="F1948">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1949">
@@ -38938,7 +38938,7 @@
         <v>56887918</v>
       </c>
       <c r="F1949">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1950">
@@ -38952,7 +38952,7 @@
         <v>56887895</v>
       </c>
       <c r="F1950">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1951">
@@ -38966,7 +38966,7 @@
         <v>57178901</v>
       </c>
       <c r="F1951">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1952">
@@ -38980,7 +38980,7 @@
         <v>57178772</v>
       </c>
       <c r="F1952">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1953">
@@ -38997,7 +38997,7 @@
         <v>00207077</v>
       </c>
       <c r="F1953">
-        <v>994000</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="1954">
@@ -39439,7 +39439,7 @@
         <v>00221045</v>
       </c>
       <c r="F1979">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1980">
@@ -39592,7 +39592,7 @@
         <v>00221034</v>
       </c>
       <c r="F1988">
-        <v>1210000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1989">
@@ -39864,7 +39864,7 @@
         <v>00221732</v>
       </c>
       <c r="F2004">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2005">
@@ -40770,7 +40770,7 @@
         <v>00228030</v>
       </c>
       <c r="F2052">
-        <v>1860000</v>
+        <v>3845000</v>
       </c>
       <c r="G2052">
         <v>1746500</v>
@@ -40810,7 +40810,7 @@
         <v>00228032</v>
       </c>
       <c r="F2054">
-        <v>1920000</v>
+        <v>3845000</v>
       </c>
       <c r="G2054">
         <v>1746500</v>
@@ -40830,7 +40830,7 @@
         <v>00228033</v>
       </c>
       <c r="F2055">
-        <v>1860000</v>
+        <v>3845000</v>
       </c>
       <c r="G2055">
         <v>1746500</v>
@@ -40850,7 +40850,7 @@
         <v>00228034</v>
       </c>
       <c r="F2056">
-        <v>1920000</v>
+        <v>3845000</v>
       </c>
       <c r="G2056">
         <v>1746500</v>
@@ -40870,7 +40870,7 @@
         <v>00228035</v>
       </c>
       <c r="F2057">
-        <v>1920000</v>
+        <v>3845000</v>
       </c>
       <c r="G2057">
         <v>1746500</v>
@@ -40970,7 +40970,7 @@
         <v>00228040</v>
       </c>
       <c r="F2062">
-        <v>1320000</v>
+        <v>2645000</v>
       </c>
       <c r="G2062">
         <v>1364000</v>
@@ -42167,7 +42167,7 @@
         <v>64111292</v>
       </c>
       <c r="F2122">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2122">
         <v>3617000</v>
@@ -42198,7 +42198,7 @@
         <v>64690629</v>
       </c>
       <c r="F2124">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2124">
         <v>1550000</v>
@@ -42212,7 +42212,7 @@
         <v>64690614</v>
       </c>
       <c r="F2125">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2125">
         <v>1550000</v>
@@ -42226,7 +42226,7 @@
         <v>64690581</v>
       </c>
       <c r="F2126">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2126">
         <v>1550000</v>
@@ -42240,7 +42240,7 @@
         <v>64690544</v>
       </c>
       <c r="F2127">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2127">
         <v>1550000</v>
@@ -42254,7 +42254,7 @@
         <v>64690511</v>
       </c>
       <c r="F2128">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2128">
         <v>1550000</v>
@@ -42305,7 +42305,7 @@
         <v>00315003</v>
       </c>
       <c r="F2131">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="G2131">
         <v>66000</v>
@@ -42526,7 +42526,7 @@
         <v>00315003</v>
       </c>
       <c r="F2144">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="G2144">
         <v>66000</v>
@@ -42557,7 +42557,7 @@
         <v>64428822</v>
       </c>
       <c r="F2146">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2146">
         <v>765450</v>
@@ -42571,7 +42571,7 @@
         <v>64333086</v>
       </c>
       <c r="F2147">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2147">
         <v>2256660</v>
@@ -42585,7 +42585,7 @@
         <v>64333041</v>
       </c>
       <c r="F2148">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2148">
         <v>1128330</v>
@@ -42599,7 +42599,7 @@
         <v>64332133</v>
       </c>
       <c r="F2149">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2149">
         <v>2608200</v>
@@ -42613,7 +42613,7 @@
         <v>64332096</v>
       </c>
       <c r="F2150">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2150">
         <v>1304100</v>
@@ -42627,7 +42627,7 @@
         <v>64331568</v>
       </c>
       <c r="F2151">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2151">
         <v>680400</v>
@@ -42641,7 +42641,7 @@
         <v>64331041</v>
       </c>
       <c r="F2152">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2152">
         <v>1338120</v>
@@ -42655,7 +42655,7 @@
         <v>64329671</v>
       </c>
       <c r="F2153">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2153">
         <v>765450</v>
@@ -42669,7 +42669,7 @@
         <v>64328929</v>
       </c>
       <c r="F2154">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2154">
         <v>1020600</v>
@@ -42683,7 +42683,7 @@
         <v>64328529</v>
       </c>
       <c r="F2155">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2155">
         <v>1020600</v>
@@ -42697,7 +42697,7 @@
         <v>64305454</v>
       </c>
       <c r="F2156">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2156">
         <v>517140</v>
@@ -42711,7 +42711,7 @@
         <v>64305180</v>
       </c>
       <c r="F2157">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2157">
         <v>901530</v>
@@ -42725,7 +42725,7 @@
         <v>64305020</v>
       </c>
       <c r="F2158">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2158">
         <v>561330</v>
@@ -42739,7 +42739,7 @@
         <v>64295538</v>
       </c>
       <c r="F2159">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2159">
         <v>425250</v>
@@ -42753,7 +42753,7 @@
         <v>64295369</v>
       </c>
       <c r="F2160">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2160">
         <v>878850</v>
@@ -42767,7 +42767,7 @@
         <v>64295105</v>
       </c>
       <c r="F2161">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2161">
         <v>561330</v>
@@ -42781,7 +42781,7 @@
         <v>64294796</v>
       </c>
       <c r="F2162">
-        <v>282</v>
+        <v>710000</v>
       </c>
       <c r="G2162">
         <v>686070</v>
@@ -43901,7 +43901,7 @@
         <v>68580695</v>
       </c>
       <c r="F2242">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2243">
@@ -43912,7 +43912,7 @@
         <v>68580509</v>
       </c>
       <c r="F2243">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2244">
@@ -43923,7 +43923,7 @@
         <v>68580412</v>
       </c>
       <c r="F2244">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2245">
@@ -43934,7 +43934,7 @@
         <v>68580248</v>
       </c>
       <c r="F2245">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2246">
@@ -43945,7 +43945,7 @@
         <v>68580059</v>
       </c>
       <c r="F2246">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2247">
@@ -43956,7 +43956,7 @@
         <v>68579941</v>
       </c>
       <c r="F2247">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2248">
@@ -43967,7 +43967,7 @@
         <v>68579550</v>
       </c>
       <c r="F2248">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2249">
@@ -43978,7 +43978,7 @@
         <v>68579471</v>
       </c>
       <c r="F2249">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2250">
@@ -43989,7 +43989,7 @@
         <v>68579358</v>
       </c>
       <c r="F2250">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2251">
@@ -44000,7 +44000,7 @@
         <v>68579117</v>
       </c>
       <c r="F2251">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2252">
@@ -44011,7 +44011,7 @@
         <v>68579081</v>
       </c>
       <c r="F2252">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2253">
@@ -44022,7 +44022,7 @@
         <v>68578915</v>
       </c>
       <c r="F2253">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2254">
@@ -44033,7 +44033,7 @@
         <v>68578887</v>
       </c>
       <c r="F2254">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2255">
@@ -44044,7 +44044,7 @@
         <v>68578792</v>
       </c>
       <c r="F2255">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2256">
@@ -44055,7 +44055,7 @@
         <v>68578665</v>
       </c>
       <c r="F2256">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2257">
@@ -44066,7 +44066,7 @@
         <v>68577686</v>
       </c>
       <c r="F2257">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2258">
@@ -44077,7 +44077,7 @@
         <v>68577652</v>
       </c>
       <c r="F2258">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2259">
@@ -44088,7 +44088,7 @@
         <v>68576994</v>
       </c>
       <c r="F2259">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2260">
@@ -44099,7 +44099,7 @@
         <v>68576906</v>
       </c>
       <c r="F2260">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2261">
@@ -44110,7 +44110,7 @@
         <v>68573468</v>
       </c>
       <c r="F2261">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2262">
@@ -44121,7 +44121,7 @@
         <v>68573370</v>
       </c>
       <c r="F2262">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2263">
@@ -44132,7 +44132,7 @@
         <v>68572279</v>
       </c>
       <c r="F2263">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2264">
@@ -44143,7 +44143,7 @@
         <v>68315781</v>
       </c>
       <c r="F2264">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2265">
@@ -44154,7 +44154,7 @@
         <v>68315647</v>
       </c>
       <c r="F2265">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2266">
@@ -44165,7 +44165,7 @@
         <v>68297855</v>
       </c>
       <c r="F2266">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2267">
@@ -44176,7 +44176,7 @@
         <v>68297737</v>
       </c>
       <c r="F2267">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2268">
@@ -44187,7 +44187,7 @@
         <v>68297319</v>
       </c>
       <c r="F2268">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2269">
@@ -44198,7 +44198,7 @@
         <v>68289446</v>
       </c>
       <c r="F2269">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2270">
@@ -44223,7 +44223,7 @@
         <v>55555555</v>
       </c>
       <c r="F2271">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2272">
@@ -44234,7 +44234,7 @@
         <v>55555556</v>
       </c>
       <c r="F2272">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2273">
@@ -44242,7 +44242,7 @@
         <v xml:space="preserve">دستمال مرطوب دافی  Q10 </v>
       </c>
       <c r="F2273">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2274">
@@ -45348,7 +45348,7 @@
         <v>00228105</v>
       </c>
       <c r="F2352">
-        <v>1821000</v>
+        <v>3770000</v>
       </c>
     </row>
     <row r="2353">
@@ -45362,7 +45362,7 @@
         <v>00228106</v>
       </c>
       <c r="F2353">
-        <v>1821000</v>
+        <v>3770000</v>
       </c>
     </row>
     <row r="2354">
@@ -45376,7 +45376,7 @@
         <v>00228107</v>
       </c>
       <c r="F2354">
-        <v>1890000</v>
+        <v>3770000</v>
       </c>
     </row>
     <row r="2355">
@@ -45390,7 +45390,7 @@
         <v>00228108</v>
       </c>
       <c r="F2355">
-        <v>1821000</v>
+        <v>3770000</v>
       </c>
     </row>
     <row r="2356">
@@ -45432,7 +45432,7 @@
         <v>00228111</v>
       </c>
       <c r="F2358">
-        <v>1890000</v>
+        <v>3770000</v>
       </c>
     </row>
     <row r="2359">
@@ -45502,7 +45502,7 @@
         <v>00228116</v>
       </c>
       <c r="F2363">
-        <v>918000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="2364">
@@ -45516,7 +45516,7 @@
         <v>00228117</v>
       </c>
       <c r="F2364">
-        <v>918000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="2365">
@@ -45530,7 +45530,7 @@
         <v>00228118</v>
       </c>
       <c r="F2365">
-        <v>918000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="2366">
@@ -45544,7 +45544,7 @@
         <v>00228119</v>
       </c>
       <c r="F2366">
-        <v>918000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="2367">
@@ -45558,7 +45558,7 @@
         <v>00228120</v>
       </c>
       <c r="F2367">
-        <v>913000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="2368">
@@ -45737,7 +45737,7 @@
         <v>72014008</v>
       </c>
       <c r="F2380">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2381">
@@ -46059,7 +46059,7 @@
         <v>00228147</v>
       </c>
       <c r="F2403">
-        <v>851000</v>
+        <v>1790000</v>
       </c>
     </row>
     <row r="2404">
@@ -46087,7 +46087,7 @@
         <v>00228149</v>
       </c>
       <c r="F2405">
-        <v>1185960</v>
+        <v>1790000</v>
       </c>
     </row>
     <row r="2406">
@@ -46101,7 +46101,7 @@
         <v>00228150</v>
       </c>
       <c r="F2406">
-        <v>851000</v>
+        <v>1790000</v>
       </c>
     </row>
     <row r="2407">
@@ -46129,7 +46129,7 @@
         <v>00228152</v>
       </c>
       <c r="F2408">
-        <v>851000</v>
+        <v>1790000</v>
       </c>
     </row>
     <row r="2409">
@@ -46143,7 +46143,7 @@
         <v>00228153</v>
       </c>
       <c r="F2409">
-        <v>1921100</v>
+        <v>2890000</v>
       </c>
     </row>
     <row r="2410">
@@ -46157,7 +46157,7 @@
         <v>00228154</v>
       </c>
       <c r="F2410">
-        <v>1921100</v>
+        <v>2890000</v>
       </c>
     </row>
     <row r="2411">
@@ -46171,7 +46171,7 @@
         <v>00228155</v>
       </c>
       <c r="F2411">
-        <v>1382000</v>
+        <v>2890000</v>
       </c>
     </row>
     <row r="2412">
@@ -46213,7 +46213,7 @@
         <v>00228158</v>
       </c>
       <c r="F2414">
-        <v>1382000</v>
+        <v>2890000</v>
       </c>
     </row>
     <row r="2415">
@@ -46227,7 +46227,7 @@
         <v>00228159</v>
       </c>
       <c r="F2415">
-        <v>1937500</v>
+        <v>3880000</v>
       </c>
     </row>
     <row r="2416">
@@ -46241,7 +46241,7 @@
         <v>00228160</v>
       </c>
       <c r="F2416">
-        <v>1937500</v>
+        <v>3880000</v>
       </c>
     </row>
     <row r="2417">
@@ -46255,7 +46255,7 @@
         <v>00228161</v>
       </c>
       <c r="F2417">
-        <v>1937500</v>
+        <v>3880000</v>
       </c>
     </row>
     <row r="2418">
@@ -46269,7 +46269,7 @@
         <v>00228162</v>
       </c>
       <c r="F2418">
-        <v>1937500</v>
+        <v>3880000</v>
       </c>
     </row>
     <row r="2419">
@@ -46283,7 +46283,7 @@
         <v>00228163</v>
       </c>
       <c r="F2419">
-        <v>1980000</v>
+        <v>3880000</v>
       </c>
     </row>
     <row r="2420">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>249</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2430">
@@ -46465,7 +46465,7 @@
         <v>00221019</v>
       </c>
       <c r="F2432">
-        <v>4394500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2433">
@@ -46479,7 +46479,7 @@
         <v>00221037</v>
       </c>
       <c r="F2433">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2434">
@@ -46521,7 +46521,7 @@
         <v>00221070</v>
       </c>
       <c r="F2436">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2437">
@@ -46577,7 +46577,7 @@
         <v>00221292</v>
       </c>
       <c r="F2440">
-        <v>1998000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2441">
@@ -46955,7 +46955,7 @@
         <v>00221026</v>
       </c>
       <c r="F2467">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2468">
@@ -47011,7 +47011,7 @@
         <v>00221349</v>
       </c>
       <c r="F2471">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2472">
@@ -47025,7 +47025,7 @@
         <v>00221352</v>
       </c>
       <c r="F2472">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2473">
@@ -47137,7 +47137,7 @@
         <v>00221038</v>
       </c>
       <c r="F2480">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2481">
@@ -47179,7 +47179,7 @@
         <v>00221292</v>
       </c>
       <c r="F2483">
-        <v>1998000</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2484">
@@ -47193,7 +47193,7 @@
         <v>00221334</v>
       </c>
       <c r="F2484">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2485">
@@ -47487,7 +47487,7 @@
         <v>00221732</v>
       </c>
       <c r="F2505">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2506">
@@ -47624,7 +47624,7 @@
         <v>74313106</v>
       </c>
       <c r="F2515">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2516">
@@ -47722,7 +47722,7 @@
         <v>00221070</v>
       </c>
       <c r="F2522">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2523">
@@ -47778,7 +47778,7 @@
         <v>00221074</v>
       </c>
       <c r="F2526">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2527">
@@ -47806,7 +47806,7 @@
         <v>00221076</v>
       </c>
       <c r="F2528">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2529">
@@ -47862,7 +47862,7 @@
         <v>00221080</v>
       </c>
       <c r="F2532">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2533">
@@ -48002,7 +48002,7 @@
         <v>00221212</v>
       </c>
       <c r="F2542">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2543">
@@ -48058,7 +48058,7 @@
         <v>00221260</v>
       </c>
       <c r="F2546">
-        <v>2299000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2547">
@@ -48685,7 +48685,7 @@
         <v>75283541</v>
       </c>
       <c r="F2591">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2592">
@@ -48727,7 +48727,7 @@
         <v>00221349</v>
       </c>
       <c r="F2594">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2595">
@@ -48741,7 +48741,7 @@
         <v>00221352</v>
       </c>
       <c r="F2595">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2596">
@@ -48881,7 +48881,7 @@
         <v>00221350</v>
       </c>
       <c r="F2605">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2606">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>249</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>249</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2618">
@@ -49063,7 +49063,7 @@
         <v>00221158</v>
       </c>
       <c r="F2618">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2619">
@@ -49105,7 +49105,7 @@
         <v>00221244</v>
       </c>
       <c r="F2621">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2622">
@@ -49119,7 +49119,7 @@
         <v>00221351</v>
       </c>
       <c r="F2622">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2623">
@@ -49315,7 +49315,7 @@
         <v>00221770</v>
       </c>
       <c r="F2636">
-        <v>1</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2637">
@@ -49413,7 +49413,7 @@
         <v>00221780</v>
       </c>
       <c r="F2643">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2644">
@@ -49469,7 +49469,7 @@
         <v>00221786</v>
       </c>
       <c r="F2647">
-        <v>1</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2648">
@@ -49830,7 +49830,7 @@
         <v>76410461</v>
       </c>
       <c r="F2673">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2674">
@@ -49886,7 +49886,7 @@
         <v>00221779</v>
       </c>
       <c r="F2677">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2678">
@@ -49911,7 +49911,7 @@
         <v>76636716</v>
       </c>
       <c r="F2679">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2680">
@@ -49922,7 +49922,7 @@
         <v>76636706</v>
       </c>
       <c r="F2680">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2681">
@@ -49933,7 +49933,7 @@
         <v>76636688</v>
       </c>
       <c r="F2681">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2682">
@@ -50255,7 +50255,7 @@
         <v>00221814</v>
       </c>
       <c r="F2704">
-        <v>1</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2705">
@@ -50381,7 +50381,7 @@
         <v>00221821</v>
       </c>
       <c r="F2713">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2714">
@@ -50798,7 +50798,7 @@
         <v>80628922</v>
       </c>
       <c r="F2743">
-        <v>282</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="2744">
@@ -50843,9 +50843,1353 @@
         <v>206</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="B2747" t="str">
+        <v>برق لب مایع پاستل شماره 301</v>
+      </c>
+      <c r="D2747" t="str">
+        <v>81946373</v>
+      </c>
+      <c r="E2747" t="str">
+        <v>00220032</v>
+      </c>
+      <c r="F2747">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="B2748" t="str">
+        <v>کرم پودر مایع SPF20 گلدن رز مدل Moisture Touch مناسب برای انواع پوست شماره 101 حجم 30 میلی‌لیتر</v>
+      </c>
+      <c r="D2748" t="str">
+        <v>81587375</v>
+      </c>
+      <c r="E2748" t="str">
+        <v>00221874</v>
+      </c>
+      <c r="F2748">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="B2749" t="str">
+        <v>کرم پودر مایع SPF20 گلدن رز مدل Moisture Touch مناسب برای انواع پوست شماره 103 حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2749" t="str">
+        <v>81587308</v>
+      </c>
+      <c r="E2749" t="str">
+        <v>00221875</v>
+      </c>
+      <c r="F2749">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="B2750" t="str">
+        <v>کرم پودر مایع SPF20 گلدن رز مدل Moisture Touch شماره 105 مناسب برای انواع پوست حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2750" t="str">
+        <v>81587246</v>
+      </c>
+      <c r="E2750" t="str">
+        <v>00221876</v>
+      </c>
+      <c r="F2750">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="B2751" t="str">
+        <v>رژلب جامد مات گلدن رز مدل Mix شماره 02 مجموعه 4 عددی</v>
+      </c>
+      <c r="D2751" t="str">
+        <v>81587078</v>
+      </c>
+      <c r="E2751" t="str">
+        <v>00221877</v>
+      </c>
+      <c r="F2751">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="B2752" t="str">
+        <v>لاک ناخن گلدن رز مدل Color Expert 02</v>
+      </c>
+      <c r="D2752" t="str">
+        <v>81992064</v>
+      </c>
+      <c r="E2752" t="str">
+        <v>00231002</v>
+      </c>
+      <c r="F2752">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="B2753" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 07</v>
+      </c>
+      <c r="D2753" t="str">
+        <v>81956873</v>
+      </c>
+      <c r="E2753" t="str">
+        <v>00231005</v>
+      </c>
+      <c r="F2753">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="B2754" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 07</v>
+      </c>
+      <c r="D2754" t="str">
+        <v>81947433</v>
+      </c>
+      <c r="E2754" t="str">
+        <v>00231005</v>
+      </c>
+      <c r="F2754">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="B2755" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 11</v>
+      </c>
+      <c r="D2755" t="str">
+        <v>81993215</v>
+      </c>
+      <c r="E2755" t="str">
+        <v>00231008</v>
+      </c>
+      <c r="F2755">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="B2756" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 15</v>
+      </c>
+      <c r="D2756" t="str">
+        <v>81947898</v>
+      </c>
+      <c r="E2756" t="str">
+        <v>00231011</v>
+      </c>
+      <c r="F2756">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="B2757" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 18</v>
+      </c>
+      <c r="D2757" t="str">
+        <v>81955977</v>
+      </c>
+      <c r="E2757" t="str">
+        <v>00231014</v>
+      </c>
+      <c r="F2757">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="B2758" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 20</v>
+      </c>
+      <c r="D2758" t="str">
+        <v>81948788</v>
+      </c>
+      <c r="E2758" t="str">
+        <v>00231016</v>
+      </c>
+      <c r="F2758">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="B2759" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 23</v>
+      </c>
+      <c r="D2759" t="str">
+        <v>81953275</v>
+      </c>
+      <c r="E2759" t="str">
+        <v>00231019</v>
+      </c>
+      <c r="F2759">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="B2760" t="str">
+        <v>لاک گلدن رز مدل اکسپرت گلدن رز شماره 24</v>
+      </c>
+      <c r="D2760" t="str">
+        <v>81946875</v>
+      </c>
+      <c r="E2760" t="str">
+        <v>00231020</v>
+      </c>
+      <c r="F2760">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="B2761" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 25</v>
+      </c>
+      <c r="D2761" t="str">
+        <v>81993249</v>
+      </c>
+      <c r="E2761" t="str">
+        <v>00231021</v>
+      </c>
+      <c r="F2761">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="B2762" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 25</v>
+      </c>
+      <c r="D2762" t="str">
+        <v>81956508</v>
+      </c>
+      <c r="E2762" t="str">
+        <v>00231021</v>
+      </c>
+      <c r="F2762">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="B2763" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 26</v>
+      </c>
+      <c r="D2763" t="str">
+        <v>81947867</v>
+      </c>
+      <c r="E2763" t="str">
+        <v>00231022</v>
+      </c>
+      <c r="F2763">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="B2764" t="str">
+        <v>لاک ناخن گلدن رز شماره 30</v>
+      </c>
+      <c r="D2764" t="str">
+        <v>81992945</v>
+      </c>
+      <c r="E2764" t="str">
+        <v>00231025</v>
+      </c>
+      <c r="F2764">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="B2765" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 30</v>
+      </c>
+      <c r="D2765" t="str">
+        <v>81947263</v>
+      </c>
+      <c r="E2765" t="str">
+        <v>00231025</v>
+      </c>
+      <c r="F2765">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="B2766" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 32</v>
+      </c>
+      <c r="D2766" t="str">
+        <v>81955798</v>
+      </c>
+      <c r="E2766" t="str">
+        <v>00231027</v>
+      </c>
+      <c r="F2766">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="B2767" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 32</v>
+      </c>
+      <c r="D2767" t="str">
+        <v>81947968</v>
+      </c>
+      <c r="E2767" t="str">
+        <v>00231027</v>
+      </c>
+      <c r="F2767">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="B2768" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 33</v>
+      </c>
+      <c r="D2768" t="str">
+        <v>81992820</v>
+      </c>
+      <c r="E2768" t="str">
+        <v>00231028</v>
+      </c>
+      <c r="F2768">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="B2769" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 33</v>
+      </c>
+      <c r="D2769" t="str">
+        <v>81957352</v>
+      </c>
+      <c r="E2769" t="str">
+        <v>00231028</v>
+      </c>
+      <c r="F2769">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="B2770" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 34</v>
+      </c>
+      <c r="D2770" t="str">
+        <v>81948006</v>
+      </c>
+      <c r="E2770" t="str">
+        <v>00231029</v>
+      </c>
+      <c r="F2770">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="B2771" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 35</v>
+      </c>
+      <c r="D2771" t="str">
+        <v>81956461</v>
+      </c>
+      <c r="E2771" t="str">
+        <v>00231030</v>
+      </c>
+      <c r="F2771">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="B2772" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 35</v>
+      </c>
+      <c r="D2772" t="str">
+        <v>81951992</v>
+      </c>
+      <c r="E2772" t="str">
+        <v>00231030</v>
+      </c>
+      <c r="F2772">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="B2773" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 36</v>
+      </c>
+      <c r="D2773" t="str">
+        <v>81957468</v>
+      </c>
+      <c r="E2773" t="str">
+        <v>00231031</v>
+      </c>
+      <c r="F2773">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="B2774" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 37</v>
+      </c>
+      <c r="D2774" t="str">
+        <v>81948153</v>
+      </c>
+      <c r="E2774" t="str">
+        <v>00231032</v>
+      </c>
+      <c r="F2774">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="B2775" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 39</v>
+      </c>
+      <c r="D2775" t="str">
+        <v>81948203</v>
+      </c>
+      <c r="E2775" t="str">
+        <v>00231033</v>
+      </c>
+      <c r="F2775">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="B2776" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 40</v>
+      </c>
+      <c r="D2776" t="str">
+        <v>81956828</v>
+      </c>
+      <c r="E2776" t="str">
+        <v>00231034</v>
+      </c>
+      <c r="F2776">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="B2777" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 42</v>
+      </c>
+      <c r="D2777" t="str">
+        <v>81956714</v>
+      </c>
+      <c r="E2777" t="str">
+        <v>00231036</v>
+      </c>
+      <c r="F2777">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="B2778" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 44</v>
+      </c>
+      <c r="D2778" t="str">
+        <v>81957294</v>
+      </c>
+      <c r="E2778" t="str">
+        <v>00231038</v>
+      </c>
+      <c r="F2778">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="B2779" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 44</v>
+      </c>
+      <c r="D2779" t="str">
+        <v>81948116</v>
+      </c>
+      <c r="E2779" t="str">
+        <v>00231038</v>
+      </c>
+      <c r="F2779">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="B2780" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 50</v>
+      </c>
+      <c r="D2780" t="str">
+        <v>81947766</v>
+      </c>
+      <c r="E2780" t="str">
+        <v>00231041</v>
+      </c>
+      <c r="F2780">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="B2781" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 50</v>
+      </c>
+      <c r="D2781" t="str">
+        <v>81947315</v>
+      </c>
+      <c r="E2781" t="str">
+        <v>00231041</v>
+      </c>
+      <c r="F2781">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="B2782" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 53</v>
+      </c>
+      <c r="D2782" t="str">
+        <v>81956335</v>
+      </c>
+      <c r="E2782" t="str">
+        <v>00231042</v>
+      </c>
+      <c r="F2782">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="B2783" t="str">
+        <v>لاک ناخن گلدن رز مدل Color Expert شماره 54</v>
+      </c>
+      <c r="D2783" t="str">
+        <v>81993682</v>
+      </c>
+      <c r="E2783" t="str">
+        <v>00231043</v>
+      </c>
+      <c r="F2783">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="B2784" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 54</v>
+      </c>
+      <c r="D2784" t="str">
+        <v>81956359</v>
+      </c>
+      <c r="E2784" t="str">
+        <v>00231043</v>
+      </c>
+      <c r="F2784">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="B2785" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 55</v>
+      </c>
+      <c r="D2785" t="str">
+        <v>81947385</v>
+      </c>
+      <c r="E2785" t="str">
+        <v>00231044</v>
+      </c>
+      <c r="F2785">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="B2786" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 57</v>
+      </c>
+      <c r="D2786" t="str">
+        <v>81951624</v>
+      </c>
+      <c r="E2786" t="str">
+        <v>00231045</v>
+      </c>
+      <c r="F2786">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="B2787" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 57</v>
+      </c>
+      <c r="D2787" t="str">
+        <v>81947681</v>
+      </c>
+      <c r="E2787" t="str">
+        <v>00231045</v>
+      </c>
+      <c r="F2787">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="B2788" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 58</v>
+      </c>
+      <c r="D2788" t="str">
+        <v>81948716</v>
+      </c>
+      <c r="E2788" t="str">
+        <v>00231046</v>
+      </c>
+      <c r="F2788">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="B2789" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 60</v>
+      </c>
+      <c r="D2789" t="str">
+        <v>81956385</v>
+      </c>
+      <c r="E2789" t="str">
+        <v>00231047</v>
+      </c>
+      <c r="F2789">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="B2790" t="str">
+        <v>لاک گلدن رز مدل کالر اکسپرت شماره 61</v>
+      </c>
+      <c r="D2790" t="str">
+        <v>81951833</v>
+      </c>
+      <c r="E2790" t="str">
+        <v>00231048</v>
+      </c>
+      <c r="F2790">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="B2791" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 69</v>
+      </c>
+      <c r="D2791" t="str">
+        <v>81952319</v>
+      </c>
+      <c r="E2791" t="str">
+        <v>00231056</v>
+      </c>
+      <c r="F2791">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="B2792" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 69</v>
+      </c>
+      <c r="D2792" t="str">
+        <v>81950315</v>
+      </c>
+      <c r="E2792" t="str">
+        <v>00231056</v>
+      </c>
+      <c r="F2792">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="B2793" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 81</v>
+      </c>
+      <c r="D2793" t="str">
+        <v>81953240</v>
+      </c>
+      <c r="E2793" t="str">
+        <v>00231065</v>
+      </c>
+      <c r="F2793">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="B2794" t="str">
+        <v>لاک گلدن رز مدل کالر اکسپرت شماره 89</v>
+      </c>
+      <c r="D2794" t="str">
+        <v>81947803</v>
+      </c>
+      <c r="E2794" t="str">
+        <v>00231072</v>
+      </c>
+      <c r="F2794">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="B2795" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 102</v>
+      </c>
+      <c r="D2795" t="str">
+        <v>81957919</v>
+      </c>
+      <c r="E2795" t="str">
+        <v>00231082</v>
+      </c>
+      <c r="F2795">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="B2796" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 105</v>
+      </c>
+      <c r="D2796" t="str">
+        <v>81992383</v>
+      </c>
+      <c r="E2796" t="str">
+        <v>00231085</v>
+      </c>
+      <c r="F2796">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="B2797" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 105</v>
+      </c>
+      <c r="D2797" t="str">
+        <v>81948244</v>
+      </c>
+      <c r="E2797" t="str">
+        <v>00231085</v>
+      </c>
+      <c r="F2797">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="B2798" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 107</v>
+      </c>
+      <c r="D2798" t="str">
+        <v>81957768</v>
+      </c>
+      <c r="E2798" t="str">
+        <v>00231087</v>
+      </c>
+      <c r="F2798">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="B2799" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 119</v>
+      </c>
+      <c r="D2799" t="str">
+        <v>81952757</v>
+      </c>
+      <c r="E2799" t="str">
+        <v>00231094</v>
+      </c>
+      <c r="F2799">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="B2800" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 136</v>
+      </c>
+      <c r="D2800" t="str">
+        <v>81952851</v>
+      </c>
+      <c r="E2800" t="str">
+        <v>00231100</v>
+      </c>
+      <c r="F2800">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="B2801" t="str">
+        <v>لاک ناخن گلدن رز مدل 143</v>
+      </c>
+      <c r="D2801" t="str">
+        <v>81993771</v>
+      </c>
+      <c r="E2801" t="str">
+        <v>00231101</v>
+      </c>
+      <c r="F2801">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="B2802" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 73</v>
+      </c>
+      <c r="D2802" t="str">
+        <v>81957501</v>
+      </c>
+      <c r="E2802" t="str">
+        <v>00231105</v>
+      </c>
+      <c r="F2802">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="B2803" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 45</v>
+      </c>
+      <c r="D2803" t="str">
+        <v>81956966</v>
+      </c>
+      <c r="E2803" t="str">
+        <v>00231110</v>
+      </c>
+      <c r="F2803">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="B2804" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 59</v>
+      </c>
+      <c r="D2804" t="str">
+        <v>81956926</v>
+      </c>
+      <c r="E2804" t="str">
+        <v>00231111</v>
+      </c>
+      <c r="F2804">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="B2805" t="str">
+        <v>لاک ناخن گلدن رز مدل Color Expert شماره 157</v>
+      </c>
+      <c r="D2805" t="str">
+        <v>81953861</v>
+      </c>
+      <c r="E2805" t="str">
+        <v>00231117</v>
+      </c>
+      <c r="F2805">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="B2806" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 51</v>
+      </c>
+      <c r="D2806" t="str">
+        <v>81953801</v>
+      </c>
+      <c r="E2806" t="str">
+        <v>00231118</v>
+      </c>
+      <c r="F2806">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="B2807" t="str">
+        <v>مداد چشم گلدن رز مدل Dream شماره 419</v>
+      </c>
+      <c r="D2807" t="str">
+        <v>81954035</v>
+      </c>
+      <c r="E2807" t="str">
+        <v>00221258</v>
+      </c>
+      <c r="F2807">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="B2808" t="str">
+        <v>مداد چشم گلدن رز مدل DREAM شماره 420</v>
+      </c>
+      <c r="D2808" t="str">
+        <v>81992130</v>
+      </c>
+      <c r="E2808" t="str">
+        <v>00221259</v>
+      </c>
+      <c r="F2808">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="B2809" t="str">
+        <v>رژ گونه گلدن رز شماره 16</v>
+      </c>
+      <c r="D2809" t="str">
+        <v>82420254</v>
+      </c>
+      <c r="E2809" t="str">
+        <v>00221327</v>
+      </c>
+      <c r="F2809">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="B2810" t="str">
+        <v>مداد چشم گلدن رز مدل Dream شماره 425</v>
+      </c>
+      <c r="D2810" t="str">
+        <v>81993606</v>
+      </c>
+      <c r="E2810" t="str">
+        <v>00221677</v>
+      </c>
+      <c r="F2810">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="B2811" t="str">
+        <v>مداد لب گلدن رز مدل Dream شماره 505</v>
+      </c>
+      <c r="D2811" t="str">
+        <v>81992494</v>
+      </c>
+      <c r="E2811" t="str">
+        <v>00221704</v>
+      </c>
+      <c r="F2811">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="B2812" t="str">
+        <v>مداد لب گلدن رز مدل Dream شماره 505</v>
+      </c>
+      <c r="D2812" t="str">
+        <v>81953985</v>
+      </c>
+      <c r="E2812" t="str">
+        <v>00221704</v>
+      </c>
+      <c r="F2812">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="B2813" t="str">
+        <v>رژ لب مایع گلدن رز مدل متالز شماره 56</v>
+      </c>
+      <c r="D2813" t="str">
+        <v>81956756</v>
+      </c>
+      <c r="E2813" t="str">
+        <v>00221711</v>
+      </c>
+      <c r="F2813">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="B2814" t="str">
+        <v>رژ لب مدادی گلدن رز شماره 02</v>
+      </c>
+      <c r="D2814" t="str">
+        <v>81993361</v>
+      </c>
+      <c r="E2814" t="str">
+        <v>00221759</v>
+      </c>
+      <c r="F2814">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="B2815" t="str">
+        <v>رژلب گلدن رز مدل Velvet شماره 21</v>
+      </c>
+      <c r="D2815" t="str">
+        <v>81952783</v>
+      </c>
+      <c r="E2815" t="str">
+        <v>00221765</v>
+      </c>
+      <c r="F2815">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="B2816" t="str">
+        <v>رژ لب مایع گلدن رز شماره 51</v>
+      </c>
+      <c r="D2816" t="str">
+        <v>81955904</v>
+      </c>
+      <c r="E2816" t="str">
+        <v>00221851</v>
+      </c>
+      <c r="F2816">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="B2817" t="str">
+        <v>مداد لب گلدن رز مدل Dream شماره 508</v>
+      </c>
+      <c r="D2817" t="str">
+        <v>81955334</v>
+      </c>
+      <c r="E2817" t="str">
+        <v>00221853</v>
+      </c>
+      <c r="F2817">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="B2818" t="str">
+        <v>رژلب مدادی گلدن رز شماره 03</v>
+      </c>
+      <c r="D2818" t="str">
+        <v>81953837</v>
+      </c>
+      <c r="E2818" t="str">
+        <v>00221854</v>
+      </c>
+      <c r="F2818">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="B2819" t="str">
+        <v>رژ لب مایع گلدن رز شماره 53</v>
+      </c>
+      <c r="D2819" t="str">
+        <v>81952517</v>
+      </c>
+      <c r="E2819" t="str">
+        <v>00221855</v>
+      </c>
+      <c r="F2819">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="B2820" t="str">
+        <v>ژل ابرو گلدن رز مدل So Cute</v>
+      </c>
+      <c r="D2820" t="str">
+        <v>81950832</v>
+      </c>
+      <c r="E2820" t="str">
+        <v>00221861</v>
+      </c>
+      <c r="F2820">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="B2821" t="str">
+        <v>کانتور گلدن رز مدل Look</v>
+      </c>
+      <c r="D2821" t="str">
+        <v>81950488</v>
+      </c>
+      <c r="E2821" t="str">
+        <v>00221862</v>
+      </c>
+      <c r="F2821">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="B2822" t="str">
+        <v>رژ لب مایع گلدن رز مدل 1221 شماره 31</v>
+      </c>
+      <c r="D2822" t="str">
+        <v>81950279</v>
+      </c>
+      <c r="E2822" t="str">
+        <v>00221863</v>
+      </c>
+      <c r="F2822">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="B2823" t="str">
+        <v>رژلب جامد مات گلدن رز مدل Mini مجموعه 4 عددی</v>
+      </c>
+      <c r="D2823" t="str">
+        <v>82420199</v>
+      </c>
+      <c r="E2823" t="str">
+        <v>00221879</v>
+      </c>
+      <c r="F2823">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="B2824" t="str">
+        <v>ریمل گلدن رز مدل Flash رنگ زرشکی تیره شماره 10</v>
+      </c>
+      <c r="D2824" t="str">
+        <v>82230424</v>
+      </c>
+      <c r="E2824" t="str">
+        <v>00221880</v>
+      </c>
+      <c r="F2824">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="B2825" t="str">
+        <v>رژ لب جامد گلدن رز مدل SHEER BRIGHT رنگ قرمز شماره 103</v>
+      </c>
+      <c r="D2825" t="str">
+        <v>82076973</v>
+      </c>
+      <c r="E2825" t="str">
+        <v>00221885</v>
+      </c>
+      <c r="F2825">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="B2826" t="str">
+        <v>خط چشم مویی مات گلدن رز مدل Flash Liner رنگ شکلاتی شماره 111</v>
+      </c>
+      <c r="D2826" t="str">
+        <v>82230296</v>
+      </c>
+      <c r="E2826" t="str">
+        <v>00221891</v>
+      </c>
+      <c r="F2826">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="B2827" t="str">
+        <v>خط چشم مویی مات گلدن رز مدل Flash Liner رنگ مشکی شماره 112</v>
+      </c>
+      <c r="D2827" t="str">
+        <v>82230322</v>
+      </c>
+      <c r="E2827" t="str">
+        <v>00221892</v>
+      </c>
+      <c r="F2827">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="B2828" t="str">
+        <v>ریمل گلدن رز مدل Flash رنگ شکلاتی شماره 11</v>
+      </c>
+      <c r="D2828" t="str">
+        <v>82230241</v>
+      </c>
+      <c r="E2828" t="str">
+        <v>00221893</v>
+      </c>
+      <c r="F2828">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="B2829" t="str">
+        <v>رژ لب مایع براق گلدن رز مدل GLEAMY MOOD شماره 201</v>
+      </c>
+      <c r="D2829" t="str">
+        <v>82077044</v>
+      </c>
+      <c r="E2829" t="str">
+        <v>00221894</v>
+      </c>
+      <c r="F2829">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="B2830" t="str">
+        <v>رژ لب مایع براق گلدن رز مدل GLEAMY MOOD شماره 202</v>
+      </c>
+      <c r="D2830" t="str">
+        <v>82077055</v>
+      </c>
+      <c r="E2830" t="str">
+        <v>00221895</v>
+      </c>
+      <c r="F2830">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="B2831" t="str">
+        <v>رژ لب مایع براق گلدن رز مدل GLEAMY MOOD شماره 203</v>
+      </c>
+      <c r="D2831" t="str">
+        <v>82077079</v>
+      </c>
+      <c r="E2831" t="str">
+        <v>00221896</v>
+      </c>
+      <c r="F2831">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="B2832" t="str">
+        <v>رژ لب مایع براق گلدن رز مدل GLEAMY MOOD شماره 204</v>
+      </c>
+      <c r="D2832" t="str">
+        <v>82077100</v>
+      </c>
+      <c r="E2832" t="str">
+        <v>00221897</v>
+      </c>
+      <c r="F2832">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="B2833" t="str">
+        <v>رژ لب مایع براق گلدن رز مدل GLEAMY MOOD شماره 205</v>
+      </c>
+      <c r="D2833" t="str">
+        <v>82077110</v>
+      </c>
+      <c r="E2833" t="str">
+        <v>00221898</v>
+      </c>
+      <c r="F2833">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="B2834" t="str">
+        <v>رژ لب مایع براق گلدن رز مدل GLEAMY MOOD شماره 206</v>
+      </c>
+      <c r="D2834" t="str">
+        <v>82077021</v>
+      </c>
+      <c r="E2834" t="str">
+        <v>00221899</v>
+      </c>
+      <c r="F2834">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="B2835" t="str">
+        <v>هایلایتر مایع گلدن رز مدل SMART GLOW رنگ صدفی شماره 201</v>
+      </c>
+      <c r="D2835" t="str">
+        <v>82076876</v>
+      </c>
+      <c r="E2835" t="str">
+        <v>00221900</v>
+      </c>
+      <c r="F2835">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="B2836" t="str">
+        <v>هایلایتر مایع گلدن رز مدل SMART GLOW رنگ طلایی شماره 202</v>
+      </c>
+      <c r="D2836" t="str">
+        <v>82076852</v>
+      </c>
+      <c r="E2836" t="str">
+        <v>00221901</v>
+      </c>
+      <c r="F2836">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="B2837" t="str">
+        <v>هایلایتر مایع گلدن رز مدل SMART GLOW رنگ رزگلد شماره 203</v>
+      </c>
+      <c r="D2837" t="str">
+        <v>82076863</v>
+      </c>
+      <c r="E2837" t="str">
+        <v>00221902</v>
+      </c>
+      <c r="F2837">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="B2838" t="str">
+        <v>هایلایتر مایع گلدن رز مدل SMART GLOW رنگ برنزی شماره 204</v>
+      </c>
+      <c r="D2838" t="str">
+        <v>82076825</v>
+      </c>
+      <c r="E2838" t="str">
+        <v>00221903</v>
+      </c>
+      <c r="F2838">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="B2839" t="str">
+        <v>مداد داخل  چشم پیچی گلدن رز مدل MATIC رنگ قهوه ای تیره شماره 202</v>
+      </c>
+      <c r="D2839" t="str">
+        <v>82076759</v>
+      </c>
+      <c r="E2839" t="str">
+        <v>00221905</v>
+      </c>
+      <c r="F2839">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="B2840" t="str">
+        <v>مداد داخل  چشم پیچی گلدن رز مدل MATIC رنگ بنفش  شماره 204</v>
+      </c>
+      <c r="D2840" t="str">
+        <v>82076722</v>
+      </c>
+      <c r="E2840" t="str">
+        <v>00221907</v>
+      </c>
+      <c r="F2840">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="B2841" t="str">
+        <v>مداد داخل چشم پیچی گلدن رز مدل MATIC رنگ آبی متوسط شماره 205</v>
+      </c>
+      <c r="D2841" t="str">
+        <v>82076699</v>
+      </c>
+      <c r="E2841" t="str">
+        <v>00221908</v>
+      </c>
+      <c r="F2841">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="B2842" t="str">
+        <v>مداد داخل  چشم پیچی گلدن رز مدل MATIC رنگ زرشکی شماره 206</v>
+      </c>
+      <c r="D2842" t="str">
+        <v>82076683</v>
+      </c>
+      <c r="E2842" t="str">
+        <v>00221909</v>
+      </c>
+      <c r="F2842">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2746"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2842"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2842"/>
+  <dimension ref="A1:G2885"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -879,7 +879,7 @@
         <v>00207178</v>
       </c>
       <c r="F24">
-        <v>2800000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="25">
@@ -899,7 +899,7 @@
         <v>00207179</v>
       </c>
       <c r="F25">
-        <v>2800000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="26">
@@ -919,7 +919,7 @@
         <v>00207180</v>
       </c>
       <c r="F26">
-        <v>2800000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="27">
@@ -939,7 +939,7 @@
         <v>00207181</v>
       </c>
       <c r="F27">
-        <v>2800000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="28">
@@ -979,7 +979,7 @@
         <v>00223070</v>
       </c>
       <c r="F29">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G29">
         <v>187000</v>
@@ -1042,7 +1042,7 @@
         <v>00223071</v>
       </c>
       <c r="F32">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G32">
         <v>187000</v>
@@ -1645,7 +1645,7 @@
         <v>00221658</v>
       </c>
       <c r="F62">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63">
@@ -1725,7 +1725,7 @@
         <v>00221662</v>
       </c>
       <c r="F66">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="67">
@@ -1765,7 +1765,7 @@
         <v>00221664</v>
       </c>
       <c r="F68">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="69">
@@ -2699,7 +2699,7 @@
         <v>00221592</v>
       </c>
       <c r="F115">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="116">
@@ -2759,7 +2759,7 @@
         <v>00221595</v>
       </c>
       <c r="F118">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="119">
@@ -3180,7 +3180,7 @@
         <v>00221614</v>
       </c>
       <c r="F138">
-        <v>5148000</v>
+        <v>482</v>
       </c>
     </row>
     <row r="139">
@@ -3280,7 +3280,7 @@
         <v>00221619</v>
       </c>
       <c r="F143">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="144">
@@ -4023,7 +4023,7 @@
         <v>00223046</v>
       </c>
       <c r="F180">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G180">
         <v>187000</v>
@@ -4046,7 +4046,7 @@
         <v>00223047</v>
       </c>
       <c r="F181">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G181">
         <v>187000</v>
@@ -4092,7 +4092,7 @@
         <v>00223049</v>
       </c>
       <c r="F183">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G183">
         <v>187000</v>
@@ -4115,7 +4115,7 @@
         <v>00223050</v>
       </c>
       <c r="F184">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G184">
         <v>187000</v>
@@ -4138,7 +4138,7 @@
         <v>00223051</v>
       </c>
       <c r="F185">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G185">
         <v>187000</v>
@@ -4207,7 +4207,7 @@
         <v>00223066</v>
       </c>
       <c r="F188">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G188">
         <v>187000</v>
@@ -4230,7 +4230,7 @@
         <v>00223054</v>
       </c>
       <c r="F189">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G189">
         <v>187000</v>
@@ -4253,7 +4253,7 @@
         <v>00223069</v>
       </c>
       <c r="F190">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G190">
         <v>187000</v>
@@ -4276,7 +4276,7 @@
         <v>00223055</v>
       </c>
       <c r="F191">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G191">
         <v>187000</v>
@@ -4299,7 +4299,7 @@
         <v>00223056</v>
       </c>
       <c r="F192">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G192">
         <v>187000</v>
@@ -4322,7 +4322,7 @@
         <v>00223028</v>
       </c>
       <c r="F193">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G193">
         <v>187000</v>
@@ -4391,7 +4391,7 @@
         <v>00223059</v>
       </c>
       <c r="F196">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G196">
         <v>187000</v>
@@ -4414,7 +4414,7 @@
         <v>00223060</v>
       </c>
       <c r="F197">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G197">
         <v>187000</v>
@@ -4460,7 +4460,7 @@
         <v>00223062</v>
       </c>
       <c r="F199">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G199">
         <v>187000</v>
@@ -4483,7 +4483,7 @@
         <v>00223063</v>
       </c>
       <c r="F200">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G200">
         <v>187000</v>
@@ -4506,7 +4506,7 @@
         <v>00223067</v>
       </c>
       <c r="F201">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G201">
         <v>187000</v>
@@ -4529,7 +4529,7 @@
         <v>00223064</v>
       </c>
       <c r="F202">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G202">
         <v>187000</v>
@@ -4953,7 +4953,7 @@
         <v>00223030</v>
       </c>
       <c r="F222">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G222">
         <v>187000</v>
@@ -4999,7 +4999,7 @@
         <v>00223017</v>
       </c>
       <c r="F224">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G224">
         <v>187000</v>
@@ -5022,7 +5022,7 @@
         <v>00223025</v>
       </c>
       <c r="F225">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G225">
         <v>187000</v>
@@ -5045,7 +5045,7 @@
         <v>00223018</v>
       </c>
       <c r="F226">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G226">
         <v>187000</v>
@@ -5068,7 +5068,7 @@
         <v>00223013</v>
       </c>
       <c r="F227">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G227">
         <v>187000</v>
@@ -5091,7 +5091,7 @@
         <v>00223002</v>
       </c>
       <c r="F228">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G228">
         <v>187000</v>
@@ -5114,7 +5114,7 @@
         <v>00223019</v>
       </c>
       <c r="F229">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G229">
         <v>187000</v>
@@ -5137,7 +5137,7 @@
         <v>00223006</v>
       </c>
       <c r="F230">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G230">
         <v>187000</v>
@@ -5160,7 +5160,7 @@
         <v>00223022</v>
       </c>
       <c r="F231">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G231">
         <v>187000</v>
@@ -5183,7 +5183,7 @@
         <v>00223014</v>
       </c>
       <c r="F232">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G232">
         <v>187000</v>
@@ -5206,7 +5206,7 @@
         <v>00223007</v>
       </c>
       <c r="F233">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G233">
         <v>187000</v>
@@ -5229,7 +5229,7 @@
         <v>00223020</v>
       </c>
       <c r="F234">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G234">
         <v>187000</v>
@@ -5252,7 +5252,7 @@
         <v>00223032</v>
       </c>
       <c r="F235">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G235">
         <v>187000</v>
@@ -5275,7 +5275,7 @@
         <v>00223021</v>
       </c>
       <c r="F236">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G236">
         <v>187000</v>
@@ -5321,7 +5321,7 @@
         <v>00223037</v>
       </c>
       <c r="F238">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G238">
         <v>187000</v>
@@ -5344,7 +5344,7 @@
         <v>00223038</v>
       </c>
       <c r="F239">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G239">
         <v>187000</v>
@@ -5367,7 +5367,7 @@
         <v>00223031</v>
       </c>
       <c r="F240">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G240">
         <v>187000</v>
@@ -5413,7 +5413,7 @@
         <v>00223001</v>
       </c>
       <c r="F242">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G242">
         <v>187000</v>
@@ -5436,7 +5436,7 @@
         <v>00223024</v>
       </c>
       <c r="F243">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G243">
         <v>187000</v>
@@ -5459,7 +5459,7 @@
         <v>00223040</v>
       </c>
       <c r="F244">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G244">
         <v>187000</v>
@@ -5482,7 +5482,7 @@
         <v>00223068</v>
       </c>
       <c r="F245">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G245">
         <v>187000</v>
@@ -5505,7 +5505,7 @@
         <v>00223033</v>
       </c>
       <c r="F246">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G246">
         <v>187000</v>
@@ -5528,7 +5528,7 @@
         <v>00223027</v>
       </c>
       <c r="F247">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G247">
         <v>187000</v>
@@ -5551,7 +5551,7 @@
         <v>00223010</v>
       </c>
       <c r="F248">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G248">
         <v>187000</v>
@@ -5574,7 +5574,7 @@
         <v>00223012</v>
       </c>
       <c r="F249">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G249">
         <v>187000</v>
@@ -5597,7 +5597,7 @@
         <v>00223028</v>
       </c>
       <c r="F250">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G250">
         <v>187000</v>
@@ -5620,7 +5620,7 @@
         <v>00223041</v>
       </c>
       <c r="F251">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G251">
         <v>187000</v>
@@ -5643,7 +5643,7 @@
         <v>00223008</v>
       </c>
       <c r="F252">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G252">
         <v>187000</v>
@@ -5666,7 +5666,7 @@
         <v>00223016</v>
       </c>
       <c r="F253">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G253">
         <v>187000</v>
@@ -5689,7 +5689,7 @@
         <v>00223003</v>
       </c>
       <c r="F254">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G254">
         <v>187000</v>
@@ -5758,7 +5758,7 @@
         <v>00223029</v>
       </c>
       <c r="F257">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G257">
         <v>187000</v>
@@ -5781,7 +5781,7 @@
         <v>00223004</v>
       </c>
       <c r="F258">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G258">
         <v>187000</v>
@@ -5804,7 +5804,7 @@
         <v>00223042</v>
       </c>
       <c r="F259">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G259">
         <v>187000</v>
@@ -5827,7 +5827,7 @@
         <v>00223043</v>
       </c>
       <c r="F260">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G260">
         <v>187000</v>
@@ -5850,7 +5850,7 @@
         <v>00223027</v>
       </c>
       <c r="F261">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G261">
         <v>187000</v>
@@ -5873,7 +5873,7 @@
         <v>00223044</v>
       </c>
       <c r="F262">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G262">
         <v>187000</v>
@@ -5896,7 +5896,7 @@
         <v>00223005</v>
       </c>
       <c r="F263">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G263">
         <v>187000</v>
@@ -5919,7 +5919,7 @@
         <v>00223072</v>
       </c>
       <c r="F264">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G264">
         <v>187000</v>
@@ -5942,7 +5942,7 @@
         <v>00223073</v>
       </c>
       <c r="F265">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G265">
         <v>187000</v>
@@ -5988,7 +5988,7 @@
         <v>00223034</v>
       </c>
       <c r="F267">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G267">
         <v>187000</v>
@@ -6192,7 +6192,7 @@
         <v>00221517</v>
       </c>
       <c r="F276">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="277">
@@ -6212,7 +6212,7 @@
         <v>00221516</v>
       </c>
       <c r="F277">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="278">
@@ -6232,7 +6232,7 @@
         <v>00221519</v>
       </c>
       <c r="F278">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="279">
@@ -6252,7 +6252,7 @@
         <v>00221518</v>
       </c>
       <c r="F279">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="280">
@@ -6312,7 +6312,7 @@
         <v>00223009</v>
       </c>
       <c r="F282">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G282">
         <v>187000</v>
@@ -6335,7 +6335,7 @@
         <v>00223026</v>
       </c>
       <c r="F283">
-        <v>187000</v>
+        <v>170000</v>
       </c>
       <c r="G283">
         <v>187000</v>
@@ -6712,7 +6712,7 @@
         <v>00221509</v>
       </c>
       <c r="F302">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="303">
@@ -6732,7 +6732,7 @@
         <v>00221506</v>
       </c>
       <c r="F303">
-        <v>2222000</v>
+        <v>299</v>
       </c>
     </row>
     <row r="304">
@@ -6892,7 +6892,7 @@
         <v>00221501</v>
       </c>
       <c r="F311">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="312">
@@ -7932,7 +7932,7 @@
         <v>00221172</v>
       </c>
       <c r="F363">
-        <v>1133000</v>
+        <v>65</v>
       </c>
     </row>
     <row r="364">
@@ -8875,7 +8875,7 @@
         <v>00221540</v>
       </c>
       <c r="F410">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="411">
@@ -9915,7 +9915,7 @@
         <v>00221414</v>
       </c>
       <c r="F462">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="463">
@@ -9935,7 +9935,7 @@
         <v>00221413</v>
       </c>
       <c r="F463">
-        <v>4950000</v>
+        <v>407</v>
       </c>
     </row>
     <row r="464">
@@ -12148,7 +12148,7 @@
         <v>00221259</v>
       </c>
       <c r="F578">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="579">
@@ -12508,7 +12508,7 @@
         <v>00221403</v>
       </c>
       <c r="F596">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="597">
@@ -12588,7 +12588,7 @@
         <v>00221248</v>
       </c>
       <c r="F600">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="601">
@@ -12948,7 +12948,7 @@
         <v>00221309</v>
       </c>
       <c r="F618">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="619">
@@ -13028,7 +13028,7 @@
         <v>00221015</v>
       </c>
       <c r="F622">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="623">
@@ -13048,7 +13048,7 @@
         <v>00221015</v>
       </c>
       <c r="F623">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="624">
@@ -13308,7 +13308,7 @@
         <v>00221047</v>
       </c>
       <c r="F636">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="637">
@@ -15860,7 +15860,7 @@
         <v>00207002</v>
       </c>
       <c r="F763">
-        <v>1971200</v>
+        <v>830000</v>
       </c>
     </row>
     <row r="764">
@@ -15900,7 +15900,7 @@
         <v>00207003</v>
       </c>
       <c r="F765">
-        <v>1971200</v>
+        <v>830000</v>
       </c>
     </row>
     <row r="766">
@@ -16769,7 +16769,7 @@
         <v>00207011</v>
       </c>
       <c r="F808">
-        <v>4634000</v>
+        <v>3310000</v>
       </c>
     </row>
     <row r="809">
@@ -16789,7 +16789,7 @@
         <v>00207011</v>
       </c>
       <c r="F809">
-        <v>4634000</v>
+        <v>3310000</v>
       </c>
     </row>
     <row r="810">
@@ -19120,7 +19120,7 @@
         <v>00221172</v>
       </c>
       <c r="F932">
-        <v>1133000</v>
+        <v>65</v>
       </c>
     </row>
     <row r="933">
@@ -21322,7 +21322,7 @@
         <v>00221272</v>
       </c>
       <c r="F1049">
-        <v>1144000</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1050">
@@ -21342,7 +21342,7 @@
         <v>00221274</v>
       </c>
       <c r="F1050">
-        <v>1144000</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1051">
@@ -21542,7 +21542,7 @@
         <v>00207011</v>
       </c>
       <c r="F1060">
-        <v>4634000</v>
+        <v>3310000</v>
       </c>
     </row>
     <row r="1061">
@@ -21562,7 +21562,7 @@
         <v>00207011</v>
       </c>
       <c r="F1061">
-        <v>4634000</v>
+        <v>3310000</v>
       </c>
     </row>
     <row r="1062">
@@ -24445,7 +24445,7 @@
         <v>00221072</v>
       </c>
       <c r="F1214">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1215">
@@ -24505,7 +24505,7 @@
         <v>00221073</v>
       </c>
       <c r="F1217">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1218">
@@ -24525,7 +24525,7 @@
         <v>00221072</v>
       </c>
       <c r="F1218">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1219">
@@ -24845,7 +24845,7 @@
         <v>00221239</v>
       </c>
       <c r="F1234">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1235">
@@ -25405,7 +25405,7 @@
         <v>00221200</v>
       </c>
       <c r="F1262">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1263">
@@ -25505,7 +25505,7 @@
         <v>00221200</v>
       </c>
       <c r="F1267">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1268">
@@ -26425,7 +26425,7 @@
         <v>00221044</v>
       </c>
       <c r="F1313">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1314">
@@ -26565,7 +26565,7 @@
         <v>00221313</v>
       </c>
       <c r="F1320">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1321">
@@ -26585,7 +26585,7 @@
         <v>00221313</v>
       </c>
       <c r="F1321">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1322">
@@ -26785,7 +26785,7 @@
         <v>00221303</v>
       </c>
       <c r="F1331">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1332">
@@ -26905,7 +26905,7 @@
         <v>00221370</v>
       </c>
       <c r="F1337">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="1338">
@@ -26925,7 +26925,7 @@
         <v>00221348</v>
       </c>
       <c r="F1338">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1339">
@@ -27265,7 +27265,7 @@
         <v>00221314</v>
       </c>
       <c r="F1355">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1356">
@@ -27305,7 +27305,7 @@
         <v>00221303</v>
       </c>
       <c r="F1357">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1358">
@@ -27325,7 +27325,7 @@
         <v>00221354</v>
       </c>
       <c r="F1358">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1359">
@@ -27405,7 +27405,7 @@
         <v>00221314</v>
       </c>
       <c r="F1362">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1363">
@@ -27585,7 +27585,7 @@
         <v>00221073</v>
       </c>
       <c r="F1371">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1372">
@@ -27725,7 +27725,7 @@
         <v>00221073</v>
       </c>
       <c r="F1378">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1379">
@@ -28461,7 +28461,7 @@
         <v>00221142</v>
       </c>
       <c r="F1413">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1414">
@@ -28541,7 +28541,7 @@
         <v>00221017</v>
       </c>
       <c r="F1417">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1418">
@@ -28581,7 +28581,7 @@
         <v>00221017</v>
       </c>
       <c r="F1419">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1420">
@@ -28641,7 +28641,7 @@
         <v>00221142</v>
       </c>
       <c r="F1422">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1423">
@@ -29795,7 +29795,7 @@
         <v>00221165</v>
       </c>
       <c r="F1474">
-        <v>3586000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1475">
@@ -29975,7 +29975,7 @@
         <v>00221325</v>
       </c>
       <c r="F1483">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1484">
@@ -30255,7 +30255,7 @@
         <v>00221140</v>
       </c>
       <c r="F1497">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1498">
@@ -30275,7 +30275,7 @@
         <v>00221143</v>
       </c>
       <c r="F1498">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1499">
@@ -31489,7 +31489,7 @@
         <v>00221305</v>
       </c>
       <c r="F1556">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1557">
@@ -31529,7 +31529,7 @@
         <v>00221003</v>
       </c>
       <c r="F1558">
-        <v>2431000</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1559">
@@ -31629,7 +31629,7 @@
         <v>00221003</v>
       </c>
       <c r="F1563">
-        <v>2431000</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1564">
@@ -32252,7 +32252,7 @@
         <v>00221305</v>
       </c>
       <c r="F1594">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1595">
@@ -32452,7 +32452,7 @@
         <v>00221015</v>
       </c>
       <c r="F1604">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1605">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="1619">
@@ -36296,7 +36296,7 @@
         <v>00221687</v>
       </c>
       <c r="F1810">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1811">
@@ -36381,7 +36381,7 @@
         <v>00221692</v>
       </c>
       <c r="F1815">
-        <v>247</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1816">
@@ -36568,7 +36568,7 @@
         <v>00221248</v>
       </c>
       <c r="F1826">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1827">
@@ -36636,7 +36636,7 @@
         <v>00221248</v>
       </c>
       <c r="F1830">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1831">
@@ -39133,7 +39133,7 @@
         <v>00221259</v>
       </c>
       <c r="F1961">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1962">
@@ -39150,7 +39150,7 @@
         <v>00221272</v>
       </c>
       <c r="F1962">
-        <v>1144000</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1963">
@@ -39524,7 +39524,7 @@
         <v>00221619</v>
       </c>
       <c r="F1984">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="1985">
@@ -39609,7 +39609,7 @@
         <v>00221709</v>
       </c>
       <c r="F1989">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1990">
@@ -39932,7 +39932,7 @@
         <v>00221736</v>
       </c>
       <c r="F2008">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2009">
@@ -40068,7 +40068,7 @@
         <v>00221744</v>
       </c>
       <c r="F2016">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2017">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2430">
@@ -46451,7 +46451,7 @@
         <v>00221003</v>
       </c>
       <c r="F2431">
-        <v>2431000</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2432">
@@ -46535,7 +46535,7 @@
         <v>00221142</v>
       </c>
       <c r="F2437">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2438">
@@ -46563,7 +46563,7 @@
         <v>00221248</v>
       </c>
       <c r="F2439">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2440">
@@ -46591,7 +46591,7 @@
         <v>00221314</v>
       </c>
       <c r="F2441">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2442">
@@ -46997,7 +46997,7 @@
         <v>00221348</v>
       </c>
       <c r="F2470">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2471">
@@ -47263,7 +47263,7 @@
         <v>00221015</v>
       </c>
       <c r="F2489">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2490">
@@ -47543,7 +47543,7 @@
         <v>00221736</v>
       </c>
       <c r="F2509">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2510">
@@ -47750,7 +47750,7 @@
         <v>00221072</v>
       </c>
       <c r="F2524">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2525">
@@ -47764,7 +47764,7 @@
         <v>00221073</v>
       </c>
       <c r="F2525">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2526">
@@ -48044,7 +48044,7 @@
         <v>00221248</v>
       </c>
       <c r="F2545">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2546">
@@ -48086,7 +48086,7 @@
         <v>00221714</v>
       </c>
       <c r="F2548">
-        <v>2695000</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2549">
@@ -48100,7 +48100,7 @@
         <v>00221715</v>
       </c>
       <c r="F2549">
-        <v>2695000</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2550">
@@ -48198,7 +48198,7 @@
         <v>00221501</v>
       </c>
       <c r="F2556">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2557">
@@ -48394,7 +48394,7 @@
         <v>00221403</v>
       </c>
       <c r="F2570">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2571">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2618">
@@ -49133,7 +49133,7 @@
         <v>00221354</v>
       </c>
       <c r="F2623">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2624">
@@ -49245,7 +49245,7 @@
         <v>00221763</v>
       </c>
       <c r="F2631">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2632">
@@ -49399,7 +49399,7 @@
         <v>00221777</v>
       </c>
       <c r="F2642">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2643">
@@ -49539,7 +49539,7 @@
         <v>00221791</v>
       </c>
       <c r="F2652">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2653">
@@ -49609,7 +49609,7 @@
         <v>00221796</v>
       </c>
       <c r="F2657">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2658">
@@ -50059,7 +50059,7 @@
         <v>00221796</v>
       </c>
       <c r="F2690">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2691">
@@ -50493,7 +50493,7 @@
         <v>00221822</v>
       </c>
       <c r="F2721">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2722">
@@ -50507,7 +50507,7 @@
         <v>00221823</v>
       </c>
       <c r="F2722">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2723">
@@ -52187,9 +52187,611 @@
         <v>199</v>
       </c>
     </row>
+    <row r="2843">
+      <c r="B2843" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 02 رنگ سفید</v>
+      </c>
+      <c r="D2843" t="str">
+        <v>82752692</v>
+      </c>
+      <c r="E2843" t="str">
+        <v>00231002</v>
+      </c>
+      <c r="F2843">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="B2844" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 17</v>
+      </c>
+      <c r="D2844" t="str">
+        <v>81948371</v>
+      </c>
+      <c r="E2844" t="str">
+        <v>00231013</v>
+      </c>
+      <c r="F2844">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="B2845" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 19 رنگ صورتی فوشیا</v>
+      </c>
+      <c r="D2845" t="str">
+        <v>82752209</v>
+      </c>
+      <c r="E2845" t="str">
+        <v>00231015</v>
+      </c>
+      <c r="F2845">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="B2846" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 21</v>
+      </c>
+      <c r="D2846" t="str">
+        <v>81957216</v>
+      </c>
+      <c r="E2846" t="str">
+        <v>00231017</v>
+      </c>
+      <c r="F2846">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="B2847" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 22</v>
+      </c>
+      <c r="D2847" t="str">
+        <v>81956215</v>
+      </c>
+      <c r="E2847" t="str">
+        <v>00231018</v>
+      </c>
+      <c r="F2847">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="B2848" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 22</v>
+      </c>
+      <c r="D2848" t="str">
+        <v>81947941</v>
+      </c>
+      <c r="E2848" t="str">
+        <v>00231018</v>
+      </c>
+      <c r="F2848">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="B2849" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 72</v>
+      </c>
+      <c r="D2849" t="str">
+        <v>81956485</v>
+      </c>
+      <c r="E2849" t="str">
+        <v>00231059</v>
+      </c>
+      <c r="F2849">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="B2850" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 72</v>
+      </c>
+      <c r="D2850" t="str">
+        <v>81953376</v>
+      </c>
+      <c r="E2850" t="str">
+        <v>00231059</v>
+      </c>
+      <c r="F2850">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="B2851" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 74</v>
+      </c>
+      <c r="D2851" t="str">
+        <v>81953217</v>
+      </c>
+      <c r="E2851" t="str">
+        <v>00231060</v>
+      </c>
+      <c r="F2851">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="B2852" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 75</v>
+      </c>
+      <c r="D2852" t="str">
+        <v>81953029</v>
+      </c>
+      <c r="E2852" t="str">
+        <v>00231061</v>
+      </c>
+      <c r="F2852">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="B2853" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 77 رنگ قرمز</v>
+      </c>
+      <c r="D2853" t="str">
+        <v>82752791</v>
+      </c>
+      <c r="E2853" t="str">
+        <v>00231062</v>
+      </c>
+      <c r="F2853">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="B2854" t="str">
+        <v>لاک ناخن گلدن رز مدل Color Expert 144</v>
+      </c>
+      <c r="D2854" t="str">
+        <v>81952938</v>
+      </c>
+      <c r="E2854" t="str">
+        <v>00231102</v>
+      </c>
+      <c r="F2854">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="B2855" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 76</v>
+      </c>
+      <c r="D2855" t="str">
+        <v>81957541</v>
+      </c>
+      <c r="E2855" t="str">
+        <v>00231104</v>
+      </c>
+      <c r="F2855">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="B2856" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 127</v>
+      </c>
+      <c r="D2856" t="str">
+        <v>81957437</v>
+      </c>
+      <c r="E2856" t="str">
+        <v>00231106</v>
+      </c>
+      <c r="F2856">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="B2857" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 126</v>
+      </c>
+      <c r="D2857" t="str">
+        <v>81957083</v>
+      </c>
+      <c r="E2857" t="str">
+        <v>00231109</v>
+      </c>
+      <c r="F2857">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="B2858" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 140 رنگ قرمز کلاسیک</v>
+      </c>
+      <c r="D2858" t="str">
+        <v>82753197</v>
+      </c>
+      <c r="E2858" t="str">
+        <v>00231121</v>
+      </c>
+      <c r="F2858">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="B2859" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 158 رنگ یاسی روشن</v>
+      </c>
+      <c r="D2859" t="str">
+        <v>82753249</v>
+      </c>
+      <c r="E2859" t="str">
+        <v>00231122</v>
+      </c>
+      <c r="F2859">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="B2860" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 161 رنگ آبی نفتی</v>
+      </c>
+      <c r="D2860" t="str">
+        <v>82753150</v>
+      </c>
+      <c r="E2860" t="str">
+        <v>00231123</v>
+      </c>
+      <c r="F2860">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="B2861" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 171 رنگ قهوه ای موکا</v>
+      </c>
+      <c r="D2861" t="str">
+        <v>82753306</v>
+      </c>
+      <c r="E2861" t="str">
+        <v>00231125</v>
+      </c>
+      <c r="F2861">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="B2862" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 402 رنگ رزگلد اکلیلی</v>
+      </c>
+      <c r="D2862" t="str">
+        <v>82752592</v>
+      </c>
+      <c r="E2862" t="str">
+        <v>00231126</v>
+      </c>
+      <c r="F2862">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="B2863" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 404 رنگ هلویی نود</v>
+      </c>
+      <c r="D2863" t="str">
+        <v>82752561</v>
+      </c>
+      <c r="E2863" t="str">
+        <v>00231127</v>
+      </c>
+      <c r="F2863">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="B2864" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 410 رنگ نقره ای هولوگرامی</v>
+      </c>
+      <c r="D2864" t="str">
+        <v>82752624</v>
+      </c>
+      <c r="E2864" t="str">
+        <v>00231130</v>
+      </c>
+      <c r="F2864">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="B2865" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 604 رنگ طلایی اکلیلی</v>
+      </c>
+      <c r="D2865" t="str">
+        <v>82752875</v>
+      </c>
+      <c r="E2865" t="str">
+        <v>00231133</v>
+      </c>
+      <c r="F2865">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="B2866" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 610 رنگ اکلیلی سبز</v>
+      </c>
+      <c r="D2866" t="str">
+        <v>82752851</v>
+      </c>
+      <c r="E2866" t="str">
+        <v>00231135</v>
+      </c>
+      <c r="F2866">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="B2867" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 611 رنگ اکلیلی بنفش</v>
+      </c>
+      <c r="D2867" t="str">
+        <v>82752819</v>
+      </c>
+      <c r="E2867" t="str">
+        <v>00231136</v>
+      </c>
+      <c r="F2867">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="B2868" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 614 رنگ سرمه ای اکلیلی</v>
+      </c>
+      <c r="D2868" t="str">
+        <v>82752645</v>
+      </c>
+      <c r="E2868" t="str">
+        <v>00231137</v>
+      </c>
+      <c r="F2868">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="B2869" t="str">
+        <v>رژ لب مایع گلدن رز مدل رول آن رنگ لیمویی شماره 03 حجم 3.4 میلی لیتر</v>
+      </c>
+      <c r="D2869" t="str">
+        <v>82732672</v>
+      </c>
+      <c r="E2869" t="str">
+        <v>00221103</v>
+      </c>
+      <c r="F2869">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="B2870" t="str">
+        <v>برق لب مایع گلدن رز مدل رول آن رنگ پرتقالی شماره 04 حجم 3.4 میلی لیتر</v>
+      </c>
+      <c r="D2870" t="str">
+        <v>82732633</v>
+      </c>
+      <c r="E2870" t="str">
+        <v>00221104</v>
+      </c>
+      <c r="F2870">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="B2871" t="str">
+        <v>برق لب مایع گلدن رز مدل رول آن شماره 05 حجم 3.4 میلی لیتر</v>
+      </c>
+      <c r="D2871" t="str">
+        <v>82731785</v>
+      </c>
+      <c r="E2871" t="str">
+        <v>00221105</v>
+      </c>
+      <c r="F2871">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="B2872" t="str">
+        <v>مداد لب گلدن رز مدل DREAM شماره 503</v>
+      </c>
+      <c r="D2872" t="str">
+        <v>81991958</v>
+      </c>
+      <c r="E2872" t="str">
+        <v>00221540</v>
+      </c>
+      <c r="F2872">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="B2873" t="str">
+        <v>رژلب مایع گلدن رز مدل Long Lasting به همراه مداد لب گلدن رز مدل Dream</v>
+      </c>
+      <c r="D2873" t="str">
+        <v>81946690</v>
+      </c>
+      <c r="E2873" t="str">
+        <v>00221871</v>
+      </c>
+      <c r="F2873">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="B2874" t="str">
+        <v>رژلب مایع گلدن رز مدل Long Lasting شماره 18 به همراه مداد لب گلدن رز مدل Dream شماره 527</v>
+      </c>
+      <c r="D2874" t="str">
+        <v>81946635</v>
+      </c>
+      <c r="E2874" t="str">
+        <v>00221872</v>
+      </c>
+      <c r="F2874">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="B2875" t="str">
+        <v>رژلب مایع گلدن رز مدل Long Lasting شماره 16 به همراه مداد لب گلدن رز مدل Dream شماره 531</v>
+      </c>
+      <c r="D2875" t="str">
+        <v>81946535</v>
+      </c>
+      <c r="E2875" t="str">
+        <v>00221873</v>
+      </c>
+      <c r="F2875">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="B2876" t="str">
+        <v>ریمل جداکننده گلدن رز مدل فلش لش رنگ برگندی شماره 10</v>
+      </c>
+      <c r="D2876" t="str">
+        <v>82732793</v>
+      </c>
+      <c r="E2876" t="str">
+        <v>00221880</v>
+      </c>
+      <c r="F2876">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="B2877" t="str">
+        <v>ریمل جدا کننده گلدن رز مدل فلش لش رنگ قهوه ای شماره 11</v>
+      </c>
+      <c r="D2877" t="str">
+        <v>82732765</v>
+      </c>
+      <c r="E2877" t="str">
+        <v>00221893</v>
+      </c>
+      <c r="F2877">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="B2878" t="str">
+        <v>مداد داخل چشم پیچی گلدن رز مدل MATIC رنگ قهوه ای متوسط شماره 203</v>
+      </c>
+      <c r="D2878" t="str">
+        <v>82076740</v>
+      </c>
+      <c r="E2878" t="str">
+        <v>00221906</v>
+      </c>
+      <c r="F2878">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="B2879" t="str">
+        <v>ریمل جدا کننده گلدن رز مدل فلش لش رنگ کورال رز شماره 06</v>
+      </c>
+      <c r="D2879" t="str">
+        <v>82732848</v>
+      </c>
+      <c r="E2879" t="str">
+        <v>00221915</v>
+      </c>
+      <c r="F2879">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="B2880" t="str">
+        <v>رژ لب مایع براق گلدن رز مدل Cotton Dry شماره 01 رنگ صورتی</v>
+      </c>
+      <c r="D2880" t="str">
+        <v>82732709</v>
+      </c>
+      <c r="E2880" t="str">
+        <v>00221917</v>
+      </c>
+      <c r="F2880">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="B2881" t="str">
+        <v>پودر تثبیت کننده آرایش فلورمار مدل Invisible</v>
+      </c>
+      <c r="D2881" t="str">
+        <v>82246296</v>
+      </c>
+      <c r="E2881" t="str">
+        <v>00207011</v>
+      </c>
+      <c r="F2881">
+        <v>3310000</v>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="B2882" t="str">
+        <v>پودر تثبیت کننده آرایش فلورمار شماره 3</v>
+      </c>
+      <c r="D2882" t="str">
+        <v>82246236</v>
+      </c>
+      <c r="E2882" t="str">
+        <v>00207014</v>
+      </c>
+      <c r="F2882">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="B2883" t="str">
+        <v>پودر تثبیت کننده آرایش فلورمار شماره 4</v>
+      </c>
+      <c r="D2883" t="str">
+        <v>82246461</v>
+      </c>
+      <c r="E2883" t="str">
+        <v>00207202</v>
+      </c>
+      <c r="F2883">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="B2884" t="str">
+        <v>پودر تثبیت کننده آرایش فلورمار شماره 4</v>
+      </c>
+      <c r="D2884" t="str">
+        <v>82246180</v>
+      </c>
+      <c r="E2884" t="str">
+        <v>00207202</v>
+      </c>
+      <c r="F2884">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="B2885" t="str">
+        <v>لاک ناخن جوردانا مدل NP شماره 936</v>
+      </c>
+      <c r="D2885" t="str">
+        <v>44076432</v>
+      </c>
+      <c r="E2885" t="str">
+        <v>00223015</v>
+      </c>
+      <c r="F2885">
+        <v>170000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2842"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2885"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2885"/>
+  <dimension ref="A1:G2938"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -499,7 +499,7 @@
         <v>00221673</v>
       </c>
       <c r="F5">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -579,7 +579,7 @@
         <v>00221669</v>
       </c>
       <c r="F9">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -1985,7 +1985,7 @@
         <v>00221586</v>
       </c>
       <c r="F79">
-        <v>2134000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="80">
@@ -2185,7 +2185,7 @@
         <v>00221599</v>
       </c>
       <c r="F89">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="90">
@@ -2305,7 +2305,7 @@
         <v>00221432</v>
       </c>
       <c r="F95">
-        <v>1251000</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96">
@@ -2445,7 +2445,7 @@
         <v>00221599</v>
       </c>
       <c r="F102">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="103">
@@ -2465,7 +2465,7 @@
         <v>00221459</v>
       </c>
       <c r="F103">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="104">
@@ -2559,7 +2559,7 @@
         <v>00221608</v>
       </c>
       <c r="F108">
-        <v>1520000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -2719,7 +2719,7 @@
         <v>00221593</v>
       </c>
       <c r="F116">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117">
@@ -4907,7 +4907,7 @@
         <v>00216004</v>
       </c>
       <c r="F220">
-        <v>1470000</v>
+        <v>1800000</v>
       </c>
       <c r="G220">
         <v>1100300</v>
@@ -7652,7 +7652,7 @@
         <v>00221468</v>
       </c>
       <c r="F349">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="350">
@@ -7912,7 +7912,7 @@
         <v>00221459</v>
       </c>
       <c r="F362">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="363">
@@ -8152,7 +8152,7 @@
         <v>00221447</v>
       </c>
       <c r="F374">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="375">
@@ -8535,7 +8535,7 @@
         <v>00221439</v>
       </c>
       <c r="F393">
-        <v>4156100</v>
+        <v>299</v>
       </c>
     </row>
     <row r="394">
@@ -8555,7 +8555,7 @@
         <v>00221439</v>
       </c>
       <c r="F394">
-        <v>4156100</v>
+        <v>299</v>
       </c>
     </row>
     <row r="395">
@@ -8755,7 +8755,7 @@
         <v>00221434</v>
       </c>
       <c r="F404">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="405">
@@ -8775,7 +8775,7 @@
         <v>00221237</v>
       </c>
       <c r="F405">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="406">
@@ -8815,7 +8815,7 @@
         <v>00221432</v>
       </c>
       <c r="F407">
-        <v>1251000</v>
+        <v>84</v>
       </c>
     </row>
     <row r="408">
@@ -9175,7 +9175,7 @@
         <v>00221154</v>
       </c>
       <c r="F425">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="426">
@@ -10015,7 +10015,7 @@
         <v>00221443</v>
       </c>
       <c r="F467">
-        <v>2321000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="468">
@@ -11337,7 +11337,7 @@
         <v>00221277</v>
       </c>
       <c r="F537">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="538">
@@ -12168,7 +12168,7 @@
         <v>00221255</v>
       </c>
       <c r="F579">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="580">
@@ -12228,7 +12228,7 @@
         <v>00221052</v>
       </c>
       <c r="F582">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="583">
@@ -12488,7 +12488,7 @@
         <v>00221089</v>
       </c>
       <c r="F595">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="596">
@@ -12548,7 +12548,7 @@
         <v>00221086</v>
       </c>
       <c r="F598">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="599">
@@ -12568,7 +12568,7 @@
         <v>00221055</v>
       </c>
       <c r="F599">
-        <v>951500</v>
+        <v>80</v>
       </c>
     </row>
     <row r="600">
@@ -12748,7 +12748,7 @@
         <v>00221067</v>
       </c>
       <c r="F608">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="609">
@@ -12868,7 +12868,7 @@
         <v>00221228</v>
       </c>
       <c r="F614">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="615">
@@ -12888,7 +12888,7 @@
         <v>00221228</v>
       </c>
       <c r="F615">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="616">
@@ -13208,7 +13208,7 @@
         <v>00221230</v>
       </c>
       <c r="F631">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="632">
@@ -13228,7 +13228,7 @@
         <v>00221230</v>
       </c>
       <c r="F632">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="633">
@@ -13248,7 +13248,7 @@
         <v>00221218</v>
       </c>
       <c r="F633">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="634">
@@ -13408,7 +13408,7 @@
         <v>00221040</v>
       </c>
       <c r="F641">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="642">
@@ -13508,7 +13508,7 @@
         <v>00221289</v>
       </c>
       <c r="F646">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="647">
@@ -13548,7 +13548,7 @@
         <v>00221409</v>
       </c>
       <c r="F648">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="649">
@@ -13608,7 +13608,7 @@
         <v>00221238</v>
       </c>
       <c r="F651">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="652">
@@ -13768,7 +13768,7 @@
         <v>00221154</v>
       </c>
       <c r="F659">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="660">
@@ -13988,7 +13988,7 @@
         <v>00221311</v>
       </c>
       <c r="F670">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="671">
@@ -15322,7 +15322,7 @@
         <v>00221237</v>
       </c>
       <c r="F734">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="735">
@@ -19020,7 +19020,7 @@
         <v>00221382</v>
       </c>
       <c r="F927">
-        <v>2150500</v>
+        <v>193</v>
       </c>
     </row>
     <row r="928">
@@ -21262,7 +21262,7 @@
         <v>00221222</v>
       </c>
       <c r="F1046">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1047">
@@ -24585,7 +24585,7 @@
         <v>00221081</v>
       </c>
       <c r="F1221">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1222">
@@ -24805,7 +24805,7 @@
         <v>00221043</v>
       </c>
       <c r="F1232">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1233">
@@ -25145,7 +25145,7 @@
         <v>00221177</v>
       </c>
       <c r="F1249">
-        <v>5670000</v>
+        <v>422</v>
       </c>
     </row>
     <row r="1250">
@@ -26045,7 +26045,7 @@
         <v>00221311</v>
       </c>
       <c r="F1294">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1295">
@@ -26065,7 +26065,7 @@
         <v>00221060</v>
       </c>
       <c r="F1295">
-        <v>6127000</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1296">
@@ -26645,7 +26645,7 @@
         <v>00221306</v>
       </c>
       <c r="F1324">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1325">
@@ -26685,7 +26685,7 @@
         <v>00221196</v>
       </c>
       <c r="F1326">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1327">
@@ -26965,7 +26965,7 @@
         <v>00221320</v>
       </c>
       <c r="F1340">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1341">
@@ -26985,7 +26985,7 @@
         <v>00221320</v>
       </c>
       <c r="F1341">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1342">
@@ -27065,7 +27065,7 @@
         <v>00221043</v>
       </c>
       <c r="F1345">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1346">
@@ -27165,7 +27165,7 @@
         <v>00221043</v>
       </c>
       <c r="F1350">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1351">
@@ -27285,7 +27285,7 @@
         <v>00221225</v>
       </c>
       <c r="F1356">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1357">
@@ -27365,7 +27365,7 @@
         <v>00221031</v>
       </c>
       <c r="F1360">
-        <v>1122000</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1361">
@@ -27385,7 +27385,7 @@
         <v>00221031</v>
       </c>
       <c r="F1361">
-        <v>1122000</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1362">
@@ -27505,7 +27505,7 @@
         <v>00221068</v>
       </c>
       <c r="F1367">
-        <v>3861000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1368">
@@ -27525,7 +27525,7 @@
         <v>00221079</v>
       </c>
       <c r="F1368">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1369">
@@ -27665,7 +27665,7 @@
         <v>00221068</v>
       </c>
       <c r="F1375">
-        <v>3861000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1376">
@@ -27745,7 +27745,7 @@
         <v>00221082</v>
       </c>
       <c r="F1379">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1380">
@@ -28421,7 +28421,7 @@
         <v>00221358</v>
       </c>
       <c r="F1411">
-        <v>2151600</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1412">
@@ -29655,7 +29655,7 @@
         <v>00221063</v>
       </c>
       <c r="F1467">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1468">
@@ -29995,7 +29995,7 @@
         <v>00221327</v>
       </c>
       <c r="F1484">
-        <v>3223000</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1485">
@@ -30075,7 +30075,7 @@
         <v>00221323</v>
       </c>
       <c r="F1488">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1489">
@@ -30095,7 +30095,7 @@
         <v>00221323</v>
       </c>
       <c r="F1489">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1490">
@@ -30135,7 +30135,7 @@
         <v>00221324</v>
       </c>
       <c r="F1491">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1492">
@@ -30507,7 +30507,7 @@
         <v>00221063</v>
       </c>
       <c r="F1509">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1510">
@@ -30890,7 +30890,7 @@
         <v>00221059</v>
       </c>
       <c r="F1528">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1529">
@@ -31449,7 +31449,7 @@
         <v>00221055</v>
       </c>
       <c r="F1554">
-        <v>951500</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1555">
@@ -31786,7 +31786,7 @@
         <v>00221055</v>
       </c>
       <c r="F1571">
-        <v>951500</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1572">
@@ -31852,7 +31852,7 @@
         <v>00221059</v>
       </c>
       <c r="F1574">
-        <v>570</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1575">
@@ -32392,7 +32392,7 @@
         <v>00221218</v>
       </c>
       <c r="F1601">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1602">
@@ -32733,7 +32733,7 @@
         <v>00221217</v>
       </c>
       <c r="F1617">
-        <v>392</v>
+        <v>412</v>
       </c>
     </row>
     <row r="1618">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1619">
@@ -36347,7 +36347,7 @@
         <v>00221690</v>
       </c>
       <c r="F1813">
-        <v>1408000</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1814">
@@ -36602,7 +36602,7 @@
         <v>00221052</v>
       </c>
       <c r="F1828">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1829">
@@ -36673,7 +36673,7 @@
         <v>00216024</v>
       </c>
       <c r="F1832">
-        <v>1440000</v>
+        <v>2000000</v>
       </c>
       <c r="G1832">
         <v>1337000</v>
@@ -36753,7 +36753,7 @@
         <v>00216028</v>
       </c>
       <c r="F1836">
-        <v>1440000</v>
+        <v>2000000</v>
       </c>
       <c r="G1836">
         <v>1337000</v>
@@ -36773,7 +36773,7 @@
         <v>00216029</v>
       </c>
       <c r="F1837">
-        <v>1150000</v>
+        <v>2000000</v>
       </c>
       <c r="G1837">
         <v>1337000</v>
@@ -36793,7 +36793,7 @@
         <v>00221052</v>
       </c>
       <c r="F1838">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1839">
@@ -38095,7 +38095,7 @@
         <v>221055</v>
       </c>
       <c r="F1904">
-        <v>951500</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1905">
@@ -38255,7 +38255,7 @@
         <v>221295</v>
       </c>
       <c r="F1912">
-        <v>1269000</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1913">
@@ -39354,7 +39354,7 @@
         <v>00221707</v>
       </c>
       <c r="F1974">
-        <v>1122000</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1975">
@@ -39371,7 +39371,7 @@
         <v>00221707</v>
       </c>
       <c r="F1975">
-        <v>1122000</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1976">
@@ -39490,7 +39490,7 @@
         <v>00221306</v>
       </c>
       <c r="F1982">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1983">
@@ -39541,7 +39541,7 @@
         <v>00221673</v>
       </c>
       <c r="F1985">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1986">
@@ -39728,7 +39728,7 @@
         <v>00221724</v>
       </c>
       <c r="F1996">
-        <v>1890000</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1997">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2430">
@@ -46633,7 +46633,7 @@
         <v>00221230</v>
       </c>
       <c r="F2444">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2445">
@@ -46647,7 +46647,7 @@
         <v>00221238</v>
       </c>
       <c r="F2445">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2446">
@@ -47053,7 +47053,7 @@
         <v>00221447</v>
       </c>
       <c r="F2474">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2475">
@@ -47151,7 +47151,7 @@
         <v>00221228</v>
       </c>
       <c r="F2481">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2482">
@@ -47277,7 +47277,7 @@
         <v>00221052</v>
       </c>
       <c r="F2490">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2491">
@@ -47403,7 +47403,7 @@
         <v>00221443</v>
       </c>
       <c r="F2499">
-        <v>2321000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2500">
@@ -47652,7 +47652,7 @@
         <v>00221063</v>
       </c>
       <c r="F2517">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2518">
@@ -47834,7 +47834,7 @@
         <v>00221079</v>
       </c>
       <c r="F2530">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2531">
@@ -47848,7 +47848,7 @@
         <v>00221079</v>
       </c>
       <c r="F2531">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2532">
@@ -47876,7 +47876,7 @@
         <v>00221082</v>
       </c>
       <c r="F2533">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2534">
@@ -47932,7 +47932,7 @@
         <v>00221086</v>
       </c>
       <c r="F2537">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2538">
@@ -48072,7 +48072,7 @@
         <v>00221323</v>
       </c>
       <c r="F2547">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2548">
@@ -48114,7 +48114,7 @@
         <v>00221717</v>
       </c>
       <c r="F2550">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2551">
@@ -48128,7 +48128,7 @@
         <v>00221746</v>
       </c>
       <c r="F2551">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2552">
@@ -48156,7 +48156,7 @@
         <v>00221081</v>
       </c>
       <c r="F2553">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2554">
@@ -48366,7 +48366,7 @@
         <v>00221068</v>
       </c>
       <c r="F2568">
-        <v>3861000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2569">
@@ -48450,7 +48450,7 @@
         <v>00221755</v>
       </c>
       <c r="F2574">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2575">
@@ -48590,7 +48590,7 @@
         <v>00221289</v>
       </c>
       <c r="F2584">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2585">
@@ -48769,7 +48769,7 @@
         <v>00221067</v>
       </c>
       <c r="F2597">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2598">
@@ -48811,7 +48811,7 @@
         <v>00221409</v>
       </c>
       <c r="F2600">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2601">
@@ -48867,7 +48867,7 @@
         <v>00221089</v>
       </c>
       <c r="F2604">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2605">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2618">
@@ -49077,7 +49077,7 @@
         <v>00221218</v>
       </c>
       <c r="F2619">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2620">
@@ -49091,7 +49091,7 @@
         <v>00221228</v>
       </c>
       <c r="F2620">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2621">
@@ -49385,7 +49385,7 @@
         <v>00221776</v>
       </c>
       <c r="F2641">
-        <v>1</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2642">
@@ -49427,7 +49427,7 @@
         <v>00221781</v>
       </c>
       <c r="F2644">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2645">
@@ -49455,7 +49455,7 @@
         <v>00221785</v>
       </c>
       <c r="F2646">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2647">
@@ -49497,7 +49497,7 @@
         <v>00221788</v>
       </c>
       <c r="F2649">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2650">
@@ -49581,7 +49581,7 @@
         <v>00221794</v>
       </c>
       <c r="F2655">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2656">
@@ -49623,7 +49623,7 @@
         <v>00221797</v>
       </c>
       <c r="F2658">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2659">
@@ -49679,7 +49679,7 @@
         <v>00221801</v>
       </c>
       <c r="F2662">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2663">
@@ -49693,7 +49693,7 @@
         <v>00221802</v>
       </c>
       <c r="F2663">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2664">
@@ -49707,7 +49707,7 @@
         <v>00221803</v>
       </c>
       <c r="F2664">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2665">
@@ -50031,7 +50031,7 @@
         <v>00221794</v>
       </c>
       <c r="F2688">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2689">
@@ -50073,7 +50073,7 @@
         <v>00221797</v>
       </c>
       <c r="F2691">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2692">
@@ -50129,7 +50129,7 @@
         <v>00221801</v>
       </c>
       <c r="F2695">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2696">
@@ -50143,7 +50143,7 @@
         <v>00221802</v>
       </c>
       <c r="F2696">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2697">
@@ -50157,7 +50157,7 @@
         <v>00221803</v>
       </c>
       <c r="F2697">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2698">
@@ -50297,7 +50297,7 @@
         <v>00221817</v>
       </c>
       <c r="F2707">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2708">
@@ -50325,7 +50325,7 @@
         <v>00221819</v>
       </c>
       <c r="F2709">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2710">
@@ -50451,7 +50451,7 @@
         <v>00216055</v>
       </c>
       <c r="F2718">
-        <v>3400000</v>
+        <v>3680000</v>
       </c>
     </row>
     <row r="2719">
@@ -50745,7 +50745,7 @@
         <v>00221842</v>
       </c>
       <c r="F2739">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2740">
@@ -51778,7 +51778,7 @@
         <v>00221711</v>
       </c>
       <c r="F2813">
-        <v>130</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2814">
@@ -52789,9 +52789,751 @@
         <v>170000</v>
       </c>
     </row>
+    <row r="2886">
+      <c r="B2886" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 27</v>
+      </c>
+      <c r="D2886" t="str">
+        <v>81953492</v>
+      </c>
+      <c r="E2886" t="str">
+        <v>00231023</v>
+      </c>
+      <c r="F2886">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="B2887" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 43</v>
+      </c>
+      <c r="D2887" t="str">
+        <v>81993649</v>
+      </c>
+      <c r="E2887" t="str">
+        <v>00231037</v>
+      </c>
+      <c r="F2887">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="B2888" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 43</v>
+      </c>
+      <c r="D2888" t="str">
+        <v>81953172</v>
+      </c>
+      <c r="E2888" t="str">
+        <v>00231037</v>
+      </c>
+      <c r="F2888">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="B2889" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 64</v>
+      </c>
+      <c r="D2889" t="str">
+        <v>81993445</v>
+      </c>
+      <c r="E2889" t="str">
+        <v>00231051</v>
+      </c>
+      <c r="F2889">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="B2890" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 68</v>
+      </c>
+      <c r="D2890" t="str">
+        <v>81992667</v>
+      </c>
+      <c r="E2890" t="str">
+        <v>00231055</v>
+      </c>
+      <c r="F2890">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="B2891" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 68</v>
+      </c>
+      <c r="D2891" t="str">
+        <v>81992596</v>
+      </c>
+      <c r="E2891" t="str">
+        <v>00231055</v>
+      </c>
+      <c r="F2891">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="B2892" t="str">
+        <v>لاک گلدن رز مدل کالر اکسپرت شماره 71</v>
+      </c>
+      <c r="D2892" t="str">
+        <v>81956784</v>
+      </c>
+      <c r="E2892" t="str">
+        <v>00231058</v>
+      </c>
+      <c r="F2892">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="B2893" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 103</v>
+      </c>
+      <c r="D2893" t="str">
+        <v>81992442</v>
+      </c>
+      <c r="E2893" t="str">
+        <v>00231083</v>
+      </c>
+      <c r="F2893">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="B2894" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 103</v>
+      </c>
+      <c r="D2894" t="str">
+        <v>81947109</v>
+      </c>
+      <c r="E2894" t="str">
+        <v>00231083</v>
+      </c>
+      <c r="F2894">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="B2895" t="str">
+        <v>لاک ناخن گلدن رز مدل Color Expert شماره 129</v>
+      </c>
+      <c r="D2895" t="str">
+        <v>81993726</v>
+      </c>
+      <c r="E2895" t="str">
+        <v>00231096</v>
+      </c>
+      <c r="F2895">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="B2896" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 133</v>
+      </c>
+      <c r="D2896" t="str">
+        <v>81952247</v>
+      </c>
+      <c r="E2896" t="str">
+        <v>00231099</v>
+      </c>
+      <c r="F2896">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="B2897" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 52</v>
+      </c>
+      <c r="D2897" t="str">
+        <v>81953563</v>
+      </c>
+      <c r="E2897" t="str">
+        <v>00231119</v>
+      </c>
+      <c r="F2897">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="B2898" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 413 رنگ سرخابی تیره</v>
+      </c>
+      <c r="D2898" t="str">
+        <v>82752238</v>
+      </c>
+      <c r="E2898" t="str">
+        <v>00231131</v>
+      </c>
+      <c r="F2898">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="B2899" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 419 رنگ قهوه ای آجری</v>
+      </c>
+      <c r="D2899" t="str">
+        <v>82752277</v>
+      </c>
+      <c r="E2899" t="str">
+        <v>00231132</v>
+      </c>
+      <c r="F2899">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="B2900" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 605 رنگ یاسی اکلیلی</v>
+      </c>
+      <c r="D2900" t="str">
+        <v>82752896</v>
+      </c>
+      <c r="E2900" t="str">
+        <v>00231134</v>
+      </c>
+      <c r="F2900">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="B2901" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 135 رنگ قرمز</v>
+      </c>
+      <c r="D2901" t="str">
+        <v>83037817</v>
+      </c>
+      <c r="E2901" t="str">
+        <v>00231138</v>
+      </c>
+      <c r="F2901">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="B2902" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 606 رنگ طلایی اکلیلی</v>
+      </c>
+      <c r="D2902" t="str">
+        <v>83038447</v>
+      </c>
+      <c r="E2902" t="str">
+        <v>00231140</v>
+      </c>
+      <c r="F2902">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="B2903" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 613 رنگ سرمه ای اکلیلی</v>
+      </c>
+      <c r="D2903" t="str">
+        <v>83038641</v>
+      </c>
+      <c r="E2903" t="str">
+        <v>00231141</v>
+      </c>
+      <c r="F2903">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="B2904" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل RLON  شماره 01 با رایحه توت فرنگی</v>
+      </c>
+      <c r="D2904" t="str">
+        <v>83036888</v>
+      </c>
+      <c r="E2904" t="str">
+        <v>00221102</v>
+      </c>
+      <c r="F2904">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2905">
+      <c r="B2905" t="str">
+        <v>رژلب مایع گلدن رز مدل Long Lasting به همراه مداد لب گلدن رز مدل Dream</v>
+      </c>
+      <c r="D2905" t="str">
+        <v>81946776</v>
+      </c>
+      <c r="E2905" t="str">
+        <v>00221870</v>
+      </c>
+      <c r="F2905">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2906">
+      <c r="B2906" t="str">
+        <v>رژلب جامد مات گلدن رز مدل Mix شماره 03 مجموعه 4 عددی</v>
+      </c>
+      <c r="D2906" t="str">
+        <v>81586973</v>
+      </c>
+      <c r="E2906" t="str">
+        <v>00221878</v>
+      </c>
+      <c r="F2906">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2907">
+      <c r="B2907" t="str">
+        <v>ریمل گلدن رز مدل Flash رنگ بادمجونی تیره شماره 09</v>
+      </c>
+      <c r="D2907" t="str">
+        <v>82230383</v>
+      </c>
+      <c r="E2907" t="str">
+        <v>00221882</v>
+      </c>
+      <c r="F2907">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2908">
+      <c r="B2908" t="str">
+        <v>ریمل جدا کننده گلدن رز مدل فلش لش رنگ دیپ پالم شماره 09</v>
+      </c>
+      <c r="D2908" t="str">
+        <v>82732822</v>
+      </c>
+      <c r="E2908" t="str">
+        <v>00221916</v>
+      </c>
+      <c r="F2908">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="B2909" t="str">
+        <v>کرم پودر گلدن رز مدل آبرسان  MOISTURE TOUCH ، مناسب پوست های خشک شماره 102 حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2909" t="str">
+        <v>83482945</v>
+      </c>
+      <c r="E2909" t="str">
+        <v>00221919</v>
+      </c>
+      <c r="F2909">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2910">
+      <c r="B2910" t="str">
+        <v>کرم پودر مایع  آبرسان SPF20 گلدن رز مدل Moisture Touch شماره 104 مناسب برای انواع پوست حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2910" t="str">
+        <v>83482967</v>
+      </c>
+      <c r="E2910" t="str">
+        <v>00221921</v>
+      </c>
+      <c r="F2910">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2911">
+      <c r="B2911" t="str">
+        <v>کرم پودر گلدن رز مدل آبرسان  MOISTURE TOUCH ، مناسب پوست های خشک شماره 106 حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2911" t="str">
+        <v>83482982</v>
+      </c>
+      <c r="E2911" t="str">
+        <v>00221923</v>
+      </c>
+      <c r="F2911">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2912">
+      <c r="B2912" t="str">
+        <v>کرم پودر گلدن رز مدل آبرسان  MOISTURE TOUCH ، مناسب پوست های خشک شماره 107 حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2912" t="str">
+        <v>83482993</v>
+      </c>
+      <c r="E2912" t="str">
+        <v>00221924</v>
+      </c>
+      <c r="F2912">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2913">
+      <c r="B2913" t="str">
+        <v>کرم پودر مایع آبرسان SPF20 گلدن رز مدل Moisture Touch شماره 108 مناسب برای پوستهای خشک حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2913" t="str">
+        <v>83483024</v>
+      </c>
+      <c r="E2913" t="str">
+        <v>00221925</v>
+      </c>
+      <c r="F2913">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2914">
+      <c r="B2914" t="str">
+        <v>کرم پودر مایع آبرسان SPF20 گلدن رز مدل Moisture Touch شماره 109 مناسب برای انواع پوست حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2914" t="str">
+        <v>83483035</v>
+      </c>
+      <c r="E2914" t="str">
+        <v>00221926</v>
+      </c>
+      <c r="F2914">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2915">
+      <c r="B2915" t="str">
+        <v>کرم پودر مایع آبرسان SPF20 گلدن رز مدل Moisture Touch شماره 112 مناسب برای انواع پوست حجم 30 میلی لیتر</v>
+      </c>
+      <c r="D2915" t="str">
+        <v>83483052</v>
+      </c>
+      <c r="E2915" t="str">
+        <v>00221929</v>
+      </c>
+      <c r="F2915">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="2916">
+      <c r="B2916" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 220</v>
+      </c>
+      <c r="D2916" t="str">
+        <v>83036824</v>
+      </c>
+      <c r="E2916" t="str">
+        <v>00216057</v>
+      </c>
+      <c r="F2916">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2917">
+      <c r="B2917" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 221</v>
+      </c>
+      <c r="D2917" t="str">
+        <v>83036876</v>
+      </c>
+      <c r="E2917" t="str">
+        <v>00216058</v>
+      </c>
+      <c r="F2917">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2918">
+      <c r="B2918" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل MATTE شماره 222</v>
+      </c>
+      <c r="D2918" t="str">
+        <v>83036872</v>
+      </c>
+      <c r="E2918" t="str">
+        <v>00216059</v>
+      </c>
+      <c r="F2918">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2919">
+      <c r="B2919" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 223</v>
+      </c>
+      <c r="D2919" t="str">
+        <v>83036865</v>
+      </c>
+      <c r="E2919" t="str">
+        <v>00216060</v>
+      </c>
+      <c r="F2919">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2920">
+      <c r="B2920" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل VELVET شماره 224</v>
+      </c>
+      <c r="D2920" t="str">
+        <v>83036855</v>
+      </c>
+      <c r="E2920" t="str">
+        <v>00216061</v>
+      </c>
+      <c r="F2920">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="B2921" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET شماره 225</v>
+      </c>
+      <c r="D2921" t="str">
+        <v>83036851</v>
+      </c>
+      <c r="E2921" t="str">
+        <v>00216062</v>
+      </c>
+      <c r="F2921">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="B2922" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 226</v>
+      </c>
+      <c r="D2922" t="str">
+        <v>83036845</v>
+      </c>
+      <c r="E2922" t="str">
+        <v>00216063</v>
+      </c>
+      <c r="F2922">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="B2923" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 227</v>
+      </c>
+      <c r="D2923" t="str">
+        <v>83036841</v>
+      </c>
+      <c r="E2923" t="str">
+        <v>00216064</v>
+      </c>
+      <c r="F2923">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="B2924" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 228</v>
+      </c>
+      <c r="D2924" t="str">
+        <v>83036838</v>
+      </c>
+      <c r="E2924" t="str">
+        <v>00216065</v>
+      </c>
+      <c r="F2924">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="B2925" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 229</v>
+      </c>
+      <c r="D2925" t="str">
+        <v>83036834</v>
+      </c>
+      <c r="E2925" t="str">
+        <v>00216066</v>
+      </c>
+      <c r="F2925">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="B2926" t="str">
+        <v>رژ لب مایع مخملی ورشیپ مدل  VELVET MATTE شماره 230</v>
+      </c>
+      <c r="D2926" t="str">
+        <v>83036829</v>
+      </c>
+      <c r="E2926" t="str">
+        <v>00216067</v>
+      </c>
+      <c r="F2926">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="2927">
+      <c r="B2927" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 101</v>
+      </c>
+      <c r="D2927" t="str">
+        <v>83482444</v>
+      </c>
+      <c r="E2927" t="str">
+        <v>00216068</v>
+      </c>
+      <c r="F2927">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="B2928" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 102</v>
+      </c>
+      <c r="D2928" t="str">
+        <v>83482459</v>
+      </c>
+      <c r="E2928" t="str">
+        <v>00216069</v>
+      </c>
+      <c r="F2928">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="B2929" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 103</v>
+      </c>
+      <c r="D2929" t="str">
+        <v>83482621</v>
+      </c>
+      <c r="E2929" t="str">
+        <v>00216070</v>
+      </c>
+      <c r="F2929">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="B2930" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 104</v>
+      </c>
+      <c r="D2930" t="str">
+        <v>83482599</v>
+      </c>
+      <c r="E2930" t="str">
+        <v>00216071</v>
+      </c>
+      <c r="F2930">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="B2931" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 105</v>
+      </c>
+      <c r="D2931" t="str">
+        <v>83482581</v>
+      </c>
+      <c r="E2931" t="str">
+        <v>00216072</v>
+      </c>
+      <c r="F2931">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="B2932" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 106</v>
+      </c>
+      <c r="D2932" t="str">
+        <v>83482558</v>
+      </c>
+      <c r="E2932" t="str">
+        <v>00216073</v>
+      </c>
+      <c r="F2932">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2933">
+      <c r="B2933" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 107</v>
+      </c>
+      <c r="D2933" t="str">
+        <v>83482528</v>
+      </c>
+      <c r="E2933" t="str">
+        <v>00216074</v>
+      </c>
+      <c r="F2933">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="B2934" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 108</v>
+      </c>
+      <c r="D2934" t="str">
+        <v>83482497</v>
+      </c>
+      <c r="E2934" t="str">
+        <v>00216075</v>
+      </c>
+      <c r="F2934">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="B2935" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 109</v>
+      </c>
+      <c r="D2935" t="str">
+        <v>83482680</v>
+      </c>
+      <c r="E2935" t="str">
+        <v>00216076</v>
+      </c>
+      <c r="F2935">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="B2936" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 110</v>
+      </c>
+      <c r="D2936" t="str">
+        <v>83482690</v>
+      </c>
+      <c r="E2936" t="str">
+        <v>00216077</v>
+      </c>
+      <c r="F2936">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="B2937" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 111</v>
+      </c>
+      <c r="D2937" t="str">
+        <v>83482718</v>
+      </c>
+      <c r="E2937" t="str">
+        <v>00216078</v>
+      </c>
+      <c r="F2937">
+        <v>2320000</v>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="B2938" t="str">
+        <v>رژ لب مدادی مات مخملی ورشیپ مدل  VELVET MATTE ضد آب شماره 112</v>
+      </c>
+      <c r="D2938" t="str">
+        <v>83482753</v>
+      </c>
+      <c r="E2938" t="str">
+        <v>00216079</v>
+      </c>
+      <c r="F2938">
+        <v>2320000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2885"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2938"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2938"/>
+  <dimension ref="A1:G2986"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -19415,7 +19415,7 @@
         <v>00216006</v>
       </c>
       <c r="F946">
-        <v>1080000</v>
+        <v>1800000</v>
       </c>
       <c r="G946">
         <v>1230000</v>
@@ -19438,7 +19438,7 @@
         <v>00216005</v>
       </c>
       <c r="F947">
-        <v>1080000</v>
+        <v>1800000</v>
       </c>
       <c r="G947">
         <v>1230000</v>
@@ -53531,9 +53531,681 @@
         <v>2320000</v>
       </c>
     </row>
+    <row r="2939">
+      <c r="B2939" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 05 رنگ کرم استخوانی</v>
+      </c>
+      <c r="D2939" t="str">
+        <v>82752672</v>
+      </c>
+      <c r="E2939" t="str">
+        <v>00231003</v>
+      </c>
+      <c r="F2939">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2940">
+      <c r="B2940" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 06</v>
+      </c>
+      <c r="D2940" t="str">
+        <v>81956170</v>
+      </c>
+      <c r="E2940" t="str">
+        <v>00231004</v>
+      </c>
+      <c r="F2940">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2941">
+      <c r="B2941" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 06</v>
+      </c>
+      <c r="D2941" t="str">
+        <v>81951885</v>
+      </c>
+      <c r="E2941" t="str">
+        <v>00231004</v>
+      </c>
+      <c r="F2941">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2942">
+      <c r="B2942" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 08</v>
+      </c>
+      <c r="D2942" t="str">
+        <v>81992547</v>
+      </c>
+      <c r="E2942" t="str">
+        <v>00231006</v>
+      </c>
+      <c r="F2942">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2943">
+      <c r="B2943" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 08</v>
+      </c>
+      <c r="D2943" t="str">
+        <v>81951445</v>
+      </c>
+      <c r="E2943" t="str">
+        <v>00231006</v>
+      </c>
+      <c r="F2943">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2944">
+      <c r="B2944" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 10 رنگ کالباسی</v>
+      </c>
+      <c r="D2944" t="str">
+        <v>83037090</v>
+      </c>
+      <c r="E2944" t="str">
+        <v>00231007</v>
+      </c>
+      <c r="F2944">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2945">
+      <c r="B2945" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 10</v>
+      </c>
+      <c r="D2945" t="str">
+        <v>81957256</v>
+      </c>
+      <c r="E2945" t="str">
+        <v>00231007</v>
+      </c>
+      <c r="F2945">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2946">
+      <c r="B2946" t="str">
+        <v>لاک گلدن رز مدل کالر اکسپرت شماره 14</v>
+      </c>
+      <c r="D2946" t="str">
+        <v>81955860</v>
+      </c>
+      <c r="E2946" t="str">
+        <v>00231010</v>
+      </c>
+      <c r="F2946">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2947">
+      <c r="B2947" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 14</v>
+      </c>
+      <c r="D2947" t="str">
+        <v>81951570</v>
+      </c>
+      <c r="E2947" t="str">
+        <v>00231010</v>
+      </c>
+      <c r="F2947">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2948">
+      <c r="B2948" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 16 رنگ صورتی</v>
+      </c>
+      <c r="D2948" t="str">
+        <v>82752304</v>
+      </c>
+      <c r="E2948" t="str">
+        <v>00231012</v>
+      </c>
+      <c r="F2948">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2949">
+      <c r="B2949" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 16</v>
+      </c>
+      <c r="D2949" t="str">
+        <v>81947200</v>
+      </c>
+      <c r="E2949" t="str">
+        <v>00231012</v>
+      </c>
+      <c r="F2949">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2950">
+      <c r="B2950" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 29</v>
+      </c>
+      <c r="D2950" t="str">
+        <v>81948068</v>
+      </c>
+      <c r="E2950" t="str">
+        <v>00231024</v>
+      </c>
+      <c r="F2950">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2951">
+      <c r="B2951" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 31 رنگ زرشکی متالیک</v>
+      </c>
+      <c r="D2951" t="str">
+        <v>83038171</v>
+      </c>
+      <c r="E2951" t="str">
+        <v>00231026</v>
+      </c>
+      <c r="F2951">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2952">
+      <c r="B2952" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 31</v>
+      </c>
+      <c r="D2952" t="str">
+        <v>81950357</v>
+      </c>
+      <c r="E2952" t="str">
+        <v>00231026</v>
+      </c>
+      <c r="F2952">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2953">
+      <c r="B2953" t="str">
+        <v>لاک ناخن گلدن رز مدل 62</v>
+      </c>
+      <c r="D2953" t="str">
+        <v>81947473</v>
+      </c>
+      <c r="E2953" t="str">
+        <v>00231049</v>
+      </c>
+      <c r="F2953">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2954">
+      <c r="B2954" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 67</v>
+      </c>
+      <c r="D2954" t="str">
+        <v>81956675</v>
+      </c>
+      <c r="E2954" t="str">
+        <v>00231054</v>
+      </c>
+      <c r="F2954">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2955">
+      <c r="B2955" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 67</v>
+      </c>
+      <c r="D2955" t="str">
+        <v>81956131</v>
+      </c>
+      <c r="E2955" t="str">
+        <v>00231054</v>
+      </c>
+      <c r="F2955">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2956">
+      <c r="B2956" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 79</v>
+      </c>
+      <c r="D2956" t="str">
+        <v>81953540</v>
+      </c>
+      <c r="E2956" t="str">
+        <v>00231063</v>
+      </c>
+      <c r="F2956">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2957">
+      <c r="B2957" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 79</v>
+      </c>
+      <c r="D2957" t="str">
+        <v>81948676</v>
+      </c>
+      <c r="E2957" t="str">
+        <v>00231063</v>
+      </c>
+      <c r="F2957">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2958">
+      <c r="B2958" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 80</v>
+      </c>
+      <c r="D2958" t="str">
+        <v>81993481</v>
+      </c>
+      <c r="E2958" t="str">
+        <v>00231064</v>
+      </c>
+      <c r="F2958">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2959">
+      <c r="B2959" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 85</v>
+      </c>
+      <c r="D2959" t="str">
+        <v>81992899</v>
+      </c>
+      <c r="E2959" t="str">
+        <v>00231068</v>
+      </c>
+      <c r="F2959">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2960">
+      <c r="B2960" t="str">
+        <v>لاک گلدن رز مدل کالر اکسپرت شماره 85</v>
+      </c>
+      <c r="D2960" t="str">
+        <v>81955830</v>
+      </c>
+      <c r="E2960" t="str">
+        <v>00231068</v>
+      </c>
+      <c r="F2960">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2961">
+      <c r="B2961" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 98</v>
+      </c>
+      <c r="D2961" t="str">
+        <v>81957650</v>
+      </c>
+      <c r="E2961" t="str">
+        <v>00231078</v>
+      </c>
+      <c r="F2961">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2962">
+      <c r="B2962" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 99</v>
+      </c>
+      <c r="D2962" t="str">
+        <v>81952895</v>
+      </c>
+      <c r="E2962" t="str">
+        <v>00231079</v>
+      </c>
+      <c r="F2962">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2963">
+      <c r="B2963" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 99</v>
+      </c>
+      <c r="D2963" t="str">
+        <v>81948302</v>
+      </c>
+      <c r="E2963" t="str">
+        <v>00231079</v>
+      </c>
+      <c r="F2963">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2964">
+      <c r="B2964" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 100</v>
+      </c>
+      <c r="D2964" t="str">
+        <v>81957713</v>
+      </c>
+      <c r="E2964" t="str">
+        <v>00231080</v>
+      </c>
+      <c r="F2964">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2965">
+      <c r="B2965" t="str">
+        <v>لاک ناخن گلدن رز مدل Color Expert شماره 100</v>
+      </c>
+      <c r="D2965" t="str">
+        <v>81952962</v>
+      </c>
+      <c r="E2965" t="str">
+        <v>00231080</v>
+      </c>
+      <c r="F2965">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2966">
+      <c r="B2966" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 101</v>
+      </c>
+      <c r="D2966" t="str">
+        <v>81956404</v>
+      </c>
+      <c r="E2966" t="str">
+        <v>00231081</v>
+      </c>
+      <c r="F2966">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2967">
+      <c r="B2967" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 101</v>
+      </c>
+      <c r="D2967" t="str">
+        <v>81952340</v>
+      </c>
+      <c r="E2967" t="str">
+        <v>00231081</v>
+      </c>
+      <c r="F2967">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2968">
+      <c r="B2968" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 106 رنگ رز آجری</v>
+      </c>
+      <c r="D2968" t="str">
+        <v>83037528</v>
+      </c>
+      <c r="E2968" t="str">
+        <v>00231086</v>
+      </c>
+      <c r="F2968">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="B2969" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 106</v>
+      </c>
+      <c r="D2969" t="str">
+        <v>81992863</v>
+      </c>
+      <c r="E2969" t="str">
+        <v>00231086</v>
+      </c>
+      <c r="F2969">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="B2970" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 106</v>
+      </c>
+      <c r="D2970" t="str">
+        <v>81957123</v>
+      </c>
+      <c r="E2970" t="str">
+        <v>00231086</v>
+      </c>
+      <c r="F2970">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="B2971" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 108</v>
+      </c>
+      <c r="D2971" t="str">
+        <v>81952600</v>
+      </c>
+      <c r="E2971" t="str">
+        <v>00231088</v>
+      </c>
+      <c r="F2971">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="B2972" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 110</v>
+      </c>
+      <c r="D2972" t="str">
+        <v>81992301</v>
+      </c>
+      <c r="E2972" t="str">
+        <v>00231090</v>
+      </c>
+      <c r="F2972">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="B2973" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 112</v>
+      </c>
+      <c r="D2973" t="str">
+        <v>81948274</v>
+      </c>
+      <c r="E2973" t="str">
+        <v>00231091</v>
+      </c>
+      <c r="F2973">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="B2974" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 113</v>
+      </c>
+      <c r="D2974" t="str">
+        <v>81955737</v>
+      </c>
+      <c r="E2974" t="str">
+        <v>00231092</v>
+      </c>
+      <c r="F2974">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="B2975" t="str">
+        <v>لاک ناخن گلدن رز مدل color expert شماره 113</v>
+      </c>
+      <c r="D2975" t="str">
+        <v>81947559</v>
+      </c>
+      <c r="E2975" t="str">
+        <v>00231092</v>
+      </c>
+      <c r="F2975">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="B2976" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 115</v>
+      </c>
+      <c r="D2976" t="str">
+        <v>81993142</v>
+      </c>
+      <c r="E2976" t="str">
+        <v>00231093</v>
+      </c>
+      <c r="F2976">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2977">
+      <c r="B2977" t="str">
+        <v>لاک ناخن گلدن رز شماره 115</v>
+      </c>
+      <c r="D2977" t="str">
+        <v>81952147</v>
+      </c>
+      <c r="E2977" t="str">
+        <v>00231093</v>
+      </c>
+      <c r="F2977">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="B2978" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 132</v>
+      </c>
+      <c r="D2978" t="str">
+        <v>81956302</v>
+      </c>
+      <c r="E2978" t="str">
+        <v>00231098</v>
+      </c>
+      <c r="F2978">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="B2979" t="str">
+        <v>لاک ناخن گلدن رز مدل Color Expert شماره 407</v>
+      </c>
+      <c r="D2979" t="str">
+        <v>81952993</v>
+      </c>
+      <c r="E2979" t="str">
+        <v>00231103</v>
+      </c>
+      <c r="F2979">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="B2980" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 111 رنگ آبی نفتی</v>
+      </c>
+      <c r="D2980" t="str">
+        <v>82752175</v>
+      </c>
+      <c r="E2980" t="str">
+        <v>00231112</v>
+      </c>
+      <c r="F2980">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="B2981" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 111</v>
+      </c>
+      <c r="D2981" t="str">
+        <v>81956050</v>
+      </c>
+      <c r="E2981" t="str">
+        <v>00231112</v>
+      </c>
+      <c r="F2981">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="B2982" t="str">
+        <v>لاک گلدن رز مدل کالر اکسپرت شماره 95</v>
+      </c>
+      <c r="D2982" t="str">
+        <v>81955762</v>
+      </c>
+      <c r="E2982" t="str">
+        <v>00231113</v>
+      </c>
+      <c r="F2982">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="B2983" t="str">
+        <v>لاک گلدن رز مدل EXPERT شماره 78</v>
+      </c>
+      <c r="D2983" t="str">
+        <v>81953903</v>
+      </c>
+      <c r="E2983" t="str">
+        <v>00231116</v>
+      </c>
+      <c r="F2983">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="B2984" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 164 رنگ بژ اکلیلی</v>
+      </c>
+      <c r="D2984" t="str">
+        <v>82753086</v>
+      </c>
+      <c r="E2984" t="str">
+        <v>00231124</v>
+      </c>
+      <c r="F2984">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="B2985" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 405 رنگ طوسی</v>
+      </c>
+      <c r="D2985" t="str">
+        <v>82752524</v>
+      </c>
+      <c r="E2985" t="str">
+        <v>00231128</v>
+      </c>
+      <c r="F2985">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="B2986" t="str">
+        <v>لاک ناخن گلدن رز مدل Expert شماره 408 رنگ سبز یشمی تیره</v>
+      </c>
+      <c r="D2986" t="str">
+        <v>82752491</v>
+      </c>
+      <c r="E2986" t="str">
+        <v>00231129</v>
+      </c>
+      <c r="F2986">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2938"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2986"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2986"/>
+  <dimension ref="A1:G3032"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7892,7 +7892,7 @@
         <v>00221256</v>
       </c>
       <c r="F361">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="362">
@@ -8012,7 +8012,7 @@
         <v>00221454</v>
       </c>
       <c r="F367">
-        <v>924000</v>
+        <v>127</v>
       </c>
     </row>
     <row r="368">
@@ -8455,7 +8455,7 @@
         <v>00221394</v>
       </c>
       <c r="F389">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="390">
@@ -8535,7 +8535,7 @@
         <v>00221439</v>
       </c>
       <c r="F393">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="394">
@@ -8555,7 +8555,7 @@
         <v>00221439</v>
       </c>
       <c r="F394">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="395">
@@ -8715,7 +8715,7 @@
         <v>00221479</v>
       </c>
       <c r="F402">
-        <v>1480000</v>
+        <v>247</v>
       </c>
     </row>
     <row r="403">
@@ -11226,7 +11226,7 @@
         <v>00221394</v>
       </c>
       <c r="F531">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="532">
@@ -12328,7 +12328,7 @@
         <v>00221087</v>
       </c>
       <c r="F587">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="588">
@@ -13888,7 +13888,7 @@
         <v>00221083</v>
       </c>
       <c r="F665">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="666">
@@ -13908,7 +13908,7 @@
         <v>00221083</v>
       </c>
       <c r="F666">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="667">
@@ -14088,7 +14088,7 @@
         <v>00221229</v>
       </c>
       <c r="F675">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="676">
@@ -14108,7 +14108,7 @@
         <v>00221229</v>
       </c>
       <c r="F676">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="677">
@@ -14128,7 +14128,7 @@
         <v>00221229</v>
       </c>
       <c r="F677">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="678">
@@ -31872,7 +31872,7 @@
         <v>00221056</v>
       </c>
       <c r="F1575">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1576">
@@ -32492,7 +32492,7 @@
         <v>00221056</v>
       </c>
       <c r="F1606">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="1607">
@@ -46507,7 +46507,7 @@
         <v>00221056</v>
       </c>
       <c r="F2435">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2436">
@@ -47890,7 +47890,7 @@
         <v>00221083</v>
       </c>
       <c r="F2534">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2535">
@@ -47946,7 +47946,7 @@
         <v>00221087</v>
       </c>
       <c r="F2538">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2539">
@@ -48909,7 +48909,7 @@
         <v>00221479</v>
       </c>
       <c r="F2607">
-        <v>1480000</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2608">
@@ -49791,7 +49791,7 @@
         <v>00221756</v>
       </c>
       <c r="F2670">
-        <v>2.12</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2671">
@@ -49805,7 +49805,7 @@
         <v>00221757</v>
       </c>
       <c r="F2671">
-        <v>2.12</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2672">
@@ -54203,9 +54203,653 @@
         <v>82</v>
       </c>
     </row>
+    <row r="2987">
+      <c r="B2987" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 216</v>
+      </c>
+      <c r="D2987" t="str">
+        <v>81956622</v>
+      </c>
+      <c r="E2987" t="str">
+        <v>00221847</v>
+      </c>
+      <c r="F2987">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="B2988" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 210</v>
+      </c>
+      <c r="D2988" t="str">
+        <v>81956592</v>
+      </c>
+      <c r="E2988" t="str">
+        <v>00221848</v>
+      </c>
+      <c r="F2988">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="B2989" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 211</v>
+      </c>
+      <c r="D2989" t="str">
+        <v>81956563</v>
+      </c>
+      <c r="E2989" t="str">
+        <v>00221849</v>
+      </c>
+      <c r="F2989">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="B2990" t="str">
+        <v>رژ لب جامد گلدن رز مدل Silky Shine شماره 203</v>
+      </c>
+      <c r="D2990" t="str">
+        <v>81956529</v>
+      </c>
+      <c r="E2990" t="str">
+        <v>00221850</v>
+      </c>
+      <c r="F2990">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="B2991" t="str">
+        <v>رژ لب جامد گلدن رز مدل Silky Shine شماره 203</v>
+      </c>
+      <c r="D2991" t="str">
+        <v>81951484</v>
+      </c>
+      <c r="E2991" t="str">
+        <v>00221850</v>
+      </c>
+      <c r="F2991">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="B2992" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 205</v>
+      </c>
+      <c r="D2992" t="str">
+        <v>81952365</v>
+      </c>
+      <c r="E2992" t="str">
+        <v>00221856</v>
+      </c>
+      <c r="F2992">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="B2993" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 212</v>
+      </c>
+      <c r="D2993" t="str">
+        <v>81952465</v>
+      </c>
+      <c r="E2993" t="str">
+        <v>00221857</v>
+      </c>
+      <c r="F2993">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="B2994" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 213</v>
+      </c>
+      <c r="D2994" t="str">
+        <v>81952378</v>
+      </c>
+      <c r="E2994" t="str">
+        <v>00221858</v>
+      </c>
+      <c r="F2994">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="B2995" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 214</v>
+      </c>
+      <c r="D2995" t="str">
+        <v>81952413</v>
+      </c>
+      <c r="E2995" t="str">
+        <v>00221859</v>
+      </c>
+      <c r="F2995">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="B2996" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل سیلکی شاین شماره 201</v>
+      </c>
+      <c r="D2996" t="str">
+        <v>81951521</v>
+      </c>
+      <c r="E2996" t="str">
+        <v>00221860</v>
+      </c>
+      <c r="F2996">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="B2997" t="str">
+        <v>رژ لب جامد گلدن رز مدل Silky Shine شماره 207</v>
+      </c>
+      <c r="D2997" t="str">
+        <v>81948555</v>
+      </c>
+      <c r="E2997" t="str">
+        <v>00221864</v>
+      </c>
+      <c r="F2997">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="B2998" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 209</v>
+      </c>
+      <c r="D2998" t="str">
+        <v>81948527</v>
+      </c>
+      <c r="E2998" t="str">
+        <v>00221865</v>
+      </c>
+      <c r="F2998">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="B2999" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 215</v>
+      </c>
+      <c r="D2999" t="str">
+        <v>81948608</v>
+      </c>
+      <c r="E2999" t="str">
+        <v>00221866</v>
+      </c>
+      <c r="F2999">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="B3000" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 218</v>
+      </c>
+      <c r="D3000" t="str">
+        <v>81948575</v>
+      </c>
+      <c r="E3000" t="str">
+        <v>00221867</v>
+      </c>
+      <c r="F3000">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="B3001" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 219</v>
+      </c>
+      <c r="D3001" t="str">
+        <v>81948634</v>
+      </c>
+      <c r="E3001" t="str">
+        <v>00221868</v>
+      </c>
+      <c r="F3001">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="B3002" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل سیلکی شاین شماره 202</v>
+      </c>
+      <c r="D3002" t="str">
+        <v>82753609</v>
+      </c>
+      <c r="E3002" t="str">
+        <v>00221912</v>
+      </c>
+      <c r="F3002">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3003">
+      <c r="B3003" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل Silky Shine شماره 220</v>
+      </c>
+      <c r="D3003" t="str">
+        <v>82753409</v>
+      </c>
+      <c r="E3003" t="str">
+        <v>00221913</v>
+      </c>
+      <c r="F3003">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3004">
+      <c r="B3004" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 101</v>
+      </c>
+      <c r="D3004" t="str">
+        <v>83533854</v>
+      </c>
+      <c r="E3004" t="str">
+        <v>00221930</v>
+      </c>
+      <c r="F3004">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3005">
+      <c r="B3005" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 102 رنگ کالباسی</v>
+      </c>
+      <c r="D3005" t="str">
+        <v>83533841</v>
+      </c>
+      <c r="E3005" t="str">
+        <v>00221931</v>
+      </c>
+      <c r="F3005">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3006">
+      <c r="B3006" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 103رنگ گوشتی</v>
+      </c>
+      <c r="D3006" t="str">
+        <v>83533830</v>
+      </c>
+      <c r="E3006" t="str">
+        <v>00221932</v>
+      </c>
+      <c r="F3006">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3007">
+      <c r="B3007" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 104 رنگ کرم کالباسی</v>
+      </c>
+      <c r="D3007" t="str">
+        <v>83533818</v>
+      </c>
+      <c r="E3007" t="str">
+        <v>00221933</v>
+      </c>
+      <c r="F3007">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3008">
+      <c r="B3008" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 105  رنگ  کالباسی</v>
+      </c>
+      <c r="D3008" t="str">
+        <v>83533804</v>
+      </c>
+      <c r="E3008" t="str">
+        <v>00221934</v>
+      </c>
+      <c r="F3008">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3009">
+      <c r="B3009" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 106 رنگ  کالباسی</v>
+      </c>
+      <c r="D3009" t="str">
+        <v>83533794</v>
+      </c>
+      <c r="E3009" t="str">
+        <v>00221935</v>
+      </c>
+      <c r="F3009">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3010">
+      <c r="B3010" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 107 رنگ  گلبهی</v>
+      </c>
+      <c r="D3010" t="str">
+        <v>83533785</v>
+      </c>
+      <c r="E3010" t="str">
+        <v>00221936</v>
+      </c>
+      <c r="F3010">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3011">
+      <c r="B3011" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 108رنگ  گوشتی</v>
+      </c>
+      <c r="D3011" t="str">
+        <v>83533774</v>
+      </c>
+      <c r="E3011" t="str">
+        <v>00221937</v>
+      </c>
+      <c r="F3011">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3012">
+      <c r="B3012" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 109  رنگ  کالباسی</v>
+      </c>
+      <c r="D3012" t="str">
+        <v>83533766</v>
+      </c>
+      <c r="E3012" t="str">
+        <v>00221938</v>
+      </c>
+      <c r="F3012">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3013">
+      <c r="B3013" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 110  رنگ  صورتی</v>
+      </c>
+      <c r="D3013" t="str">
+        <v>83533735</v>
+      </c>
+      <c r="E3013" t="str">
+        <v>00221939</v>
+      </c>
+      <c r="F3013">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3014">
+      <c r="B3014" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 111  رنگ  صورتی یاسی</v>
+      </c>
+      <c r="D3014" t="str">
+        <v>83533721</v>
+      </c>
+      <c r="E3014" t="str">
+        <v>00221940</v>
+      </c>
+      <c r="F3014">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3015">
+      <c r="B3015" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 112  رنگ گوشتی</v>
+      </c>
+      <c r="D3015" t="str">
+        <v>83533705</v>
+      </c>
+      <c r="E3015" t="str">
+        <v>00221941</v>
+      </c>
+      <c r="F3015">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3016">
+      <c r="B3016" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 113 رنگ گوشتی</v>
+      </c>
+      <c r="D3016" t="str">
+        <v>83533695</v>
+      </c>
+      <c r="E3016" t="str">
+        <v>00221942</v>
+      </c>
+      <c r="F3016">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3017">
+      <c r="B3017" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 114  رنگ صورتی قرمز</v>
+      </c>
+      <c r="D3017" t="str">
+        <v>83533668</v>
+      </c>
+      <c r="E3017" t="str">
+        <v>00221943</v>
+      </c>
+      <c r="F3017">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3018">
+      <c r="B3018" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 115 رنگ قرمز</v>
+      </c>
+      <c r="D3018" t="str">
+        <v>83533650</v>
+      </c>
+      <c r="E3018" t="str">
+        <v>00221944</v>
+      </c>
+      <c r="F3018">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3019">
+      <c r="B3019" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ صورتی گوشتی شماره 116</v>
+      </c>
+      <c r="D3019" t="str">
+        <v>83533640</v>
+      </c>
+      <c r="E3019" t="str">
+        <v>00221945</v>
+      </c>
+      <c r="F3019">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3020">
+      <c r="B3020" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ قرمز شماره 117</v>
+      </c>
+      <c r="D3020" t="str">
+        <v>83533602</v>
+      </c>
+      <c r="E3020" t="str">
+        <v>00221946</v>
+      </c>
+      <c r="F3020">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3021">
+      <c r="B3021" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ قرمز پررنگ شماره 118</v>
+      </c>
+      <c r="D3021" t="str">
+        <v>83533589</v>
+      </c>
+      <c r="E3021" t="str">
+        <v>00221947</v>
+      </c>
+      <c r="F3021">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3022">
+      <c r="B3022" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ قرمز قهوه ای شماره 119</v>
+      </c>
+      <c r="D3022" t="str">
+        <v>83533576</v>
+      </c>
+      <c r="E3022" t="str">
+        <v>00221948</v>
+      </c>
+      <c r="F3022">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3023">
+      <c r="B3023" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE  رنگ قهوه ای شماره 120</v>
+      </c>
+      <c r="D3023" t="str">
+        <v>83533540</v>
+      </c>
+      <c r="E3023" t="str">
+        <v>00221949</v>
+      </c>
+      <c r="F3023">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3024">
+      <c r="B3024" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ قهوه ای شماره 121</v>
+      </c>
+      <c r="D3024" t="str">
+        <v>83533524</v>
+      </c>
+      <c r="E3024" t="str">
+        <v>00221950</v>
+      </c>
+      <c r="F3024">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3025">
+      <c r="B3025" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ کالباسی گوشتی شماره 122</v>
+      </c>
+      <c r="D3025" t="str">
+        <v>83533511</v>
+      </c>
+      <c r="E3025" t="str">
+        <v>00221951</v>
+      </c>
+      <c r="F3025">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3026">
+      <c r="B3026" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ گوشتی شماره 123</v>
+      </c>
+      <c r="D3026" t="str">
+        <v>83533494</v>
+      </c>
+      <c r="E3026" t="str">
+        <v>00221952</v>
+      </c>
+      <c r="F3026">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3027">
+      <c r="B3027" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE رنگ کالباسی گوشتی شماره 124</v>
+      </c>
+      <c r="D3027" t="str">
+        <v>83533481</v>
+      </c>
+      <c r="E3027" t="str">
+        <v>00221953</v>
+      </c>
+      <c r="F3027">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3028">
+      <c r="B3028" t="str">
+        <v>رژ لب جامد پودری مات گلدن رز مدل PURE MATTE شماره 125 رنگ شاتوتی</v>
+      </c>
+      <c r="D3028" t="str">
+        <v>83533469</v>
+      </c>
+      <c r="E3028" t="str">
+        <v>00221954</v>
+      </c>
+      <c r="F3028">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3029">
+      <c r="B3029" t="str">
+        <v>رژ لب جامد مات گلدن رز مدل PURE MATTE شماره 126 رنگ قهوه ای</v>
+      </c>
+      <c r="D3029" t="str">
+        <v>83533454</v>
+      </c>
+      <c r="E3029" t="str">
+        <v>00221955</v>
+      </c>
+      <c r="F3029">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3030">
+      <c r="B3030" t="str">
+        <v>رژ لب جامد مات گلدن رز مدل PURE MATTE شماره 127 رنگ قرمز</v>
+      </c>
+      <c r="D3030" t="str">
+        <v>83533446</v>
+      </c>
+      <c r="E3030" t="str">
+        <v>00221956</v>
+      </c>
+      <c r="F3030">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="B3031" t="str">
+        <v>رژ لب جامد مات گلدن رز مدل PURE MATTE شماره 128 رنگ قهوه ای</v>
+      </c>
+      <c r="D3031" t="str">
+        <v>83533437</v>
+      </c>
+      <c r="E3031" t="str">
+        <v>00221957</v>
+      </c>
+      <c r="F3031">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="B3032" t="str">
+        <v>رژ لب جامد پودری گلدن رز مدل PURE MATTE شماره 129</v>
+      </c>
+      <c r="D3032" t="str">
+        <v>83533423</v>
+      </c>
+      <c r="E3032" t="str">
+        <v>00221958</v>
+      </c>
+      <c r="F3032">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2986"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3032"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -3880,7 +3880,7 @@
         <v>00221625</v>
       </c>
       <c r="F173">
-        <v>1804000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="174">
@@ -4618,7 +4618,7 @@
         <v>00221242</v>
       </c>
       <c r="F206">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="207">
@@ -7552,7 +7552,7 @@
         <v>00221472</v>
       </c>
       <c r="F344">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="345">
@@ -7672,7 +7672,7 @@
         <v>00221536</v>
       </c>
       <c r="F350">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="351">
@@ -8595,7 +8595,7 @@
         <v>00221437</v>
       </c>
       <c r="F396">
-        <v>4036500</v>
+        <v>299</v>
       </c>
     </row>
     <row r="397">
@@ -8615,7 +8615,7 @@
         <v>00221437</v>
       </c>
       <c r="F397">
-        <v>4036500</v>
+        <v>299</v>
       </c>
     </row>
     <row r="398">
@@ -9995,7 +9995,7 @@
         <v>00221442</v>
       </c>
       <c r="F466">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="467">
@@ -12068,7 +12068,7 @@
         <v>00221410</v>
       </c>
       <c r="F574">
-        <v>2072400</v>
+        <v>186</v>
       </c>
     </row>
     <row r="575">
@@ -12308,7 +12308,7 @@
         <v>00221090</v>
       </c>
       <c r="F586">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="587">
@@ -24365,7 +24365,7 @@
         <v>00221061</v>
       </c>
       <c r="F1210">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1211">
@@ -28521,7 +28521,7 @@
         <v>00221022</v>
       </c>
       <c r="F1416">
-        <v>2550000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1417">
@@ -30724,7 +30724,7 @@
         <v>00221134</v>
       </c>
       <c r="F1520">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1521">
@@ -32072,7 +32072,7 @@
         <v>00221054</v>
       </c>
       <c r="F1585">
-        <v>3063500</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1586">
@@ -34831,7 +34831,7 @@
         <v>00221410</v>
       </c>
       <c r="F1730">
-        <v>2072400</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1731">
@@ -36551,7 +36551,7 @@
         <v>00221022</v>
       </c>
       <c r="F1825">
-        <v>2550000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1826">
@@ -47249,7 +47249,7 @@
         <v>00221625</v>
       </c>
       <c r="F2488">
-        <v>1804000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2489">
@@ -47974,7 +47974,7 @@
         <v>00221090</v>
       </c>
       <c r="F2540">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2541">
@@ -48030,7 +48030,7 @@
         <v>00221242</v>
       </c>
       <c r="F2544">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2545">
@@ -48184,7 +48184,7 @@
         <v>00221134</v>
       </c>
       <c r="F2555">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2556">
@@ -50213,7 +50213,7 @@
         <v>00221811</v>
       </c>
       <c r="F2701">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2702">
@@ -50241,7 +50241,7 @@
         <v>00221813</v>
       </c>
       <c r="F2703">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2704">
@@ -50521,7 +50521,7 @@
         <v>00221824</v>
       </c>
       <c r="F2723">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2724">

--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3032"/>
+  <dimension ref="A1:G3042"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2502,7 +2502,7 @@
         <v>45822594</v>
       </c>
       <c r="F105">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="106">
@@ -2519,7 +2519,7 @@
         <v>45822531</v>
       </c>
       <c r="F106">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="107">
@@ -11925,7 +11925,7 @@
         <v>38147716</v>
       </c>
       <c r="F567">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G567">
         <v>35000</v>
@@ -11945,7 +11945,7 @@
         <v>38147321</v>
       </c>
       <c r="F568">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G568">
         <v>35000</v>
@@ -11965,7 +11965,7 @@
         <v>38146217</v>
       </c>
       <c r="F569">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G569">
         <v>35000</v>
@@ -13648,7 +13648,7 @@
         <v>00221240</v>
       </c>
       <c r="F653">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="654">
@@ -14871,7 +14871,7 @@
         <v>35978635</v>
       </c>
       <c r="F714">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="715">
@@ -14888,7 +14888,7 @@
         <v>35978537</v>
       </c>
       <c r="F715">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="716">
@@ -20367,7 +20367,7 @@
         <v>34371439</v>
       </c>
       <c r="F999">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1000">
@@ -25425,7 +25425,7 @@
         <v>00221199</v>
       </c>
       <c r="F1263">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1264">
@@ -25565,7 +25565,7 @@
         <v>00221197</v>
       </c>
       <c r="F1270">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1271">
@@ -25885,7 +25885,7 @@
         <v>00221199</v>
       </c>
       <c r="F1286">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1287">
@@ -30681,7 +30681,7 @@
         <v>30834962</v>
       </c>
       <c r="F1518">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1519">
@@ -30930,7 +30930,7 @@
         <v>00221195</v>
       </c>
       <c r="F1530">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1531">
@@ -30950,7 +30950,7 @@
         <v>00221195</v>
       </c>
       <c r="F1531">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1532">
@@ -33096,7 +33096,7 @@
         <v>55003389</v>
       </c>
       <c r="F1635">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1636">
@@ -34351,7 +34351,7 @@
         <v>48696472</v>
       </c>
       <c r="F1703">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1704">
@@ -34368,7 +34368,7 @@
         <v>48696438</v>
       </c>
       <c r="F1704">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1705">
@@ -34385,7 +34385,7 @@
         <v>48696304</v>
       </c>
       <c r="F1705">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1706">
@@ -34402,7 +34402,7 @@
         <v>48696268</v>
       </c>
       <c r="F1706">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1707">
@@ -34419,7 +34419,7 @@
         <v>48484996</v>
       </c>
       <c r="F1707">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1708">
@@ -34436,7 +34436,7 @@
         <v>48005865</v>
       </c>
       <c r="F1708">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1709">
@@ -34453,7 +34453,7 @@
         <v>48005831</v>
       </c>
       <c r="F1709">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1710">
@@ -34470,7 +34470,7 @@
         <v>48005800</v>
       </c>
       <c r="F1710">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1711">
@@ -34487,7 +34487,7 @@
         <v>48005774</v>
       </c>
       <c r="F1711">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1712">
@@ -34504,7 +34504,7 @@
         <v>48004979</v>
       </c>
       <c r="F1712">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1713">
@@ -34521,7 +34521,7 @@
         <v>48004895</v>
       </c>
       <c r="F1713">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1714">
@@ -34538,7 +34538,7 @@
         <v>48004738</v>
       </c>
       <c r="F1714">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1715">
@@ -34555,7 +34555,7 @@
         <v>49176643</v>
       </c>
       <c r="F1715">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1715">
         <v>974800</v>
@@ -34575,7 +34575,7 @@
         <v>49095632</v>
       </c>
       <c r="F1716">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1716">
         <v>657500</v>
@@ -34595,7 +34595,7 @@
         <v>48005692</v>
       </c>
       <c r="F1717">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1718">
@@ -34612,7 +34612,7 @@
         <v>48805764</v>
       </c>
       <c r="F1718">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1719">
@@ -34629,7 +34629,7 @@
         <v>48499213</v>
       </c>
       <c r="F1719">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1719">
         <v>450000</v>
@@ -34649,7 +34649,7 @@
         <v>48499173</v>
       </c>
       <c r="F1720">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1720">
         <v>1740000</v>
@@ -34669,7 +34669,7 @@
         <v>48483945</v>
       </c>
       <c r="F1721">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1721">
         <v>1740000</v>
@@ -34689,7 +34689,7 @@
         <v>48483874</v>
       </c>
       <c r="F1722">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1722">
         <v>590000</v>
@@ -34709,7 +34709,7 @@
         <v>48483840</v>
       </c>
       <c r="F1723">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1723">
         <v>590000</v>
@@ -34729,7 +34729,7 @@
         <v>47445192</v>
       </c>
       <c r="F1724">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1725">
@@ -34746,7 +34746,7 @@
         <v>47445075</v>
       </c>
       <c r="F1725">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1726">
@@ -34763,7 +34763,7 @@
         <v>44470822</v>
       </c>
       <c r="F1726">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1727">
@@ -34780,7 +34780,7 @@
         <v>43636861</v>
       </c>
       <c r="F1727">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1728">
@@ -36228,7 +36228,7 @@
         <v>111111</v>
       </c>
       <c r="F1806">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1807">
@@ -36824,7 +36824,7 @@
         <v>56329672</v>
       </c>
       <c r="F1840">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1840">
         <v>275200</v>
@@ -37541,7 +37541,7 @@
         <v>50000020</v>
       </c>
       <c r="F1876">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1876">
         <v>275200</v>
@@ -37558,7 +37558,7 @@
         <v>50000030</v>
       </c>
       <c r="F1877">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1877">
         <v>275200</v>
@@ -37575,7 +37575,7 @@
         <v>50000040</v>
       </c>
       <c r="F1878">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G1878">
         <v>275200</v>
@@ -38924,7 +38924,7 @@
         <v>57178841</v>
       </c>
       <c r="F1948">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1949">
@@ -38938,7 +38938,7 @@
         <v>56887918</v>
       </c>
       <c r="F1949">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1950">
@@ -38952,7 +38952,7 @@
         <v>56887895</v>
       </c>
       <c r="F1950">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1951">
@@ -38966,7 +38966,7 @@
         <v>57178901</v>
       </c>
       <c r="F1951">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1952">
@@ -38980,7 +38980,7 @@
         <v>57178772</v>
       </c>
       <c r="F1952">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="1953">
@@ -42167,7 +42167,7 @@
         <v>64111292</v>
       </c>
       <c r="F2122">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2122">
         <v>3617000</v>
@@ -42198,7 +42198,7 @@
         <v>64690629</v>
       </c>
       <c r="F2124">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2124">
         <v>1550000</v>
@@ -42212,7 +42212,7 @@
         <v>64690614</v>
       </c>
       <c r="F2125">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2125">
         <v>1550000</v>
@@ -42226,7 +42226,7 @@
         <v>64690581</v>
       </c>
       <c r="F2126">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2126">
         <v>1550000</v>
@@ -42240,7 +42240,7 @@
         <v>64690544</v>
       </c>
       <c r="F2127">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2127">
         <v>1550000</v>
@@ -42254,7 +42254,7 @@
         <v>64690511</v>
       </c>
       <c r="F2128">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2128">
         <v>1550000</v>
@@ -42557,7 +42557,7 @@
         <v>64428822</v>
       </c>
       <c r="F2146">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2146">
         <v>765450</v>
@@ -42571,7 +42571,7 @@
         <v>64333086</v>
       </c>
       <c r="F2147">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2147">
         <v>2256660</v>
@@ -42585,7 +42585,7 @@
         <v>64333041</v>
       </c>
       <c r="F2148">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2148">
         <v>1128330</v>
@@ -42599,7 +42599,7 @@
         <v>64332133</v>
       </c>
       <c r="F2149">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2149">
         <v>2608200</v>
@@ -42613,7 +42613,7 @@
         <v>64332096</v>
       </c>
       <c r="F2150">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2150">
         <v>1304100</v>
@@ -42627,7 +42627,7 @@
         <v>64331568</v>
       </c>
       <c r="F2151">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2151">
         <v>680400</v>
@@ -42641,7 +42641,7 @@
         <v>64331041</v>
       </c>
       <c r="F2152">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2152">
         <v>1338120</v>
@@ -42655,7 +42655,7 @@
         <v>64329671</v>
       </c>
       <c r="F2153">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2153">
         <v>765450</v>
@@ -42669,7 +42669,7 @@
         <v>64328929</v>
       </c>
       <c r="F2154">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2154">
         <v>1020600</v>
@@ -42683,7 +42683,7 @@
         <v>64328529</v>
       </c>
       <c r="F2155">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2155">
         <v>1020600</v>
@@ -42697,7 +42697,7 @@
         <v>64305454</v>
       </c>
       <c r="F2156">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2156">
         <v>517140</v>
@@ -42711,7 +42711,7 @@
         <v>64305180</v>
       </c>
       <c r="F2157">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2157">
         <v>901530</v>
@@ -42725,7 +42725,7 @@
         <v>64305020</v>
       </c>
       <c r="F2158">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2158">
         <v>561330</v>
@@ -42739,7 +42739,7 @@
         <v>64295538</v>
       </c>
       <c r="F2159">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2159">
         <v>425250</v>
@@ -42753,7 +42753,7 @@
         <v>64295369</v>
       </c>
       <c r="F2160">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2160">
         <v>878850</v>
@@ -42767,7 +42767,7 @@
         <v>64295105</v>
       </c>
       <c r="F2161">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2161">
         <v>561330</v>
@@ -42781,7 +42781,7 @@
         <v>64294796</v>
       </c>
       <c r="F2162">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
       <c r="G2162">
         <v>686070</v>
@@ -43901,7 +43901,7 @@
         <v>68580695</v>
       </c>
       <c r="F2242">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2243">
@@ -43912,7 +43912,7 @@
         <v>68580509</v>
       </c>
       <c r="F2243">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2244">
@@ -43923,7 +43923,7 @@
         <v>68580412</v>
       </c>
       <c r="F2244">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2245">
@@ -43934,7 +43934,7 @@
         <v>68580248</v>
       </c>
       <c r="F2245">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2246">
@@ -43945,7 +43945,7 @@
         <v>68580059</v>
       </c>
       <c r="F2246">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2247">
@@ -43956,7 +43956,7 @@
         <v>68579941</v>
       </c>
       <c r="F2247">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2248">
@@ -43967,7 +43967,7 @@
         <v>68579550</v>
       </c>
       <c r="F2248">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2249">
@@ -43978,7 +43978,7 @@
         <v>68579471</v>
       </c>
       <c r="F2249">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2250">
@@ -43989,7 +43989,7 @@
         <v>68579358</v>
       </c>
       <c r="F2250">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2251">
@@ -44000,7 +44000,7 @@
         <v>68579117</v>
       </c>
       <c r="F2251">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2252">
@@ -44011,7 +44011,7 @@
         <v>68579081</v>
       </c>
       <c r="F2252">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2253">
@@ -44022,7 +44022,7 @@
         <v>68578915</v>
       </c>
       <c r="F2253">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2254">
@@ -44033,7 +44033,7 @@
         <v>68578887</v>
       </c>
       <c r="F2254">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2255">
@@ -44044,7 +44044,7 @@
         <v>68578792</v>
       </c>
       <c r="F2255">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2256">
@@ -44055,7 +44055,7 @@
         <v>68578665</v>
       </c>
       <c r="F2256">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2257">
@@ -44066,7 +44066,7 @@
         <v>68577686</v>
       </c>
       <c r="F2257">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2258">
@@ -44077,7 +44077,7 @@
         <v>68577652</v>
       </c>
       <c r="F2258">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2259">
@@ -44088,7 +44088,7 @@
         <v>68576994</v>
       </c>
       <c r="F2259">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2260">
@@ -44099,7 +44099,7 @@
         <v>68576906</v>
       </c>
       <c r="F2260">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2261">
@@ -44110,7 +44110,7 @@
         <v>68573468</v>
       </c>
       <c r="F2261">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2262">
@@ -44121,7 +44121,7 @@
         <v>68573370</v>
       </c>
       <c r="F2262">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2263">
@@ -44132,7 +44132,7 @@
         <v>68572279</v>
       </c>
       <c r="F2263">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2264">
@@ -44143,7 +44143,7 @@
         <v>68315781</v>
       </c>
       <c r="F2264">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2265">
@@ -44154,7 +44154,7 @@
         <v>68315647</v>
       </c>
       <c r="F2265">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2266">
@@ -44165,7 +44165,7 @@
         <v>68297855</v>
       </c>
       <c r="F2266">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2267">
@@ -44176,7 +44176,7 @@
         <v>68297737</v>
       </c>
       <c r="F2267">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2268">
@@ -44187,7 +44187,7 @@
         <v>68297319</v>
       </c>
       <c r="F2268">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2269">
@@ -44198,7 +44198,7 @@
         <v>68289446</v>
       </c>
       <c r="F2269">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2270">
@@ -44223,7 +44223,7 @@
         <v>55555555</v>
       </c>
       <c r="F2271">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2272">
@@ -44234,7 +44234,7 @@
         <v>55555556</v>
       </c>
       <c r="F2272">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2273">
@@ -44242,7 +44242,7 @@
         <v xml:space="preserve">دستمال مرطوب دافی  Q10 </v>
       </c>
       <c r="F2273">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2274">
@@ -45737,7 +45737,7 @@
         <v>72014008</v>
       </c>
       <c r="F2380">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2381">
@@ -47165,7 +47165,7 @@
         <v>00221240</v>
       </c>
       <c r="F2482">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2483">
@@ -47624,7 +47624,7 @@
         <v>74313106</v>
       </c>
       <c r="F2515">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2516">
@@ -48268,7 +48268,7 @@
         <v>00208009</v>
       </c>
       <c r="F2561">
-        <v>1295000</v>
+        <v>1841000</v>
       </c>
     </row>
     <row r="2562">
@@ -48685,7 +48685,7 @@
         <v>75283541</v>
       </c>
       <c r="F2591">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2592">
@@ -49749,7 +49749,7 @@
         <v>00221806</v>
       </c>
       <c r="F2667">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2668">
@@ -49763,7 +49763,7 @@
         <v>00221807</v>
       </c>
       <c r="F2668">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2669">
@@ -49777,7 +49777,7 @@
         <v>00221808</v>
       </c>
       <c r="F2669">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2670">
@@ -49830,7 +49830,7 @@
         <v>76410461</v>
       </c>
       <c r="F2673">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2674">
@@ -49911,7 +49911,7 @@
         <v>76636716</v>
       </c>
       <c r="F2679">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2680">
@@ -49922,7 +49922,7 @@
         <v>76636706</v>
       </c>
       <c r="F2680">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2681">
@@ -49933,7 +49933,7 @@
         <v>76636688</v>
       </c>
       <c r="F2681">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2682">
@@ -50479,7 +50479,7 @@
         <v>00208020</v>
       </c>
       <c r="F2720">
-        <v>1750000</v>
+        <v>1645000</v>
       </c>
     </row>
     <row r="2721">
@@ -50798,7 +50798,7 @@
         <v>80628922</v>
       </c>
       <c r="F2743">
-        <v>710000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="2744">
@@ -54847,9 +54847,149 @@
         <v>217</v>
       </c>
     </row>
+    <row r="3033">
+      <c r="B3033" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 10</v>
+      </c>
+      <c r="D3033" t="str">
+        <v>83482771</v>
+      </c>
+      <c r="E3033" t="str">
+        <v>00208021</v>
+      </c>
+      <c r="F3033">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="B3034" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 11</v>
+      </c>
+      <c r="D3034" t="str">
+        <v>83533900</v>
+      </c>
+      <c r="E3034" t="str">
+        <v>00208022</v>
+      </c>
+      <c r="F3034">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3035">
+      <c r="B3035" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 12</v>
+      </c>
+      <c r="D3035" t="str">
+        <v>83533919</v>
+      </c>
+      <c r="E3035" t="str">
+        <v>00208023</v>
+      </c>
+      <c r="F3035">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3036">
+      <c r="B3036" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 13</v>
+      </c>
+      <c r="D3036" t="str">
+        <v>83482797</v>
+      </c>
+      <c r="E3036" t="str">
+        <v>00208024</v>
+      </c>
+      <c r="F3036">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3037">
+      <c r="B3037" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 14</v>
+      </c>
+      <c r="D3037" t="str">
+        <v>83482813</v>
+      </c>
+      <c r="E3037" t="str">
+        <v>00208025</v>
+      </c>
+      <c r="F3037">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3038">
+      <c r="B3038" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 15</v>
+      </c>
+      <c r="D3038" t="str">
+        <v>83482849</v>
+      </c>
+      <c r="E3038" t="str">
+        <v>00208026</v>
+      </c>
+      <c r="F3038">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3039">
+      <c r="B3039" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 16</v>
+      </c>
+      <c r="D3039" t="str">
+        <v>83482862</v>
+      </c>
+      <c r="E3039" t="str">
+        <v>00208027</v>
+      </c>
+      <c r="F3039">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3040">
+      <c r="B3040" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 17</v>
+      </c>
+      <c r="D3040" t="str">
+        <v>83482882</v>
+      </c>
+      <c r="E3040" t="str">
+        <v>00208028</v>
+      </c>
+      <c r="F3040">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3041">
+      <c r="B3041" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 18</v>
+      </c>
+      <c r="D3041" t="str">
+        <v>83482889</v>
+      </c>
+      <c r="E3041" t="str">
+        <v>00208029</v>
+      </c>
+      <c r="F3041">
+        <v>120400</v>
+      </c>
+    </row>
+    <row r="3042">
+      <c r="B3042" t="str">
+        <v>رژ لب مایع براق ایلماز شماره 19</v>
+      </c>
+      <c r="D3042" t="str">
+        <v>83533909</v>
+      </c>
+      <c r="E3042" t="str">
+        <v>00208030</v>
+      </c>
+      <c r="F3042">
+        <v>120400</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3032"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3042"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -2125,7 +2125,7 @@
         <v>00221597</v>
       </c>
       <c r="F86">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="87">
@@ -3540,7 +3540,7 @@
         <v>00221559</v>
       </c>
       <c r="F156">
-        <v>3220800</v>
+        <v>257</v>
       </c>
     </row>
     <row r="157">
@@ -6672,7 +6672,7 @@
         <v>00221380</v>
       </c>
       <c r="F300">
-        <v>4036500</v>
+        <v>299</v>
       </c>
     </row>
     <row r="301">
@@ -7012,7 +7012,7 @@
         <v>00221499</v>
       </c>
       <c r="F317">
-        <v>2706000</v>
+        <v>243</v>
       </c>
     </row>
     <row r="318">
@@ -8655,7 +8655,7 @@
         <v>00221436</v>
       </c>
       <c r="F399">
-        <v>123</v>
+        <v>146</v>
       </c>
     </row>
     <row r="400">
@@ -8675,7 +8675,7 @@
         <v>00221435</v>
       </c>
       <c r="F400">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="401">
@@ -8695,7 +8695,7 @@
         <v>00221435</v>
       </c>
       <c r="F401">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="402">
@@ -9455,7 +9455,7 @@
         <v>00221422</v>
       </c>
       <c r="F439">
-        <v>3009600</v>
+        <v>270</v>
       </c>
     </row>
     <row r="440">
@@ -9735,7 +9735,7 @@
         <v>00221071</v>
       </c>
       <c r="F453">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="454">
@@ -9755,7 +9755,7 @@
         <v>00221071</v>
       </c>
       <c r="F454">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="455">
@@ -24345,7 +24345,7 @@
         <v>00221145</v>
       </c>
       <c r="F1209">
-        <v>4301000</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1210">
@@ -25485,7 +25485,7 @@
         <v>00221286</v>
       </c>
       <c r="F1266">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1267">
@@ -27185,7 +27185,7 @@
         <v>00221315</v>
       </c>
       <c r="F1351">
-        <v>1957500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1352">
@@ -27205,7 +27205,7 @@
         <v>00221315</v>
       </c>
       <c r="F1352">
-        <v>1957500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1353">
@@ -27565,7 +27565,7 @@
         <v>00221071</v>
       </c>
       <c r="F1370">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1371">
@@ -27705,7 +27705,7 @@
         <v>00221071</v>
       </c>
       <c r="F1377">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1378">
@@ -39762,7 +39762,7 @@
         <v>00221726</v>
       </c>
       <c r="F1998">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1999">
@@ -40085,7 +40085,7 @@
         <v>00221422</v>
       </c>
       <c r="F2017">
-        <v>3009600</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2018">
@@ -47039,7 +47039,7 @@
         <v>00221435</v>
       </c>
       <c r="F2473">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2474">
@@ -47736,7 +47736,7 @@
         <v>00221071</v>
       </c>
       <c r="F2523">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2524">
@@ -48562,7 +48562,7 @@
         <v>00221286</v>
       </c>
       <c r="F2582">
-        <v>2744500</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2583">
@@ -49301,7 +49301,7 @@
         <v>00221769</v>
       </c>
       <c r="F2635">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2636">
@@ -49721,7 +49721,7 @@
         <v>00221804</v>
       </c>
       <c r="F2665">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2666">
@@ -50171,7 +50171,7 @@
         <v>00221804</v>
       </c>
       <c r="F2698">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2699">
@@ -50395,7 +50395,7 @@
         <v>00221825</v>
       </c>
       <c r="F2714">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2715">

--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3042"/>
+  <dimension ref="A1:G3089"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1665,7 +1665,7 @@
         <v>00221659</v>
       </c>
       <c r="F63">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64">
@@ -2502,7 +2502,7 @@
         <v>45822594</v>
       </c>
       <c r="F105">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="106">
@@ -2519,7 +2519,7 @@
         <v>45822531</v>
       </c>
       <c r="F106">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="107">
@@ -4861,7 +4861,7 @@
         <v>00216003</v>
       </c>
       <c r="F218">
-        <v>970000</v>
+        <v>2210000</v>
       </c>
       <c r="G218">
         <v>1100300</v>
@@ -4907,7 +4907,7 @@
         <v>00216004</v>
       </c>
       <c r="F220">
-        <v>1800000</v>
+        <v>2210000</v>
       </c>
       <c r="G220">
         <v>1100300</v>
@@ -8092,7 +8092,7 @@
         <v>00221450</v>
       </c>
       <c r="F371">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="372">
@@ -8112,7 +8112,7 @@
         <v>00221449</v>
       </c>
       <c r="F372">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="373">
@@ -8415,7 +8415,7 @@
         <v>00221319</v>
       </c>
       <c r="F387">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="388">
@@ -11925,7 +11925,7 @@
         <v>38147716</v>
       </c>
       <c r="F567">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G567">
         <v>35000</v>
@@ -11945,7 +11945,7 @@
         <v>38147321</v>
       </c>
       <c r="F568">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G568">
         <v>35000</v>
@@ -11965,7 +11965,7 @@
         <v>38146217</v>
       </c>
       <c r="F569">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G569">
         <v>35000</v>
@@ -12608,7 +12608,7 @@
         <v>00221084</v>
       </c>
       <c r="F601">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="602">
@@ -12628,7 +12628,7 @@
         <v>00221084</v>
       </c>
       <c r="F602">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="603">
@@ -13968,7 +13968,7 @@
         <v>00221319</v>
       </c>
       <c r="F669">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="670">
@@ -14871,7 +14871,7 @@
         <v>35978635</v>
       </c>
       <c r="F714">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="715">
@@ -14888,7 +14888,7 @@
         <v>35978537</v>
       </c>
       <c r="F715">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="716">
@@ -20202,7 +20202,7 @@
         <v>00221028</v>
       </c>
       <c r="F990">
-        <v>1122000</v>
+        <v>98</v>
       </c>
     </row>
     <row r="991">
@@ -20222,7 +20222,7 @@
         <v>00221028</v>
       </c>
       <c r="F991">
-        <v>1122000</v>
+        <v>98</v>
       </c>
     </row>
     <row r="992">
@@ -20367,7 +20367,7 @@
         <v>34371439</v>
       </c>
       <c r="F999">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1000">
@@ -21362,7 +21362,7 @@
         <v>00221276</v>
       </c>
       <c r="F1051">
-        <v>1144000</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1052">
@@ -24645,7 +24645,7 @@
         <v>00221041</v>
       </c>
       <c r="F1224">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1225">
@@ -24665,7 +24665,7 @@
         <v>00221041</v>
       </c>
       <c r="F1225">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1226">
@@ -24745,7 +24745,7 @@
         <v>00221131</v>
       </c>
       <c r="F1229">
-        <v>4263600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1230">
@@ -24885,7 +24885,7 @@
         <v>00221131</v>
       </c>
       <c r="F1236">
-        <v>4263600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1237">
@@ -25545,7 +25545,7 @@
         <v>00221041</v>
       </c>
       <c r="F1269">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1270">
@@ -26345,7 +26345,7 @@
         <v>00221029</v>
       </c>
       <c r="F1309">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1310">
@@ -26365,7 +26365,7 @@
         <v>00221029</v>
       </c>
       <c r="F1310">
-        <v>1122000</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1311">
@@ -26825,7 +26825,7 @@
         <v>00221131</v>
       </c>
       <c r="F1333">
-        <v>4263600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1334">
@@ -27345,7 +27345,7 @@
         <v>00221226</v>
       </c>
       <c r="F1359">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1360">
@@ -30681,7 +30681,7 @@
         <v>30834962</v>
       </c>
       <c r="F1518">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1519">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="1619">
@@ -33096,7 +33096,7 @@
         <v>55003389</v>
       </c>
       <c r="F1635">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1636">
@@ -34351,7 +34351,7 @@
         <v>48696472</v>
       </c>
       <c r="F1703">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1704">
@@ -34368,7 +34368,7 @@
         <v>48696438</v>
       </c>
       <c r="F1704">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1705">
@@ -34385,7 +34385,7 @@
         <v>48696304</v>
       </c>
       <c r="F1705">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1706">
@@ -34402,7 +34402,7 @@
         <v>48696268</v>
       </c>
       <c r="F1706">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1707">
@@ -34419,7 +34419,7 @@
         <v>48484996</v>
       </c>
       <c r="F1707">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1708">
@@ -34436,7 +34436,7 @@
         <v>48005865</v>
       </c>
       <c r="F1708">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1709">
@@ -34453,7 +34453,7 @@
         <v>48005831</v>
       </c>
       <c r="F1709">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1710">
@@ -34470,7 +34470,7 @@
         <v>48005800</v>
       </c>
       <c r="F1710">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1711">
@@ -34487,7 +34487,7 @@
         <v>48005774</v>
       </c>
       <c r="F1711">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1712">
@@ -34504,7 +34504,7 @@
         <v>48004979</v>
       </c>
       <c r="F1712">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1713">
@@ -34521,7 +34521,7 @@
         <v>48004895</v>
       </c>
       <c r="F1713">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1714">
@@ -34538,7 +34538,7 @@
         <v>48004738</v>
       </c>
       <c r="F1714">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1715">
@@ -34555,7 +34555,7 @@
         <v>49176643</v>
       </c>
       <c r="F1715">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1715">
         <v>974800</v>
@@ -34575,7 +34575,7 @@
         <v>49095632</v>
       </c>
       <c r="F1716">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1716">
         <v>657500</v>
@@ -34595,7 +34595,7 @@
         <v>48005692</v>
       </c>
       <c r="F1717">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1718">
@@ -34612,7 +34612,7 @@
         <v>48805764</v>
       </c>
       <c r="F1718">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1719">
@@ -34629,7 +34629,7 @@
         <v>48499213</v>
       </c>
       <c r="F1719">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1719">
         <v>450000</v>
@@ -34649,7 +34649,7 @@
         <v>48499173</v>
       </c>
       <c r="F1720">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1720">
         <v>1740000</v>
@@ -34669,7 +34669,7 @@
         <v>48483945</v>
       </c>
       <c r="F1721">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1721">
         <v>1740000</v>
@@ -34689,7 +34689,7 @@
         <v>48483874</v>
       </c>
       <c r="F1722">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1722">
         <v>590000</v>
@@ -34709,7 +34709,7 @@
         <v>48483840</v>
       </c>
       <c r="F1723">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1723">
         <v>590000</v>
@@ -34729,7 +34729,7 @@
         <v>47445192</v>
       </c>
       <c r="F1724">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1725">
@@ -34746,7 +34746,7 @@
         <v>47445075</v>
       </c>
       <c r="F1725">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1726">
@@ -34763,7 +34763,7 @@
         <v>44470822</v>
       </c>
       <c r="F1726">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1727">
@@ -34780,7 +34780,7 @@
         <v>43636861</v>
       </c>
       <c r="F1727">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1728">
@@ -36228,7 +36228,7 @@
         <v>111111</v>
       </c>
       <c r="F1806">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1807">
@@ -36693,7 +36693,7 @@
         <v>00216025</v>
       </c>
       <c r="F1833">
-        <v>1440000</v>
+        <v>2230000</v>
       </c>
       <c r="G1833">
         <v>1337000</v>
@@ -36824,7 +36824,7 @@
         <v>56329672</v>
       </c>
       <c r="F1840">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1840">
         <v>275200</v>
@@ -37541,7 +37541,7 @@
         <v>50000020</v>
       </c>
       <c r="F1876">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1876">
         <v>275200</v>
@@ -37558,7 +37558,7 @@
         <v>50000030</v>
       </c>
       <c r="F1877">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1877">
         <v>275200</v>
@@ -37575,7 +37575,7 @@
         <v>50000040</v>
       </c>
       <c r="F1878">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G1878">
         <v>275200</v>
@@ -38924,7 +38924,7 @@
         <v>57178841</v>
       </c>
       <c r="F1948">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1949">
@@ -38938,7 +38938,7 @@
         <v>56887918</v>
       </c>
       <c r="F1949">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1950">
@@ -38952,7 +38952,7 @@
         <v>56887895</v>
       </c>
       <c r="F1950">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1951">
@@ -38966,7 +38966,7 @@
         <v>57178901</v>
       </c>
       <c r="F1951">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1952">
@@ -38980,7 +38980,7 @@
         <v>57178772</v>
       </c>
       <c r="F1952">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="1953">
@@ -39422,7 +39422,7 @@
         <v>00221041</v>
       </c>
       <c r="F1978">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1979">
@@ -39660,7 +39660,7 @@
         <v>00221718</v>
       </c>
       <c r="F1992">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1993">
@@ -42167,7 +42167,7 @@
         <v>64111292</v>
       </c>
       <c r="F2122">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2122">
         <v>3617000</v>
@@ -42198,7 +42198,7 @@
         <v>64690629</v>
       </c>
       <c r="F2124">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2124">
         <v>1550000</v>
@@ -42212,7 +42212,7 @@
         <v>64690614</v>
       </c>
       <c r="F2125">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2125">
         <v>1550000</v>
@@ -42226,7 +42226,7 @@
         <v>64690581</v>
       </c>
       <c r="F2126">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2126">
         <v>1550000</v>
@@ -42240,7 +42240,7 @@
         <v>64690544</v>
       </c>
       <c r="F2127">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2127">
         <v>1550000</v>
@@ -42254,7 +42254,7 @@
         <v>64690511</v>
       </c>
       <c r="F2128">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2128">
         <v>1550000</v>
@@ -42557,7 +42557,7 @@
         <v>64428822</v>
       </c>
       <c r="F2146">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2146">
         <v>765450</v>
@@ -42571,7 +42571,7 @@
         <v>64333086</v>
       </c>
       <c r="F2147">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2147">
         <v>2256660</v>
@@ -42585,7 +42585,7 @@
         <v>64333041</v>
       </c>
       <c r="F2148">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2148">
         <v>1128330</v>
@@ -42599,7 +42599,7 @@
         <v>64332133</v>
       </c>
       <c r="F2149">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2149">
         <v>2608200</v>
@@ -42613,7 +42613,7 @@
         <v>64332096</v>
       </c>
       <c r="F2150">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2150">
         <v>1304100</v>
@@ -42627,7 +42627,7 @@
         <v>64331568</v>
       </c>
       <c r="F2151">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2151">
         <v>680400</v>
@@ -42641,7 +42641,7 @@
         <v>64331041</v>
       </c>
       <c r="F2152">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2152">
         <v>1338120</v>
@@ -42655,7 +42655,7 @@
         <v>64329671</v>
       </c>
       <c r="F2153">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2153">
         <v>765450</v>
@@ -42669,7 +42669,7 @@
         <v>64328929</v>
       </c>
       <c r="F2154">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2154">
         <v>1020600</v>
@@ -42683,7 +42683,7 @@
         <v>64328529</v>
       </c>
       <c r="F2155">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2155">
         <v>1020600</v>
@@ -42697,7 +42697,7 @@
         <v>64305454</v>
       </c>
       <c r="F2156">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2156">
         <v>517140</v>
@@ -42711,7 +42711,7 @@
         <v>64305180</v>
       </c>
       <c r="F2157">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2157">
         <v>901530</v>
@@ -42725,7 +42725,7 @@
         <v>64305020</v>
       </c>
       <c r="F2158">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2158">
         <v>561330</v>
@@ -42739,7 +42739,7 @@
         <v>64295538</v>
       </c>
       <c r="F2159">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2159">
         <v>425250</v>
@@ -42753,7 +42753,7 @@
         <v>64295369</v>
       </c>
       <c r="F2160">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2160">
         <v>878850</v>
@@ -42767,7 +42767,7 @@
         <v>64295105</v>
       </c>
       <c r="F2161">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2161">
         <v>561330</v>
@@ -42781,7 +42781,7 @@
         <v>64294796</v>
       </c>
       <c r="F2162">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
       <c r="G2162">
         <v>686070</v>
@@ -43901,7 +43901,7 @@
         <v>68580695</v>
       </c>
       <c r="F2242">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2243">
@@ -43912,7 +43912,7 @@
         <v>68580509</v>
       </c>
       <c r="F2243">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2244">
@@ -43923,7 +43923,7 @@
         <v>68580412</v>
       </c>
       <c r="F2244">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2245">
@@ -43934,7 +43934,7 @@
         <v>68580248</v>
       </c>
       <c r="F2245">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2246">
@@ -43945,7 +43945,7 @@
         <v>68580059</v>
       </c>
       <c r="F2246">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2247">
@@ -43956,7 +43956,7 @@
         <v>68579941</v>
       </c>
       <c r="F2247">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2248">
@@ -43967,7 +43967,7 @@
         <v>68579550</v>
       </c>
       <c r="F2248">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2249">
@@ -43978,7 +43978,7 @@
         <v>68579471</v>
       </c>
       <c r="F2249">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2250">
@@ -43989,7 +43989,7 @@
         <v>68579358</v>
       </c>
       <c r="F2250">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2251">
@@ -44000,7 +44000,7 @@
         <v>68579117</v>
       </c>
       <c r="F2251">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2252">
@@ -44011,7 +44011,7 @@
         <v>68579081</v>
       </c>
       <c r="F2252">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2253">
@@ -44022,7 +44022,7 @@
         <v>68578915</v>
       </c>
       <c r="F2253">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2254">
@@ -44033,7 +44033,7 @@
         <v>68578887</v>
       </c>
       <c r="F2254">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2255">
@@ -44044,7 +44044,7 @@
         <v>68578792</v>
       </c>
       <c r="F2255">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2256">
@@ -44055,7 +44055,7 @@
         <v>68578665</v>
       </c>
       <c r="F2256">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2257">
@@ -44066,7 +44066,7 @@
         <v>68577686</v>
       </c>
       <c r="F2257">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2258">
@@ -44077,7 +44077,7 @@
         <v>68577652</v>
       </c>
       <c r="F2258">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2259">
@@ -44088,7 +44088,7 @@
         <v>68576994</v>
       </c>
       <c r="F2259">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2260">
@@ -44099,7 +44099,7 @@
         <v>68576906</v>
       </c>
       <c r="F2260">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2261">
@@ -44110,7 +44110,7 @@
         <v>68573468</v>
       </c>
       <c r="F2261">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2262">
@@ -44121,7 +44121,7 @@
         <v>68573370</v>
       </c>
       <c r="F2262">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2263">
@@ -44132,7 +44132,7 @@
         <v>68572279</v>
       </c>
       <c r="F2263">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2264">
@@ -44143,7 +44143,7 @@
         <v>68315781</v>
       </c>
       <c r="F2264">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2265">
@@ -44154,7 +44154,7 @@
         <v>68315647</v>
       </c>
       <c r="F2265">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2266">
@@ -44165,7 +44165,7 @@
         <v>68297855</v>
       </c>
       <c r="F2266">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2267">
@@ -44176,7 +44176,7 @@
         <v>68297737</v>
       </c>
       <c r="F2267">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2268">
@@ -44187,7 +44187,7 @@
         <v>68297319</v>
       </c>
       <c r="F2268">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2269">
@@ -44198,7 +44198,7 @@
         <v>68289446</v>
       </c>
       <c r="F2269">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2270">
@@ -44223,7 +44223,7 @@
         <v>55555555</v>
       </c>
       <c r="F2271">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2272">
@@ -44234,7 +44234,7 @@
         <v>55555556</v>
       </c>
       <c r="F2272">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2273">
@@ -44242,7 +44242,7 @@
         <v xml:space="preserve">دستمال مرطوب دافی  Q10 </v>
       </c>
       <c r="F2273">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2274">
@@ -45737,7 +45737,7 @@
         <v>72014008</v>
       </c>
       <c r="F2380">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2381">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2430">
@@ -46969,7 +46969,7 @@
         <v>00221131</v>
       </c>
       <c r="F2468">
-        <v>4263600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2469">
@@ -47081,7 +47081,7 @@
         <v>00221449</v>
       </c>
       <c r="F2476">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2477">
@@ -47417,7 +47417,7 @@
         <v>00221450</v>
       </c>
       <c r="F2500">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2501">
@@ -47624,7 +47624,7 @@
         <v>74313106</v>
       </c>
       <c r="F2515">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2516">
@@ -47904,7 +47904,7 @@
         <v>00221084</v>
       </c>
       <c r="F2535">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2536">
@@ -48685,7 +48685,7 @@
         <v>75283541</v>
       </c>
       <c r="F2591">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2592">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2618">
@@ -49343,7 +49343,7 @@
         <v>00221772</v>
       </c>
       <c r="F2638">
-        <v>1</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2639">
@@ -49735,7 +49735,7 @@
         <v>00221805</v>
       </c>
       <c r="F2666">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2667">
@@ -49830,7 +49830,7 @@
         <v>76410461</v>
       </c>
       <c r="F2673">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2674">
@@ -49911,7 +49911,7 @@
         <v>76636716</v>
       </c>
       <c r="F2679">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2680">
@@ -49922,7 +49922,7 @@
         <v>76636706</v>
       </c>
       <c r="F2680">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2681">
@@ -49933,7 +49933,7 @@
         <v>76636688</v>
       </c>
       <c r="F2681">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2682">
@@ -50185,7 +50185,7 @@
         <v>00221805</v>
       </c>
       <c r="F2699">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2700">
@@ -50773,7 +50773,7 @@
         <v>00221844</v>
       </c>
       <c r="F2741">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2742">
@@ -50798,7 +50798,7 @@
         <v>80628922</v>
       </c>
       <c r="F2743">
-        <v>1700000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="2744">
@@ -54987,9 +54987,667 @@
         <v>120400</v>
       </c>
     </row>
+    <row r="3043">
+      <c r="B3043" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل VLVT شماره 01 رنگ قهوه ای نود</v>
+      </c>
+      <c r="D3043" t="str">
+        <v>84179732</v>
+      </c>
+      <c r="E3043" t="str">
+        <v>00221033</v>
+      </c>
+      <c r="F3043">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3044">
+      <c r="B3044" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل VLVT شماره 39 رنگ صورتی قهوه ای</v>
+      </c>
+      <c r="D3044" t="str">
+        <v>84191529</v>
+      </c>
+      <c r="E3044" t="str">
+        <v>00221050</v>
+      </c>
+      <c r="F3044">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3045">
+      <c r="B3045" t="str">
+        <v>پرایمر مژه گلدن رز مدل فرچه ای</v>
+      </c>
+      <c r="D3045" t="str">
+        <v>83750991</v>
+      </c>
+      <c r="E3045" t="str">
+        <v>00221058</v>
+      </c>
+      <c r="F3045">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3046">
+      <c r="B3046" t="str">
+        <v>مداد لب گلدن رس مدل DRM شماره 530 رنگ آلویی تیره</v>
+      </c>
+      <c r="D3046" t="str">
+        <v>84191813</v>
+      </c>
+      <c r="E3046" t="str">
+        <v>00221237</v>
+      </c>
+      <c r="F3046">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3047">
+      <c r="B3047" t="str">
+        <v>مداد چشم گلدن رس مدل DRM شماره 407 رنگ قهوه ای شکلاتی</v>
+      </c>
+      <c r="D3047" t="str">
+        <v>84151648</v>
+      </c>
+      <c r="E3047" t="str">
+        <v>00221255</v>
+      </c>
+      <c r="F3047">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3048">
+      <c r="B3048" t="str">
+        <v>رژ لب مایع مات گلدن رس مدل MM LPNG شماره 05 رنگ رز مرجانی</v>
+      </c>
+      <c r="D3048" t="str">
+        <v>84191964</v>
+      </c>
+      <c r="E3048" t="str">
+        <v>00221283</v>
+      </c>
+      <c r="F3048">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3049">
+      <c r="B3049" t="str">
+        <v>پالت هایلایتر گلدن رس مدل STRBNG شماره 01</v>
+      </c>
+      <c r="D3049" t="str">
+        <v>84186287</v>
+      </c>
+      <c r="E3049" t="str">
+        <v>00221294</v>
+      </c>
+      <c r="F3049">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3050">
+      <c r="B3050" t="str">
+        <v>رژ لب مدادی مات گلدن رس مدل CRYN شماره 11 رنگ رز قهوه ای</v>
+      </c>
+      <c r="D3050" t="str">
+        <v>84191103</v>
+      </c>
+      <c r="E3050" t="str">
+        <v>00221305</v>
+      </c>
+      <c r="F3050">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3051">
+      <c r="B3051" t="str">
+        <v>رژ لب مدادی مات گلدن رس مدل CRYN شماره 13 رنگ رز آجری</v>
+      </c>
+      <c r="D3051" t="str">
+        <v>84192099</v>
+      </c>
+      <c r="E3051" t="str">
+        <v>00221306</v>
+      </c>
+      <c r="F3051">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3052">
+      <c r="B3052" t="str">
+        <v>رژ لب مدادی مات گلدن رس مدل CRYN شماره 16 رنگ قرمز گیلاسی</v>
+      </c>
+      <c r="D3052" t="str">
+        <v>84191880</v>
+      </c>
+      <c r="E3052" t="str">
+        <v>00221309</v>
+      </c>
+      <c r="F3052">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3053">
+      <c r="B3053" t="str">
+        <v>خط چشم ماژیکی گلدن رس مدل DPLN شماره 01 رنگ مشکی</v>
+      </c>
+      <c r="D3053" t="str">
+        <v>84191393</v>
+      </c>
+      <c r="E3053" t="str">
+        <v>00221359</v>
+      </c>
+      <c r="F3053">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3054">
+      <c r="B3054" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل STN شماره 09 رنگ رز ماو</v>
+      </c>
+      <c r="D3054" t="str">
+        <v>84191459</v>
+      </c>
+      <c r="E3054" t="str">
+        <v>00221379</v>
+      </c>
+      <c r="F3054">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3055">
+      <c r="B3055" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل STN شماره 10 رنگ رز تمشکی</v>
+      </c>
+      <c r="D3055" t="str">
+        <v>84191315</v>
+      </c>
+      <c r="E3055" t="str">
+        <v>00221381</v>
+      </c>
+      <c r="F3055">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3056">
+      <c r="B3056" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل STN شماره 11 رنگ رز بری</v>
+      </c>
+      <c r="D3056" t="str">
+        <v>84192193</v>
+      </c>
+      <c r="E3056" t="str">
+        <v>00221382</v>
+      </c>
+      <c r="F3056">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3057">
+      <c r="B3057" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل STN شماره 24 رنگ قرمز آجری</v>
+      </c>
+      <c r="D3057" t="str">
+        <v>84191721</v>
+      </c>
+      <c r="E3057" t="str">
+        <v>00221390</v>
+      </c>
+      <c r="F3057">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3058">
+      <c r="B3058" t="str">
+        <v>رژ لب مدادی مات گلدن رس مدل CRYN شماره 12 رنگ رز چرک</v>
+      </c>
+      <c r="D3058" t="str">
+        <v>84190372</v>
+      </c>
+      <c r="E3058" t="str">
+        <v>00221394</v>
+      </c>
+      <c r="F3058">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="B3059" t="str">
+        <v>مداد لب گلدن رس مدل DRM شماره 533 رنگ زرشکی</v>
+      </c>
+      <c r="D3059" t="str">
+        <v>84182973</v>
+      </c>
+      <c r="E3059" t="str">
+        <v>00221434</v>
+      </c>
+      <c r="F3059">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3060">
+      <c r="B3060" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل STN شماره 03 رنگ نود دارچینی</v>
+      </c>
+      <c r="D3060" t="str">
+        <v>84189633</v>
+      </c>
+      <c r="E3060" t="str">
+        <v>00221481</v>
+      </c>
+      <c r="F3060">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3061">
+      <c r="B3061" t="str">
+        <v>مداد چشم گلدن رس مدل DRM شماره 406 رنگ قهوه ای اسپرسو</v>
+      </c>
+      <c r="D3061" t="str">
+        <v>84153193</v>
+      </c>
+      <c r="E3061" t="str">
+        <v>00221667</v>
+      </c>
+      <c r="F3061">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3062">
+      <c r="B3062" t="str">
+        <v>مداد چشم گلدن رس مدل DRM شماره 409 رنگ قهوه ای دارچینی</v>
+      </c>
+      <c r="D3062" t="str">
+        <v>84153298</v>
+      </c>
+      <c r="E3062" t="str">
+        <v>00221668</v>
+      </c>
+      <c r="F3062">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3063">
+      <c r="B3063" t="str">
+        <v>مداد چشم گلدن رس مدل DRM شماره 410 رنگ قهوه ای موکا</v>
+      </c>
+      <c r="D3063" t="str">
+        <v>84153157</v>
+      </c>
+      <c r="E3063" t="str">
+        <v>00221669</v>
+      </c>
+      <c r="F3063">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3064">
+      <c r="B3064" t="str">
+        <v>صابون ابرو گلدن رس مدل WXD به همراه برس ابرو</v>
+      </c>
+      <c r="D3064" t="str">
+        <v>84184664</v>
+      </c>
+      <c r="E3064" t="str">
+        <v>00221693</v>
+      </c>
+      <c r="F3064">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3065">
+      <c r="B3065" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل  Sweet Kiss شماره 05 رنگ موکا</v>
+      </c>
+      <c r="D3065" t="str">
+        <v>84188505</v>
+      </c>
+      <c r="E3065" t="str">
+        <v>00221809</v>
+      </c>
+      <c r="F3065">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3066">
+      <c r="B3066" t="str">
+        <v>مداد لب گلدن رس مدل DRM شماره 542 رنگ قرمز صورتی</v>
+      </c>
+      <c r="D3066" t="str">
+        <v>84192305</v>
+      </c>
+      <c r="E3066" t="str">
+        <v>00221844</v>
+      </c>
+      <c r="F3066">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3067">
+      <c r="B3067" t="str">
+        <v>ریمل ضد آب حجم دهنده گلدن رس مدل Burgandy</v>
+      </c>
+      <c r="D3067" t="str">
+        <v>84150580</v>
+      </c>
+      <c r="E3067" t="str">
+        <v>00221880</v>
+      </c>
+      <c r="F3067">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3068">
+      <c r="B3068" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل GLMY شماره 201 رنگ نود رز قهوه ای</v>
+      </c>
+      <c r="D3068" t="str">
+        <v>84178577</v>
+      </c>
+      <c r="E3068" t="str">
+        <v>00221894</v>
+      </c>
+      <c r="F3068">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3069">
+      <c r="B3069" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل GLMY شماره 202 رنگ نود آجری</v>
+      </c>
+      <c r="D3069" t="str">
+        <v>84185746</v>
+      </c>
+      <c r="E3069" t="str">
+        <v>00221895</v>
+      </c>
+      <c r="F3069">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3070">
+      <c r="B3070" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل GLMY شماره 203 رنگ رز وود</v>
+      </c>
+      <c r="D3070" t="str">
+        <v>84184111</v>
+      </c>
+      <c r="E3070" t="str">
+        <v>00221896</v>
+      </c>
+      <c r="F3070">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3071">
+      <c r="B3071" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل GLMY شماره 204 رنگ صورتی رز</v>
+      </c>
+      <c r="D3071" t="str">
+        <v>84178043</v>
+      </c>
+      <c r="E3071" t="str">
+        <v>00221897</v>
+      </c>
+      <c r="F3071">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3072">
+      <c r="B3072" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل GLMY شماره 205 رنگ مرجانی نئونی</v>
+      </c>
+      <c r="D3072" t="str">
+        <v>84191673</v>
+      </c>
+      <c r="E3072" t="str">
+        <v>00221898</v>
+      </c>
+      <c r="F3072">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3073">
+      <c r="B3073" t="str">
+        <v>لیپ گلاس براق گلدن رس مدل GLMY شماره 206 رنگ زرشکی آلبالویی</v>
+      </c>
+      <c r="D3073" t="str">
+        <v>84191841</v>
+      </c>
+      <c r="E3073" t="str">
+        <v>00221899</v>
+      </c>
+      <c r="F3073">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3074">
+      <c r="B3074" t="str">
+        <v>مداد داخل چشم پیچی گلدن رز مدل MATIC رنگ قهوه ای شماره 207</v>
+      </c>
+      <c r="D3074" t="str">
+        <v>82076666</v>
+      </c>
+      <c r="E3074" t="str">
+        <v>00221910</v>
+      </c>
+      <c r="F3074">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="B3075" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny شماره 01 رنگ قهوه ای دارچینی</v>
+      </c>
+      <c r="D3075" t="str">
+        <v>84187305</v>
+      </c>
+      <c r="E3075" t="str">
+        <v>00221959</v>
+      </c>
+      <c r="F3075">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3076">
+      <c r="B3076" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny شماره 02 رنگ قهوه ای دارچینی</v>
+      </c>
+      <c r="D3076" t="str">
+        <v>84181480</v>
+      </c>
+      <c r="E3076" t="str">
+        <v>00221960</v>
+      </c>
+      <c r="F3076">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3077">
+      <c r="B3077" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny شماره 03 رنگ رز آجری</v>
+      </c>
+      <c r="D3077" t="str">
+        <v>84177701</v>
+      </c>
+      <c r="E3077" t="str">
+        <v>00221961</v>
+      </c>
+      <c r="F3077">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3078">
+      <c r="B3078" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny Matte شماره 04 رنگ رز آجری</v>
+      </c>
+      <c r="D3078" t="str">
+        <v>84179150</v>
+      </c>
+      <c r="E3078" t="str">
+        <v>00221962</v>
+      </c>
+      <c r="F3078">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3079">
+      <c r="B3079" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny Matte شماره 05 رنگ رز آجری</v>
+      </c>
+      <c r="D3079" t="str">
+        <v>84180773</v>
+      </c>
+      <c r="E3079" t="str">
+        <v>00221963</v>
+      </c>
+      <c r="F3079">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3080">
+      <c r="B3080" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny شماره 06 رنگ هلویی کهربایی</v>
+      </c>
+      <c r="D3080" t="str">
+        <v>84188008</v>
+      </c>
+      <c r="E3080" t="str">
+        <v>00221964</v>
+      </c>
+      <c r="F3080">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="B3081" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny Matte شماره 07 رنگ سرخابی</v>
+      </c>
+      <c r="D3081" t="str">
+        <v>84186857</v>
+      </c>
+      <c r="E3081" t="str">
+        <v>00221965</v>
+      </c>
+      <c r="F3081">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="B3082" t="str">
+        <v>رژ لب جامد مات گلدن رس مدل Satiny شماره 08 رنگ قرمز آبنباتی</v>
+      </c>
+      <c r="D3082" t="str">
+        <v>84153258</v>
+      </c>
+      <c r="E3082" t="str">
+        <v>00221966</v>
+      </c>
+      <c r="F3082">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="B3083" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل SILKY SHINE HYDRATING رنگ کرم قهوه ای شماره 204</v>
+      </c>
+      <c r="D3083" t="str">
+        <v>83879111</v>
+      </c>
+      <c r="E3083" t="str">
+        <v>00221967</v>
+      </c>
+      <c r="F3083">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="B3084" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل SILKY SHINE HYDRATINGE رنگ کرم کالباسی شماره 206</v>
+      </c>
+      <c r="D3084" t="str">
+        <v>83879101</v>
+      </c>
+      <c r="E3084" t="str">
+        <v>00221968</v>
+      </c>
+      <c r="F3084">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="B3085" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل SILKY SHINE HYDRATING رنگ کرم کالباسی شماره 208</v>
+      </c>
+      <c r="D3085" t="str">
+        <v>83879097</v>
+      </c>
+      <c r="E3085" t="str">
+        <v>00221969</v>
+      </c>
+      <c r="F3085">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="B3086" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل SILKY SHINE HYDRATING رنگ قهوه ای شماره 217</v>
+      </c>
+      <c r="D3086" t="str">
+        <v>83879076</v>
+      </c>
+      <c r="E3086" t="str">
+        <v>00221970</v>
+      </c>
+      <c r="F3086">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="B3087" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل SILKY SHINE HYDRATING رنگ قهوه ای شماره 221</v>
+      </c>
+      <c r="D3087" t="str">
+        <v>83879065</v>
+      </c>
+      <c r="E3087" t="str">
+        <v>00221971</v>
+      </c>
+      <c r="F3087">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="B3088" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل LKSILKY SHINE HYDRATING رنگ قهوه ای شماره 222</v>
+      </c>
+      <c r="D3088" t="str">
+        <v>83879047</v>
+      </c>
+      <c r="E3088" t="str">
+        <v>00221972</v>
+      </c>
+      <c r="F3088">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="B3089" t="str">
+        <v>رژ لب جامد براق گلدن رز مدل SILKY SHINE HYDRATING رنگ زرشکی شماره 224</v>
+      </c>
+      <c r="D3089" t="str">
+        <v>83879015</v>
+      </c>
+      <c r="E3089" t="str">
+        <v>00221973</v>
+      </c>
+      <c r="F3089">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3042"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3089"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/model/data/buy-price.xlsx
+++ b/model/data/buy-price.xlsx
@@ -599,7 +599,7 @@
         <v>00221668</v>
       </c>
       <c r="F10">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -2502,7 +2502,7 @@
         <v>45822594</v>
       </c>
       <c r="F105">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="106">
@@ -2519,7 +2519,7 @@
         <v>45822531</v>
       </c>
       <c r="F106">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="107">
@@ -3920,7 +3920,7 @@
         <v>00221573</v>
       </c>
       <c r="F175">
-        <v>2222000</v>
+        <v>299</v>
       </c>
     </row>
     <row r="176">
@@ -6772,7 +6772,7 @@
         <v>00221508</v>
       </c>
       <c r="F305">
-        <v>2084500</v>
+        <v>177</v>
       </c>
     </row>
     <row r="306">
@@ -6852,7 +6852,7 @@
         <v>00221502</v>
       </c>
       <c r="F309">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="310">
@@ -6912,7 +6912,7 @@
         <v>00221503</v>
       </c>
       <c r="F312">
-        <v>2046000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="313">
@@ -7752,7 +7752,7 @@
         <v>00221466</v>
       </c>
       <c r="F354">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="355">
@@ -7812,7 +7812,7 @@
         <v>00221463</v>
       </c>
       <c r="F357">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="358">
@@ -8215,7 +8215,7 @@
         <v>00221299</v>
       </c>
       <c r="F377">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="378">
@@ -9695,7 +9695,7 @@
         <v>00221408</v>
       </c>
       <c r="F451">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="452">
@@ -9975,7 +9975,7 @@
         <v>00221007</v>
       </c>
       <c r="F465">
-        <v>1705000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="466">
@@ -11925,7 +11925,7 @@
         <v>38147716</v>
       </c>
       <c r="F567">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G567">
         <v>35000</v>
@@ -11945,7 +11945,7 @@
         <v>38147321</v>
       </c>
       <c r="F568">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G568">
         <v>35000</v>
@@ -11965,7 +11965,7 @@
         <v>38146217</v>
       </c>
       <c r="F569">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G569">
         <v>35000</v>
@@ -13268,7 +13268,7 @@
         <v>00221236</v>
       </c>
       <c r="F634">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="635">
@@ -13588,7 +13588,7 @@
         <v>00221408</v>
       </c>
       <c r="F650">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="651">
@@ -14248,7 +14248,7 @@
         <v>00221050</v>
       </c>
       <c r="F683">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="684">
@@ -14268,7 +14268,7 @@
         <v>00221050</v>
       </c>
       <c r="F684">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="685">
@@ -14871,7 +14871,7 @@
         <v>35978635</v>
       </c>
       <c r="F714">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="715">
@@ -14888,7 +14888,7 @@
         <v>35978537</v>
       </c>
       <c r="F715">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="716">
@@ -20367,7 +20367,7 @@
         <v>34371439</v>
       </c>
       <c r="F999">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1000">
@@ -24825,7 +24825,7 @@
         <v>00221295</v>
       </c>
       <c r="F1233">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1234">
@@ -25245,7 +25245,7 @@
         <v>00221224</v>
       </c>
       <c r="F1254">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1255">
@@ -25665,7 +25665,7 @@
         <v>00221299</v>
       </c>
       <c r="F1275">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1276">
@@ -25705,7 +25705,7 @@
         <v>00221224</v>
       </c>
       <c r="F1277">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1278">
@@ -26125,7 +26125,7 @@
         <v>00221339</v>
       </c>
       <c r="F1298">
-        <v>6534000</v>
+        <v>534</v>
       </c>
     </row>
     <row r="1299">
@@ -26505,7 +26505,7 @@
         <v>00221007</v>
       </c>
       <c r="F1317">
-        <v>1705000</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1318">
@@ -26845,7 +26845,7 @@
         <v>00221317</v>
       </c>
       <c r="F1334">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1335">
@@ -26865,7 +26865,7 @@
         <v>00221317</v>
       </c>
       <c r="F1335">
-        <v>1611500</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1336">
@@ -28201,7 +28201,7 @@
         <v>00221332</v>
       </c>
       <c r="F1400">
-        <v>2151600</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1401">
@@ -29635,7 +29635,7 @@
         <v>00221331</v>
       </c>
       <c r="F1466">
-        <v>2151600</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1467">
@@ -30681,7 +30681,7 @@
         <v>30834962</v>
       </c>
       <c r="F1518">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1519">
@@ -32753,7 +32753,7 @@
         <v>00221001</v>
       </c>
       <c r="F1618">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1619">
@@ -33096,7 +33096,7 @@
         <v>55003389</v>
       </c>
       <c r="F1635">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1636">
@@ -34351,7 +34351,7 @@
         <v>48696472</v>
       </c>
       <c r="F1703">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1704">
@@ -34368,7 +34368,7 @@
         <v>48696438</v>
       </c>
       <c r="F1704">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1705">
@@ -34385,7 +34385,7 @@
         <v>48696304</v>
       </c>
       <c r="F1705">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1706">
@@ -34402,7 +34402,7 @@
         <v>48696268</v>
       </c>
       <c r="F1706">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1707">
@@ -34419,7 +34419,7 @@
         <v>48484996</v>
       </c>
       <c r="F1707">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1708">
@@ -34436,7 +34436,7 @@
         <v>48005865</v>
       </c>
       <c r="F1708">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1709">
@@ -34453,7 +34453,7 @@
         <v>48005831</v>
       </c>
       <c r="F1709">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1710">
@@ -34470,7 +34470,7 @@
         <v>48005800</v>
       </c>
       <c r="F1710">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1711">
@@ -34487,7 +34487,7 @@
         <v>48005774</v>
       </c>
       <c r="F1711">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1712">
@@ -34504,7 +34504,7 @@
         <v>48004979</v>
       </c>
       <c r="F1712">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1713">
@@ -34521,7 +34521,7 @@
         <v>48004895</v>
       </c>
       <c r="F1713">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1714">
@@ -34538,7 +34538,7 @@
         <v>48004738</v>
       </c>
       <c r="F1714">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1715">
@@ -34555,7 +34555,7 @@
         <v>49176643</v>
       </c>
       <c r="F1715">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1715">
         <v>974800</v>
@@ -34575,7 +34575,7 @@
         <v>49095632</v>
       </c>
       <c r="F1716">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1716">
         <v>657500</v>
@@ -34595,7 +34595,7 @@
         <v>48005692</v>
       </c>
       <c r="F1717">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1718">
@@ -34612,7 +34612,7 @@
         <v>48805764</v>
       </c>
       <c r="F1718">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1719">
@@ -34629,7 +34629,7 @@
         <v>48499213</v>
       </c>
       <c r="F1719">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1719">
         <v>450000</v>
@@ -34649,7 +34649,7 @@
         <v>48499173</v>
       </c>
       <c r="F1720">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1720">
         <v>1740000</v>
@@ -34669,7 +34669,7 @@
         <v>48483945</v>
       </c>
       <c r="F1721">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1721">
         <v>1740000</v>
@@ -34689,7 +34689,7 @@
         <v>48483874</v>
       </c>
       <c r="F1722">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1722">
         <v>590000</v>
@@ -34709,7 +34709,7 @@
         <v>48483840</v>
       </c>
       <c r="F1723">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1723">
         <v>590000</v>
@@ -34729,7 +34729,7 @@
         <v>47445192</v>
       </c>
       <c r="F1724">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1725">
@@ -34746,7 +34746,7 @@
         <v>47445075</v>
       </c>
       <c r="F1725">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1726">
@@ -34763,7 +34763,7 @@
         <v>44470822</v>
       </c>
       <c r="F1726">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1727">
@@ -34780,7 +34780,7 @@
         <v>43636861</v>
       </c>
       <c r="F1727">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1728">
@@ -36228,7 +36228,7 @@
         <v>111111</v>
       </c>
       <c r="F1806">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1807">
@@ -36810,7 +36810,7 @@
         <v>00221078</v>
       </c>
       <c r="F1839">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1840">
@@ -36824,7 +36824,7 @@
         <v>56329672</v>
       </c>
       <c r="F1840">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1840">
         <v>275200</v>
@@ -37541,7 +37541,7 @@
         <v>50000020</v>
       </c>
       <c r="F1876">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1876">
         <v>275200</v>
@@ -37558,7 +37558,7 @@
         <v>50000030</v>
       </c>
       <c r="F1877">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1877">
         <v>275200</v>
@@ -37575,7 +37575,7 @@
         <v>50000040</v>
       </c>
       <c r="F1878">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G1878">
         <v>275200</v>
@@ -38115,7 +38115,7 @@
         <v>221078</v>
       </c>
       <c r="F1905">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1906">
@@ -38175,7 +38175,7 @@
         <v>221052</v>
       </c>
       <c r="F1908">
-        <v>2362500</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1909">
@@ -38215,7 +38215,7 @@
         <v>221249</v>
       </c>
       <c r="F1910">
-        <v>984500</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1911">
@@ -38924,7 +38924,7 @@
         <v>57178841</v>
       </c>
       <c r="F1948">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1949">
@@ -38938,7 +38938,7 @@
         <v>56887918</v>
       </c>
       <c r="F1949">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1950">
@@ -38952,7 +38952,7 @@
         <v>56887895</v>
       </c>
       <c r="F1950">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1951">
@@ -38966,7 +38966,7 @@
         <v>57178901</v>
       </c>
       <c r="F1951">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1952">
@@ -38980,7 +38980,7 @@
         <v>57178772</v>
       </c>
       <c r="F1952">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1953">
@@ -39184,7 +39184,7 @@
         <v>00221466</v>
       </c>
       <c r="F1964">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1965">
@@ -39677,7 +39677,7 @@
         <v>00221719</v>
       </c>
       <c r="F1993">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1994">
@@ -42167,7 +42167,7 @@
         <v>64111292</v>
       </c>
       <c r="F2122">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2122">
         <v>3617000</v>
@@ -42198,7 +42198,7 @@
         <v>64690629</v>
       </c>
       <c r="F2124">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2124">
         <v>1550000</v>
@@ -42212,7 +42212,7 @@
         <v>64690614</v>
       </c>
       <c r="F2125">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2125">
         <v>1550000</v>
@@ -42226,7 +42226,7 @@
         <v>64690581</v>
       </c>
       <c r="F2126">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2126">
         <v>1550000</v>
@@ -42240,7 +42240,7 @@
         <v>64690544</v>
       </c>
       <c r="F2127">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2127">
         <v>1550000</v>
@@ -42254,7 +42254,7 @@
         <v>64690511</v>
       </c>
       <c r="F2128">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2128">
         <v>1550000</v>
@@ -42557,7 +42557,7 @@
         <v>64428822</v>
       </c>
       <c r="F2146">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2146">
         <v>765450</v>
@@ -42571,7 +42571,7 @@
         <v>64333086</v>
       </c>
       <c r="F2147">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2147">
         <v>2256660</v>
@@ -42585,7 +42585,7 @@
         <v>64333041</v>
       </c>
       <c r="F2148">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2148">
         <v>1128330</v>
@@ -42599,7 +42599,7 @@
         <v>64332133</v>
       </c>
       <c r="F2149">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2149">
         <v>2608200</v>
@@ -42613,7 +42613,7 @@
         <v>64332096</v>
       </c>
       <c r="F2150">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2150">
         <v>1304100</v>
@@ -42627,7 +42627,7 @@
         <v>64331568</v>
       </c>
       <c r="F2151">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2151">
         <v>680400</v>
@@ -42641,7 +42641,7 @@
         <v>64331041</v>
       </c>
       <c r="F2152">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2152">
         <v>1338120</v>
@@ -42655,7 +42655,7 @@
         <v>64329671</v>
       </c>
       <c r="F2153">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2153">
         <v>765450</v>
@@ -42669,7 +42669,7 @@
         <v>64328929</v>
       </c>
       <c r="F2154">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2154">
         <v>1020600</v>
@@ -42683,7 +42683,7 @@
         <v>64328529</v>
       </c>
       <c r="F2155">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2155">
         <v>1020600</v>
@@ -42697,7 +42697,7 @@
         <v>64305454</v>
       </c>
       <c r="F2156">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2156">
         <v>517140</v>
@@ -42711,7 +42711,7 @@
         <v>64305180</v>
       </c>
       <c r="F2157">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2157">
         <v>901530</v>
@@ -42725,7 +42725,7 @@
         <v>64305020</v>
       </c>
       <c r="F2158">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2158">
         <v>561330</v>
@@ -42739,7 +42739,7 @@
         <v>64295538</v>
       </c>
       <c r="F2159">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2159">
         <v>425250</v>
@@ -42753,7 +42753,7 @@
         <v>64295369</v>
       </c>
       <c r="F2160">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2160">
         <v>878850</v>
@@ -42767,7 +42767,7 @@
         <v>64295105</v>
       </c>
       <c r="F2161">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2161">
         <v>561330</v>
@@ -42781,7 +42781,7 @@
         <v>64294796</v>
       </c>
       <c r="F2162">
-        <v>2300000</v>
+        <v>162</v>
       </c>
       <c r="G2162">
         <v>686070</v>
@@ -43901,7 +43901,7 @@
         <v>68580695</v>
       </c>
       <c r="F2242">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2243">
@@ -43912,7 +43912,7 @@
         <v>68580509</v>
       </c>
       <c r="F2243">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2244">
@@ -43923,7 +43923,7 @@
         <v>68580412</v>
       </c>
       <c r="F2244">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2245">
@@ -43934,7 +43934,7 @@
         <v>68580248</v>
       </c>
       <c r="F2245">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2246">
@@ -43945,7 +43945,7 @@
         <v>68580059</v>
       </c>
       <c r="F2246">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2247">
@@ -43956,7 +43956,7 @@
         <v>68579941</v>
       </c>
       <c r="F2247">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2248">
@@ -43967,7 +43967,7 @@
         <v>68579550</v>
       </c>
       <c r="F2248">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2249">
@@ -43978,7 +43978,7 @@
         <v>68579471</v>
       </c>
       <c r="F2249">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2250">
@@ -43989,7 +43989,7 @@
         <v>68579358</v>
       </c>
       <c r="F2250">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2251">
@@ -44000,7 +44000,7 @@
         <v>68579117</v>
       </c>
       <c r="F2251">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2252">
@@ -44011,7 +44011,7 @@
         <v>68579081</v>
       </c>
       <c r="F2252">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2253">
@@ -44022,7 +44022,7 @@
         <v>68578915</v>
       </c>
       <c r="F2253">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2254">
@@ -44033,7 +44033,7 @@
         <v>68578887</v>
       </c>
       <c r="F2254">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2255">
@@ -44044,7 +44044,7 @@
         <v>68578792</v>
       </c>
       <c r="F2255">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2256">
@@ -44055,7 +44055,7 @@
         <v>68578665</v>
       </c>
       <c r="F2256">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2257">
@@ -44066,7 +44066,7 @@
         <v>68577686</v>
       </c>
       <c r="F2257">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2258">
@@ -44077,7 +44077,7 @@
         <v>68577652</v>
       </c>
       <c r="F2258">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2259">
@@ -44088,7 +44088,7 @@
         <v>68576994</v>
       </c>
       <c r="F2259">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2260">
@@ -44099,7 +44099,7 @@
         <v>68576906</v>
       </c>
       <c r="F2260">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2261">
@@ -44110,7 +44110,7 @@
         <v>68573468</v>
       </c>
       <c r="F2261">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2262">
@@ -44121,7 +44121,7 @@
         <v>68573370</v>
       </c>
       <c r="F2262">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2263">
@@ -44132,7 +44132,7 @@
         <v>68572279</v>
       </c>
       <c r="F2263">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2264">
@@ -44143,7 +44143,7 @@
         <v>68315781</v>
       </c>
       <c r="F2264">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2265">
@@ -44154,7 +44154,7 @@
         <v>68315647</v>
       </c>
       <c r="F2265">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2266">
@@ -44165,7 +44165,7 @@
         <v>68297855</v>
       </c>
       <c r="F2266">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2267">
@@ -44176,7 +44176,7 @@
         <v>68297737</v>
       </c>
       <c r="F2267">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2268">
@@ -44187,7 +44187,7 @@
         <v>68297319</v>
       </c>
       <c r="F2268">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2269">
@@ -44198,7 +44198,7 @@
         <v>68289446</v>
       </c>
       <c r="F2269">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2270">
@@ -44223,7 +44223,7 @@
         <v>55555555</v>
       </c>
       <c r="F2271">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2272">
@@ -44234,7 +44234,7 @@
         <v>55555556</v>
       </c>
       <c r="F2272">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2273">
@@ -44242,7 +44242,7 @@
         <v xml:space="preserve">دستمال مرطوب دافی  Q10 </v>
       </c>
       <c r="F2273">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2274">
@@ -45737,7 +45737,7 @@
         <v>72014008</v>
       </c>
       <c r="F2380">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2381">
@@ -46423,7 +46423,7 @@
         <v>00221001</v>
       </c>
       <c r="F2429">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2430">
@@ -47624,7 +47624,7 @@
         <v>74313106</v>
       </c>
       <c r="F2515">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2516">
@@ -48380,7 +48380,7 @@
         <v>00221078</v>
       </c>
       <c r="F2569">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2570">
@@ -48685,7 +48685,7 @@
         <v>75283541</v>
       </c>
       <c r="F2591">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2592">
@@ -48895,7 +48895,7 @@
         <v>00221408</v>
       </c>
       <c r="F2606">
-        <v>3190000</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2607">
@@ -49007,7 +49007,7 @@
         <v>00221721</v>
       </c>
       <c r="F2614">
-        <v>1</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2615">
@@ -49035,7 +49035,7 @@
         <v>00221001</v>
       </c>
       <c r="F2616">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2617">
@@ -49049,7 +49049,7 @@
         <v>00221001</v>
       </c>
       <c r="F2617">
-        <v>239</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2618">
@@ -49830,7 +49830,7 @@
         <v>76410461</v>
       </c>
       <c r="F2673">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2674">
@@ -49911,7 +49911,7 @@
         <v>76636716</v>
       </c>
       <c r="F2679">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2680">
@@ -49922,7 +49922,7 @@
         <v>76636706</v>
       </c>
       <c r="F2680">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2681">
@@ -49933,7 +49933,7 @@
         <v>76636688</v>
       </c>
       <c r="F2681">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2682">
@@ -50311,7 +50311,7 @@
         <v>00221818</v>
       </c>
       <c r="F2708">
-        <v>1</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2709">
@@ -50798,7 +50798,7 @@
         <v>80628922</v>
       </c>
       <c r="F2743">
-        <v>2300000</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2744">
